--- a/tasklist/生命・生態系関連.xlsx
+++ b/tasklist/生命・生態系関連.xlsx
@@ -21,6 +21,9 @@
     <sheet name="更新履歴 " sheetId="13" state="visible" r:id="rId13"/>
     <sheet name="関連性マトリクス" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">核心課題!$A$1:$I$29</definedName>
+  </definedNames>
   <calcPr/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{D0CA8CA8-9F24-4464-BF8E-62219DCF47F9}"/>
@@ -29,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="447" uniqueCount="447">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="449">
   <si>
     <t>課題ID</t>
   </si>
@@ -154,6 +157,12 @@
     <t xml:space="preserve">→ 資源配分の最適解を導出</t>
   </si>
   <si>
+    <t>sympy</t>
+  </si>
+  <si>
+    <t>26.05.01</t>
+  </si>
+  <si>
     <t>BIO-505</t>
   </si>
   <si>
@@ -169,6 +178,9 @@
     <t>中</t>
   </si>
   <si>
+    <t>数式・目的関数・制約条件・パラメータ不足</t>
+  </si>
+  <si>
     <t>BIO-506</t>
   </si>
   <si>
@@ -500,9 +512,6 @@
   </si>
   <si>
     <t>観測データ不足</t>
-  </si>
-  <si>
-    <t>sympy</t>
   </si>
   <si>
     <t>26.04.08</t>
@@ -1383,7 +1392,7 @@
     <numFmt numFmtId="167" formatCode="00.0"/>
     <numFmt numFmtId="168" formatCode="yyyy/mm/dd"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="11.000000"/>
       <name val="Calibri"/>
@@ -1392,6 +1401,11 @@
     <font>
       <sz val="10.000000"/>
       <name val="Times New Roman"/>
+    </font>
+    <font>
+      <sz val="12.000000"/>
+      <color indexed="2"/>
+      <name val="Liberation Sans"/>
     </font>
     <font>
       <sz val="10.500000"/>
@@ -1433,47 +1447,47 @@
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf fontId="2" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
       <protection hidden="0" locked="1"/>
     </xf>
-    <xf fontId="2" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf fontId="2" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf fontId="2" fillId="0" borderId="0" numFmtId="165" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf fontId="2" fillId="0" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf fontId="3" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf fontId="2" fillId="0" borderId="0" numFmtId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf fontId="3" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf fontId="2" fillId="0" borderId="0" numFmtId="166" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf fontId="3" fillId="0" borderId="0" numFmtId="165" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf fontId="3" fillId="0" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf fontId="4" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf fontId="2" fillId="0" borderId="0" numFmtId="167" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf fontId="3" fillId="0" borderId="0" numFmtId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf fontId="2" fillId="0" borderId="0" numFmtId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf fontId="3" fillId="0" borderId="0" numFmtId="166" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf fontId="2" fillId="0" borderId="0" numFmtId="168" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf fontId="5" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf fontId="3" fillId="0" borderId="0" numFmtId="167" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf fontId="3" fillId="0" borderId="0" numFmtId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf fontId="3" fillId="0" borderId="0" numFmtId="168" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1934,6 +1948,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetPr>
+    <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
+    <pageSetUpPr autoPageBreaks="1" fitToPage="1"/>
+  </sheetPr>
   <sheetFormatPr baseColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" style="1" width="10.28125"/>
@@ -2017,10 +2035,10 @@
       <c r="G3" s="1">
         <v>2035</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="H3" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="I3" s="1" t="s">
         <v>20</v>
       </c>
     </row>
@@ -2083,7 +2101,7 @@
       </c>
     </row>
     <row r="6" ht="42.75">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="2" t="s">
         <v>31</v>
       </c>
       <c r="B6" s="1" t="s">
@@ -2104,7 +2122,7 @@
       </c>
     </row>
     <row r="7" ht="28.5">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="2" t="s">
         <v>34</v>
       </c>
       <c r="B7" s="1" t="s">
@@ -2125,7 +2143,7 @@
       </c>
     </row>
     <row r="8" ht="28.5">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="2" t="s">
         <v>38</v>
       </c>
       <c r="B8" s="1" t="s">
@@ -2139,50 +2157,56 @@
       <c r="F8" s="1"/>
       <c r="G8" s="1"/>
       <c r="H8" s="1" t="s">
-        <v>13</v>
+        <v>41</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="9" ht="42.75">
       <c r="A9" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G9" s="1">
         <v>2060</v>
       </c>
+      <c r="H9" s="3" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="10" ht="42.75">
       <c r="A10" s="1" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G10" s="1">
         <v>2065</v>
@@ -2190,16 +2214,16 @@
     </row>
     <row r="11" ht="42.75">
       <c r="A11" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>11</v>
@@ -2213,22 +2237,22 @@
     </row>
     <row r="12" ht="42.75">
       <c r="A12" s="1" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G12" s="1">
         <v>2070</v>
@@ -2236,19 +2260,19 @@
     </row>
     <row r="13" ht="57">
       <c r="A13" s="1" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>12</v>
@@ -2259,22 +2283,22 @@
     </row>
     <row r="14" ht="42.75">
       <c r="A14" s="1" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G14" s="1">
         <v>2080</v>
@@ -2282,22 +2306,22 @@
     </row>
     <row r="15" ht="42.75">
       <c r="A15" s="1" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G15" s="1">
         <v>2090</v>
@@ -2305,16 +2329,16 @@
     </row>
     <row r="16" ht="42.75">
       <c r="A16" s="1" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>11</v>
@@ -2328,22 +2352,22 @@
     </row>
     <row r="17" ht="42.75">
       <c r="A17" s="1" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G17" s="1">
         <v>2065</v>
@@ -2351,22 +2375,22 @@
     </row>
     <row r="18" ht="42.75">
       <c r="A18" s="1" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="G18" s="1">
         <v>2100</v>
@@ -2374,22 +2398,22 @@
     </row>
     <row r="19" ht="42.75">
       <c r="A19" s="1" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C19" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="F19" s="1" t="s">
         <v>86</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="F19" s="1" t="s">
-        <v>83</v>
       </c>
       <c r="G19" s="1">
         <v>2110</v>
@@ -2397,22 +2421,22 @@
     </row>
     <row r="20" ht="42.75">
       <c r="A20" s="1" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G20" s="1">
         <v>2120</v>
@@ -2420,16 +2444,16 @@
     </row>
     <row r="21" ht="42.75">
       <c r="A21" s="1" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="E21" s="1" t="s">
         <v>11</v>
@@ -2443,19 +2467,19 @@
     </row>
     <row r="22" ht="42.75">
       <c r="A22" s="1" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>12</v>
@@ -2468,22 +2492,22 @@
     </row>
     <row r="23" ht="42.75">
       <c r="A23" s="1" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="E23" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G23" s="1">
         <v>2080</v>
@@ -2491,16 +2515,16 @@
     </row>
     <row r="24" ht="42.75">
       <c r="A24" s="1" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>11</v>
@@ -2514,10 +2538,10 @@
     </row>
     <row r="25" ht="28.5">
       <c r="A25" s="4" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C25" s="4"/>
       <c r="D25" s="1"/>
@@ -2525,49 +2549,49 @@
         <v>13</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
     </row>
     <row r="26" ht="28.5">
       <c r="A26" s="4" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="C26" s="4"/>
     </row>
     <row r="27" ht="42.75">
       <c r="A27" s="4" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="C27" s="4"/>
     </row>
     <row r="28" ht="42.75">
       <c r="A28" s="4" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="C28" s="4"/>
     </row>
     <row r="29" ht="28.5">
       <c r="A29" s="4" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="C29" s="4"/>
     </row>
   </sheetData>
   <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <pageSetup paperSize="9" scale="60" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
   <headerFooter/>
 </worksheet>
 </file>
@@ -2582,182 +2606,182 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="5" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="E1" s="5" t="s">
         <v>1</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="2" ht="25.5">
       <c r="A2" s="5" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="C2" s="10">
         <v>6.0220000000000003e+23</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="3" ht="25.5">
       <c r="A3" s="5" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="C3" s="14">
         <v>46244</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="4" ht="25.5">
       <c r="A4" s="5" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C4" s="5">
         <v>101.325</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="5" ht="25.5">
       <c r="A5" s="5" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="C5" s="5">
         <v>1366</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="6" ht="25.5">
       <c r="A6" s="5" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="C6" s="5">
         <v>587</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="7" ht="25.5">
       <c r="A7" s="5" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="C7" s="10">
         <v>299800000</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="8" ht="25.5">
       <c r="A8" s="5" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="C8" s="10">
         <v>6.6259999999999998e-34</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="9" ht="25.5">
       <c r="A9" s="5" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="C9" s="10">
         <v>1.3809999999999999e-23</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
   </sheetData>
@@ -2779,56 +2803,56 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="5" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="H1" s="5" t="s">
         <v>1</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="J1" s="5"/>
       <c r="K1" s="5"/>
     </row>
     <row r="2" ht="25.5">
       <c r="A2" s="5" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="F2" s="5">
         <v>0.23999999999999999</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="H2" s="5">
         <v>0.22</v>
@@ -2837,7 +2861,7 @@
         <v>0.089999999999999997</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="K2" s="5">
         <v>0.29999999999999999</v>
@@ -2845,19 +2869,19 @@
     </row>
     <row r="3" ht="25.5">
       <c r="A3" s="5" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="D3" s="5">
         <v>0.45000000000000001</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="F3" s="5">
         <v>0.42999999999999999</v>
@@ -2866,7 +2890,7 @@
         <v>0.050000000000000003</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="I3" s="5">
         <v>0.25</v>
@@ -2876,19 +2900,19 @@
     </row>
     <row r="4" ht="25.5">
       <c r="A4" s="5" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="D4" s="5">
         <v>0.59999999999999998</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="F4" s="5">
         <v>0.55000000000000004</v>
@@ -2897,7 +2921,7 @@
         <v>0.089999999999999997</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="I4" s="5">
         <v>0.25</v>
@@ -2907,19 +2931,19 @@
     </row>
     <row r="5" ht="25.5">
       <c r="A5" s="5" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="D5" s="5">
         <v>0.29999999999999999</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="F5" s="5">
         <v>0.29999999999999999</v>
@@ -2928,7 +2952,7 @@
         <v>0</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="I5" s="5">
         <v>0.20000000000000001</v>
@@ -2938,19 +2962,19 @@
     </row>
     <row r="6" ht="25.5">
       <c r="A6" s="5" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="D6" s="5">
         <v>0.46999999999999997</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="F6" s="5">
         <v>0.45000000000000001</v>
@@ -2959,7 +2983,7 @@
         <v>0.040000000000000001</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="I6" s="5">
         <v>0.14999999999999999</v>
@@ -2988,25 +3012,25 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="5" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="2" ht="25.5">
@@ -3014,22 +3038,22 @@
         <v>12</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="F2" s="5">
         <v>2025</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="3" ht="25.5">
@@ -3037,114 +3061,114 @@
         <v>12</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="F3" s="5">
         <v>2026</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
     </row>
     <row r="4" ht="25.5">
       <c r="A4" s="5" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="F4" s="5">
         <v>2024</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="5" ht="38.25">
       <c r="A5" s="5" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="F5" s="5">
         <v>2024</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="6" ht="25.5">
       <c r="A6" s="5" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="F6" s="5">
         <v>2030</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
     </row>
     <row r="7" ht="25.5">
       <c r="A7" s="5" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="F7" s="5">
         <v>2028</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
     </row>
   </sheetData>
@@ -3171,28 +3195,28 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="5" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="2" ht="25.5">
@@ -3200,10 +3224,10 @@
         <v>45306</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="D2" s="5">
         <v>0.20000000000000001</v>
@@ -3212,13 +3236,13 @@
         <v>0.22</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="3" ht="25.5">
@@ -3226,10 +3250,10 @@
         <v>45301</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="D3" s="5">
         <v>0.12</v>
@@ -3238,13 +3262,13 @@
         <v>0.14999999999999999</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="4" ht="25.5">
@@ -3252,10 +3276,10 @@
         <v>45265</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="D4" s="5">
         <v>150</v>
@@ -3264,13 +3288,13 @@
         <v>180</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="5" ht="38.25">
@@ -3278,10 +3302,10 @@
         <v>45250</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="D5" s="5">
         <v>0.080000000000000002</v>
@@ -3290,13 +3314,13 @@
         <v>0.10000000000000001</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
     </row>
   </sheetData>
@@ -3319,104 +3343,104 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="5" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="2" ht="38.25">
       <c r="A2" s="5" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C2" s="5">
         <v>0.84999999999999998</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="3" ht="38.25">
       <c r="A3" s="5" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="C3" s="5">
         <v>0.59999999999999998</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
     </row>
     <row r="4" ht="38.25">
       <c r="A4" s="5" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C4" s="5">
         <v>0.75</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
     <row r="5" ht="38.25">
       <c r="A5" s="5" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C5" s="5">
         <v>0.40000000000000002</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
     </row>
     <row r="6" ht="38.25">
       <c r="A6" s="5" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="C6" s="5">
         <v>-0.69999999999999996</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
     </row>
   </sheetData>
@@ -3439,32 +3463,32 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="5" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
     </row>
     <row r="2" ht="25.5">
       <c r="A2" s="5" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C3" s="6">
         <v>1</v>
@@ -3472,10 +3496,10 @@
     </row>
     <row r="4">
       <c r="A4" s="5" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="C4" s="5">
         <v>2024</v>
@@ -3483,35 +3507,35 @@
     </row>
     <row r="5" ht="38.25">
       <c r="A5" s="5" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
     </row>
     <row r="6" ht="25.5">
       <c r="A6" s="5" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
     </row>
   </sheetData>
@@ -3534,92 +3558,92 @@
   <sheetData>
     <row r="1" ht="14.25">
       <c r="A1" s="5" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="J1" s="5" t="s">
         <v>1</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
     </row>
     <row r="2" ht="51">
       <c r="A2" s="5" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="E2" s="7">
         <v>0.0001</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="L2" s="5" t="s">
-        <v>157</v>
+        <v>41</v>
       </c>
       <c r="M2" s="5" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="3" ht="51">
       <c r="A3" s="5" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="E3" s="8">
         <v>0.22</v>
@@ -3628,36 +3652,36 @@
         <v>0.25</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="J3" s="5" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="K3" s="5" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="M3" s="9" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="4" ht="38.25">
       <c r="A4" s="5" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="E4" s="6">
         <v>0.5</v>
@@ -3666,39 +3690,39 @@
         <v>0.80000000000000004</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="K4" s="5" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="L4" s="5" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="M4" s="5" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="5" ht="25.5">
       <c r="A5" s="5" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="E5" s="10">
         <v>1.0000000000000001e-15</v>
@@ -3707,19 +3731,19 @@
         <v>1e-10</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="J5" s="5" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="K5" s="5" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
   </sheetData>
@@ -3741,52 +3765,52 @@
   <sheetData>
     <row r="1" ht="14.25">
       <c r="A1" s="5" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="J1" s="5" t="s">
         <v>1</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="L1" s="5"/>
     </row>
     <row r="2" ht="51">
       <c r="A2" s="5" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="E2" s="11">
         <v>0.012</v>
@@ -3795,39 +3819,39 @@
         <v>0.014999999999999999</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="H2" s="5" t="s">
         <v>12</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="L2" s="5" t="s">
         <v>19</v>
       </c>
       <c r="M2" s="5" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="3" ht="51">
       <c r="A3" s="5" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="E3" s="8">
         <v>0.14999999999999999</v>
@@ -3836,39 +3860,39 @@
         <v>0.29999999999999999</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="J3" s="5" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="K3" s="5" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="L3" s="5" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="M3" s="5" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="4" ht="51">
       <c r="A4" s="5" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="E4" s="6">
         <v>0.29999999999999999</v>
@@ -3877,39 +3901,39 @@
         <v>0.90000000000000002</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="K4" s="5" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="L4" s="5" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="M4" s="5" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="5" s="12" customFormat="1" ht="38.25">
       <c r="A5" s="12" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="E5" s="12">
         <v>10</v>
@@ -3918,23 +3942,23 @@
         <v>5</v>
       </c>
       <c r="G5" s="12" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="H5" s="12" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="I5" s="12" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="J5" s="12" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="K5" s="12" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="L5" s="12"/>
       <c r="M5" s="9" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
   </sheetData>
@@ -3958,60 +3982,60 @@
   <sheetData>
     <row r="1" ht="14.25">
       <c r="A1" s="5" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="J1" s="5" t="s">
         <v>1</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
     </row>
     <row r="2" ht="63.75">
       <c r="A2" s="5" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H2" s="5">
         <v>180</v>
@@ -4020,39 +4044,39 @@
         <v>3650</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="L2" s="5" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="M2" s="5" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="N2" s="5" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="O2" s="5" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="P2" s="5" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="3" ht="51">
       <c r="A3" s="5" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="E3" s="8">
         <v>0.84999999999999998</v>
@@ -4061,33 +4085,33 @@
         <v>0.98999999999999999</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="J3" s="5" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="K3" s="5" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="4" ht="38.25">
       <c r="A4" s="5" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="E4" s="6">
         <v>1.5</v>
@@ -4096,33 +4120,33 @@
         <v>2.5</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="K4" s="5" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
     </row>
     <row r="5" ht="51">
       <c r="A5" s="5" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="E5" s="6">
         <v>0.69999999999999996</v>
@@ -4131,19 +4155,19 @@
         <v>1.05</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="H5" s="5" t="s">
         <v>12</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="J5" s="5" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="K5" s="5" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
     </row>
   </sheetData>
@@ -4165,51 +4189,51 @@
   <sheetData>
     <row r="1" ht="14.25">
       <c r="A1" s="5" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="J1" s="5" t="s">
         <v>1</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
     </row>
     <row r="2" ht="38.25">
       <c r="A2" s="5" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="E2" s="8">
         <v>0.25</v>
@@ -4218,33 +4242,33 @@
         <v>0.90000000000000002</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="3" ht="63.75">
       <c r="A3" s="5" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="E3" s="6">
         <v>1.5</v>
@@ -4253,33 +4277,33 @@
         <v>10</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="J3" s="5" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="K3" s="5" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="4" ht="25.5">
       <c r="A4" s="5" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="E4" s="8">
         <v>0.01</v>
@@ -4288,33 +4312,33 @@
         <v>0.10000000000000001</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="K4" s="5" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="5" ht="38.25">
       <c r="A5" s="5" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="E5" s="8">
         <v>0.29999999999999999</v>
@@ -4323,19 +4347,19 @@
         <v>0.80000000000000004</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="J5" s="5" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="K5" s="5" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
   </sheetData>
@@ -4359,51 +4383,51 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="5" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="J1" s="5" t="s">
         <v>1</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
     </row>
     <row r="2" ht="38.25">
       <c r="A2" s="5" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="E2" s="5">
         <v>0.10000000000000001</v>
@@ -4412,33 +4436,33 @@
         <v>0.94999999999999996</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
     </row>
     <row r="3" ht="51">
       <c r="A3" s="5" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="E3" s="5">
         <v>100</v>
@@ -4447,33 +4471,33 @@
         <v>1</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="H3" s="5" t="s">
         <v>12</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="J3" s="5" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="K3" s="5" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="4" ht="51">
       <c r="A4" s="5" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="E4" s="5">
         <v>0.10000000000000001</v>
@@ -4482,33 +4506,33 @@
         <v>0.001</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="K4" s="5" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="5" ht="51">
       <c r="A5" s="5" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="E5" s="5">
         <v>0.69999999999999996</v>
@@ -4517,19 +4541,19 @@
         <v>0.98999999999999999</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="J5" s="5" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="K5" s="5" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
   </sheetData>
@@ -4553,37 +4577,37 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="5" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="J1" s="5" t="s">
         <v>1</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
     </row>
     <row r="2" ht="38.25">
@@ -4591,13 +4615,13 @@
         <v>7</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E2" s="5">
         <v>10000</v>
@@ -4606,19 +4630,19 @@
         <v>100</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="3" ht="51">
@@ -4626,13 +4650,13 @@
         <v>15</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="E3" s="5">
         <v>100</v>
@@ -4641,19 +4665,19 @@
         <v>10</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="J3" s="5" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="K3" s="5" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="4" ht="51">
@@ -4661,19 +4685,19 @@
         <v>21</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="G4" s="5">
         <v>10</v>
@@ -4682,19 +4706,19 @@
         <v>2</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="K4" s="5" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="L4" s="5" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="M4" s="5" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="5" ht="51">
@@ -4702,13 +4726,13 @@
         <v>25</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="E5" s="5">
         <v>0.80000000000000004</v>
@@ -4717,19 +4741,19 @@
         <v>0.59999999999999998</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="J5" s="5" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="K5" s="5" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
   </sheetData>
@@ -4754,45 +4778,45 @@
   <sheetData>
     <row r="1" ht="28.5">
       <c r="A1" s="5" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="F1" s="5" t="s">
         <v>1</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
     </row>
     <row r="2" ht="25.5">
       <c r="A2" s="5" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="C2" s="10">
         <v>200000000000</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="G2" s="5" t="s">
         <v>12</v>
@@ -4800,22 +4824,22 @@
     </row>
     <row r="3" ht="42.75">
       <c r="A3" s="5" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="C3" s="5">
         <v>5500</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="G3" s="5" t="s">
         <v>12</v>
@@ -4823,45 +4847,45 @@
     </row>
     <row r="4" ht="28.5">
       <c r="A4" s="5" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="C4" s="5">
         <v>24</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="5" ht="25.5">
       <c r="A5" s="5" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="C5" s="10">
         <v>4540000000</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="G5" s="5" t="s">
         <v>12</v>
@@ -4869,45 +4893,45 @@
     </row>
     <row r="6" ht="28.5">
       <c r="A6" s="5" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="C6" s="10">
         <v>500000000</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="7" ht="28.5">
       <c r="A7" s="5" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="C7" s="5">
         <v>230</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="G7" s="5" t="s">
         <v>12</v>
@@ -4915,45 +4939,45 @@
     </row>
     <row r="8" ht="28.5">
       <c r="A8" s="5" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="C8" s="5">
         <v>0.01</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="9" ht="25.5">
       <c r="A9" s="5" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="C9" s="5">
         <v>1366</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="G9" s="5" t="s">
         <v>12</v>
@@ -4961,22 +4985,22 @@
     </row>
     <row r="10" ht="25.5">
       <c r="A10" s="5" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="C10" s="5">
         <v>587</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="G10" s="5" t="s">
         <v>12</v>
@@ -4984,22 +5008,22 @@
     </row>
     <row r="11" ht="25.5">
       <c r="A11" s="5" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C11" s="5">
         <v>101.325</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="G11" s="5" t="s">
         <v>12</v>

--- a/tasklist/生命・生態系関連.xlsx
+++ b/tasklist/生命・生態系関連.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="449">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="451" uniqueCount="451">
   <si>
     <t>課題ID</t>
   </si>
@@ -178,7 +178,7 @@
     <t>中</t>
   </si>
   <si>
-    <t>数式・目的関数・制約条件・パラメータ不足</t>
+    <t>26.05.30</t>
   </si>
   <si>
     <t>BIO-506</t>
@@ -341,6 +341,12 @@
   </si>
   <si>
     <t>どこまで改造しても「人間」と言えるかの定量化</t>
+  </si>
+  <si>
+    <t>+maxima</t>
+  </si>
+  <si>
+    <t>26.05.29</t>
   </si>
   <si>
     <t>BIO-519</t>
@@ -1392,7 +1398,7 @@
     <numFmt numFmtId="167" formatCode="00.0"/>
     <numFmt numFmtId="168" formatCode="yyyy/mm/dd"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="11.000000"/>
       <name val="Calibri"/>
@@ -1403,6 +1409,13 @@
       <name val="Times New Roman"/>
     </font>
     <font>
+      <b/>
+      <sz val="11.000000"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="12.000000"/>
       <color indexed="2"/>
       <name val="Liberation Sans"/>
@@ -1422,12 +1435,18 @@
       <name val="IPAゴシック"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1" tint="0.499984740745262"/>
+        <bgColor theme="1" tint="0.499984740745262"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -1442,7 +1461,7 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="20">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -1451,43 +1470,56 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf fontId="2" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf fontId="3" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1" quotePrefix="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
       <protection hidden="0" locked="1"/>
     </xf>
-    <xf fontId="3" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf fontId="0" fillId="2" borderId="0" numFmtId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf fontId="3" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf fontId="0" fillId="2" borderId="0" numFmtId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf fontId="3" fillId="0" borderId="0" numFmtId="165" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf fontId="3" fillId="0" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+      <protection hidden="0" locked="1"/>
     </xf>
     <xf fontId="4" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf fontId="3" fillId="0" borderId="0" numFmtId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf fontId="4" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf fontId="3" fillId="0" borderId="0" numFmtId="166" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf fontId="4" fillId="0" borderId="0" numFmtId="165" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf fontId="4" fillId="0" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf fontId="5" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf fontId="3" fillId="0" borderId="0" numFmtId="167" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf fontId="4" fillId="0" borderId="0" numFmtId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf fontId="3" fillId="0" borderId="0" numFmtId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf fontId="4" fillId="0" borderId="0" numFmtId="166" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf fontId="3" fillId="0" borderId="0" numFmtId="168" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf fontId="6" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf fontId="4" fillId="0" borderId="0" numFmtId="167" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf fontId="4" fillId="0" borderId="0" numFmtId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf fontId="4" fillId="0" borderId="0" numFmtId="168" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2163,75 +2195,76 @@
         <v>42</v>
       </c>
     </row>
-    <row r="9" ht="42.75">
-      <c r="A9" s="1" t="s">
+    <row r="9" s="3" customFormat="1" ht="42.75">
+      <c r="A9" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C9" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="D9" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="E9" s="1" t="s">
+      <c r="E9" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="F9" s="1" t="s">
+      <c r="F9" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="G9" s="1">
+      <c r="G9" s="3">
         <v>2060</v>
       </c>
-      <c r="H9" s="3" t="s">
+      <c r="H9" s="4"/>
+      <c r="I9" s="3" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="10" ht="42.75">
-      <c r="A10" s="1" t="s">
+    <row r="10" s="3" customFormat="1" ht="42.75">
+      <c r="A10" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B10" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="C10" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="D10" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="E10" s="1" t="s">
+      <c r="E10" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="F10" s="1" t="s">
+      <c r="F10" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="G10" s="1">
+      <c r="G10" s="3">
         <v>2065</v>
       </c>
     </row>
-    <row r="11" ht="42.75">
-      <c r="A11" s="1" t="s">
+    <row r="11" s="3" customFormat="1" ht="42.75">
+      <c r="A11" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="B11" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="C11" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="D11" s="1" t="s">
+      <c r="D11" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="E11" s="1" t="s">
+      <c r="E11" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="F11" s="1" t="s">
+      <c r="F11" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G11" s="1">
+      <c r="G11" s="3">
         <v>2030</v>
       </c>
     </row>
@@ -2281,26 +2314,26 @@
         <v>2075</v>
       </c>
     </row>
-    <row r="14" ht="42.75">
-      <c r="A14" s="1" t="s">
+    <row r="14" s="3" customFormat="1" ht="42.75">
+      <c r="A14" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="B14" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="C14" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="D14" s="1" t="s">
+      <c r="D14" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="E14" s="1" t="s">
+      <c r="E14" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="F14" s="1" t="s">
+      <c r="F14" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="G14" s="1">
+      <c r="G14" s="3">
         <v>2080</v>
       </c>
     </row>
@@ -2487,21 +2520,25 @@
       <c r="G22" s="1">
         <v>2040</v>
       </c>
-      <c r="H22" s="1"/>
-      <c r="I22" s="1"/>
+      <c r="H22" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="23" ht="42.75">
       <c r="A23" s="1" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E23" s="1" t="s">
         <v>11</v>
@@ -2515,16 +2552,16 @@
     </row>
     <row r="24" ht="42.75">
       <c r="A24" s="1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>11</v>
@@ -2537,56 +2574,57 @@
       </c>
     </row>
     <row r="25" ht="28.5">
-      <c r="A25" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="B25" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="C25" s="4"/>
+      <c r="A25" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="C25" s="6"/>
       <c r="D25" s="1"/>
       <c r="H25" s="1" t="s">
         <v>13</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="26" ht="28.5">
-      <c r="A26" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="B26" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="C26" s="4"/>
+    </row>
+    <row r="26" s="7" customFormat="1" ht="28.5">
+      <c r="A26" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="B26" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="C26" s="8"/>
+      <c r="D26" s="7"/>
     </row>
     <row r="27" ht="42.75">
-      <c r="A27" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="B27" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="C27" s="4"/>
+      <c r="A27" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="C27" s="6"/>
     </row>
     <row r="28" ht="42.75">
-      <c r="A28" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="B28" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="C28" s="4"/>
+      <c r="A28" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="C28" s="6"/>
     </row>
     <row r="29" ht="28.5">
-      <c r="A29" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="B29" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="C29" s="4"/>
+      <c r="A29" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="C29" s="6"/>
     </row>
   </sheetData>
   <printOptions headings="0" gridLines="0"/>
@@ -2605,183 +2643,183 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="9" t="s">
+        <v>343</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>305</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>306</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="2" ht="25.5">
+      <c r="A2" s="9" t="s">
+        <v>344</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>345</v>
+      </c>
+      <c r="C2" s="14">
+        <v>6.0220000000000003e+23</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>346</v>
+      </c>
+      <c r="E2" s="9" t="s">
+        <v>347</v>
+      </c>
+      <c r="F2" s="9" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="3" ht="25.5">
+      <c r="A3" s="9" t="s">
+        <v>349</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>350</v>
+      </c>
+      <c r="C3" s="18">
+        <v>46244</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>351</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>187</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="4" ht="25.5">
+      <c r="A4" s="9" t="s">
+        <v>353</v>
+      </c>
+      <c r="B4" s="9" t="s">
         <v>341</v>
       </c>
-      <c r="B1" s="5" t="s">
-        <v>303</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>304</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="2" ht="25.5">
-      <c r="A2" s="5" t="s">
+      <c r="C4" s="9">
+        <v>101.325</v>
+      </c>
+      <c r="D4" s="9" t="s">
         <v>342</v>
       </c>
-      <c r="B2" s="5" t="s">
-        <v>343</v>
-      </c>
-      <c r="C2" s="10">
-        <v>6.0220000000000003e+23</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>344</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>345</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="3" ht="25.5">
-      <c r="A3" s="5" t="s">
-        <v>347</v>
-      </c>
-      <c r="B3" s="5" t="s">
+      <c r="E4" s="9" t="s">
+        <v>329</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="5" ht="25.5">
+      <c r="A5" s="9" t="s">
+        <v>355</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>356</v>
+      </c>
+      <c r="C5" s="9">
+        <v>1366</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>335</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="6" ht="25.5">
+      <c r="A6" s="9" t="s">
+        <v>358</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>359</v>
+      </c>
+      <c r="C6" s="9">
+        <v>587</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>335</v>
+      </c>
+      <c r="E6" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="F6" s="9" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="7" ht="25.5">
+      <c r="A7" s="9" t="s">
+        <v>360</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>361</v>
+      </c>
+      <c r="C7" s="14">
+        <v>299800000</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>362</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>363</v>
+      </c>
+      <c r="F7" s="9" t="s">
         <v>348</v>
       </c>
-      <c r="C3" s="14">
-        <v>46244</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>349</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>185</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="4" ht="25.5">
-      <c r="A4" s="5" t="s">
-        <v>351</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>339</v>
-      </c>
-      <c r="C4" s="5">
-        <v>101.325</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>340</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>327</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="5" ht="25.5">
-      <c r="A5" s="5" t="s">
-        <v>353</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>354</v>
-      </c>
-      <c r="C5" s="5">
-        <v>1366</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>333</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="6" ht="25.5">
-      <c r="A6" s="5" t="s">
-        <v>356</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>357</v>
-      </c>
-      <c r="C6" s="5">
-        <v>587</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>333</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="7" ht="25.5">
-      <c r="A7" s="5" t="s">
-        <v>358</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>359</v>
-      </c>
-      <c r="C7" s="10">
-        <v>299800000</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>360</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>361</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>346</v>
-      </c>
     </row>
     <row r="8" ht="25.5">
-      <c r="A8" s="5" t="s">
-        <v>362</v>
-      </c>
-      <c r="B8" s="5" t="s">
+      <c r="A8" s="9" t="s">
+        <v>364</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>365</v>
+      </c>
+      <c r="C8" s="14">
+        <v>6.6259999999999998e-34</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>366</v>
+      </c>
+      <c r="E8" s="9" t="s">
         <v>363</v>
       </c>
-      <c r="C8" s="10">
-        <v>6.6259999999999998e-34</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>364</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>361</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>346</v>
+      <c r="F8" s="9" t="s">
+        <v>348</v>
       </c>
     </row>
     <row r="9" ht="25.5">
-      <c r="A9" s="5" t="s">
-        <v>365</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>366</v>
-      </c>
-      <c r="C9" s="10">
+      <c r="A9" s="9" t="s">
+        <v>367</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>368</v>
+      </c>
+      <c r="C9" s="14">
         <v>1.3809999999999999e-23</v>
       </c>
-      <c r="D9" s="5" t="s">
-        <v>367</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>361</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>346</v>
+      <c r="D9" s="9" t="s">
+        <v>369</v>
+      </c>
+      <c r="E9" s="9" t="s">
+        <v>363</v>
+      </c>
+      <c r="F9" s="9" t="s">
+        <v>348</v>
       </c>
     </row>
   </sheetData>
@@ -2802,194 +2840,194 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="s">
-        <v>368</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>369</v>
-      </c>
-      <c r="C1" s="5" t="s">
+      <c r="A1" s="9" t="s">
         <v>370</v>
       </c>
-      <c r="D1" s="5" t="s">
-        <v>145</v>
-      </c>
-      <c r="E1" s="5" t="s">
+      <c r="B1" s="9" t="s">
         <v>371</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="C1" s="9" t="s">
         <v>372</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="D1" s="9" t="s">
+        <v>147</v>
+      </c>
+      <c r="E1" s="9" t="s">
         <v>373</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="F1" s="9" t="s">
+        <v>374</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>375</v>
+      </c>
+      <c r="H1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="I1" s="5" t="s">
-        <v>374</v>
-      </c>
-      <c r="J1" s="5"/>
-      <c r="K1" s="5"/>
+      <c r="I1" s="9" t="s">
+        <v>376</v>
+      </c>
+      <c r="J1" s="9"/>
+      <c r="K1" s="9"/>
     </row>
     <row r="2" ht="25.5">
-      <c r="A2" s="5" t="s">
-        <v>375</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>376</v>
-      </c>
-      <c r="C2" s="5" t="s">
+      <c r="A2" s="9" t="s">
         <v>377</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="B2" s="9" t="s">
         <v>378</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="C2" s="9" t="s">
         <v>379</v>
       </c>
-      <c r="F2" s="5">
+      <c r="D2" s="9" t="s">
+        <v>380</v>
+      </c>
+      <c r="E2" s="9" t="s">
+        <v>381</v>
+      </c>
+      <c r="F2" s="9">
         <v>0.23999999999999999</v>
       </c>
-      <c r="G2" s="5" t="s">
-        <v>380</v>
-      </c>
-      <c r="H2" s="5">
+      <c r="G2" s="9" t="s">
+        <v>382</v>
+      </c>
+      <c r="H2" s="9">
         <v>0.22</v>
       </c>
-      <c r="I2" s="5">
+      <c r="I2" s="9">
         <v>0.089999999999999997</v>
       </c>
-      <c r="J2" s="5" t="s">
-        <v>381</v>
-      </c>
-      <c r="K2" s="5">
+      <c r="J2" s="9" t="s">
+        <v>383</v>
+      </c>
+      <c r="K2" s="9">
         <v>0.29999999999999999</v>
       </c>
     </row>
     <row r="3" ht="25.5">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="9" t="s">
+        <v>384</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>385</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>386</v>
+      </c>
+      <c r="D3" s="9">
+        <v>0.45000000000000001</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>387</v>
+      </c>
+      <c r="F3" s="9">
+        <v>0.42999999999999999</v>
+      </c>
+      <c r="G3" s="9">
+        <v>0.050000000000000003</v>
+      </c>
+      <c r="H3" s="9" t="s">
+        <v>388</v>
+      </c>
+      <c r="I3" s="9">
+        <v>0.25</v>
+      </c>
+      <c r="J3" s="9"/>
+      <c r="K3" s="9"/>
+    </row>
+    <row r="4" ht="25.5">
+      <c r="A4" s="9" t="s">
+        <v>389</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>390</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>391</v>
+      </c>
+      <c r="D4" s="9">
+        <v>0.59999999999999998</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>392</v>
+      </c>
+      <c r="F4" s="9">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="G4" s="9">
+        <v>0.089999999999999997</v>
+      </c>
+      <c r="H4" s="9" t="s">
+        <v>264</v>
+      </c>
+      <c r="I4" s="9">
+        <v>0.25</v>
+      </c>
+      <c r="J4" s="9"/>
+      <c r="K4" s="9"/>
+    </row>
+    <row r="5" ht="25.5">
+      <c r="A5" s="9" t="s">
+        <v>393</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>394</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>395</v>
+      </c>
+      <c r="D5" s="9">
+        <v>0.29999999999999999</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>396</v>
+      </c>
+      <c r="F5" s="9">
+        <v>0.29999999999999999</v>
+      </c>
+      <c r="G5" s="9">
+        <v>0</v>
+      </c>
+      <c r="H5" s="9" t="s">
+        <v>397</v>
+      </c>
+      <c r="I5" s="9">
+        <v>0.20000000000000001</v>
+      </c>
+      <c r="J5" s="9"/>
+      <c r="K5" s="9"/>
+    </row>
+    <row r="6" ht="25.5">
+      <c r="A6" s="9" t="s">
+        <v>398</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>399</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>400</v>
+      </c>
+      <c r="D6" s="9">
+        <v>0.46999999999999997</v>
+      </c>
+      <c r="E6" s="9" t="s">
         <v>382</v>
       </c>
-      <c r="B3" s="5" t="s">
-        <v>383</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>384</v>
-      </c>
-      <c r="D3" s="5">
+      <c r="F6" s="9">
         <v>0.45000000000000001</v>
       </c>
-      <c r="E3" s="5" t="s">
-        <v>385</v>
-      </c>
-      <c r="F3" s="5">
-        <v>0.42999999999999999</v>
-      </c>
-      <c r="G3" s="5">
-        <v>0.050000000000000003</v>
-      </c>
-      <c r="H3" s="5" t="s">
-        <v>386</v>
-      </c>
-      <c r="I3" s="5">
-        <v>0.25</v>
-      </c>
-      <c r="J3" s="5"/>
-      <c r="K3" s="5"/>
-    </row>
-    <row r="4" ht="25.5">
-      <c r="A4" s="5" t="s">
-        <v>387</v>
-      </c>
-      <c r="B4" s="5" t="s">
+      <c r="G6" s="9">
+        <v>0.040000000000000001</v>
+      </c>
+      <c r="H6" s="9" t="s">
         <v>388</v>
       </c>
-      <c r="C4" s="5" t="s">
-        <v>389</v>
-      </c>
-      <c r="D4" s="5">
-        <v>0.59999999999999998</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>390</v>
-      </c>
-      <c r="F4" s="5">
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="G4" s="5">
-        <v>0.089999999999999997</v>
-      </c>
-      <c r="H4" s="5" t="s">
-        <v>262</v>
-      </c>
-      <c r="I4" s="5">
-        <v>0.25</v>
-      </c>
-      <c r="J4" s="5"/>
-      <c r="K4" s="5"/>
-    </row>
-    <row r="5" ht="25.5">
-      <c r="A5" s="5" t="s">
-        <v>391</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>392</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>393</v>
-      </c>
-      <c r="D5" s="5">
-        <v>0.29999999999999999</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>394</v>
-      </c>
-      <c r="F5" s="5">
-        <v>0.29999999999999999</v>
-      </c>
-      <c r="G5" s="5">
-        <v>0</v>
-      </c>
-      <c r="H5" s="5" t="s">
-        <v>395</v>
-      </c>
-      <c r="I5" s="5">
-        <v>0.20000000000000001</v>
-      </c>
-      <c r="J5" s="5"/>
-      <c r="K5" s="5"/>
-    </row>
-    <row r="6" ht="25.5">
-      <c r="A6" s="5" t="s">
-        <v>396</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>397</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>398</v>
-      </c>
-      <c r="D6" s="5">
-        <v>0.46999999999999997</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>380</v>
-      </c>
-      <c r="F6" s="5">
-        <v>0.45000000000000001</v>
-      </c>
-      <c r="G6" s="5">
-        <v>0.040000000000000001</v>
-      </c>
-      <c r="H6" s="5" t="s">
-        <v>386</v>
-      </c>
-      <c r="I6" s="5">
+      <c r="I6" s="9">
         <v>0.14999999999999999</v>
       </c>
-      <c r="J6" s="5"/>
-      <c r="K6" s="5"/>
+      <c r="J6" s="9"/>
+      <c r="K6" s="9"/>
     </row>
   </sheetData>
   <printOptions headings="0" gridLines="0"/>
@@ -3003,172 +3041,172 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="2" style="5" width="9.140625"/>
-    <col customWidth="1" min="3" max="3" style="5" width="11.421875"/>
-    <col customWidth="1" min="4" max="4" style="5" width="10.8515625"/>
-    <col customWidth="1" min="5" max="5" style="5" width="14.140625"/>
-    <col min="6" max="16384" style="5" width="9.140625"/>
+    <col min="1" max="2" style="9" width="9.140625"/>
+    <col customWidth="1" min="3" max="3" style="9" width="11.421875"/>
+    <col customWidth="1" min="4" max="4" style="9" width="10.8515625"/>
+    <col customWidth="1" min="5" max="5" style="9" width="14.140625"/>
+    <col min="6" max="16384" style="9" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="s">
-        <v>399</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>400</v>
-      </c>
-      <c r="E1" s="5" t="s">
+      <c r="A1" s="9" t="s">
         <v>401</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="B1" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="D1" s="9" t="s">
         <v>402</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="E1" s="9" t="s">
         <v>403</v>
       </c>
+      <c r="F1" s="9" t="s">
+        <v>404</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>405</v>
+      </c>
     </row>
     <row r="2" ht="25.5">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>152</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>159</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>404</v>
-      </c>
-      <c r="F2" s="5">
+      <c r="B2" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>154</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="E2" s="9" t="s">
+        <v>406</v>
+      </c>
+      <c r="F2" s="9">
         <v>2025</v>
       </c>
-      <c r="G2" s="5" t="s">
-        <v>405</v>
+      <c r="G2" s="9" t="s">
+        <v>407</v>
       </c>
     </row>
     <row r="3" ht="25.5">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="5" t="s">
-        <v>236</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>237</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>406</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>407</v>
-      </c>
-      <c r="F3" s="5">
+      <c r="B3" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>408</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>409</v>
+      </c>
+      <c r="F3" s="9">
         <v>2026</v>
       </c>
-      <c r="G3" s="5" t="s">
-        <v>408</v>
+      <c r="G3" s="9" t="s">
+        <v>410</v>
       </c>
     </row>
     <row r="4" ht="25.5">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>181</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>182</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>410</v>
-      </c>
-      <c r="F4" s="5">
+      <c r="B4" s="9" t="s">
+        <v>183</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>411</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>412</v>
+      </c>
+      <c r="F4" s="9">
         <v>2024</v>
       </c>
-      <c r="G4" s="5" t="s">
-        <v>411</v>
+      <c r="G4" s="9" t="s">
+        <v>413</v>
       </c>
     </row>
     <row r="5" ht="38.25">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="B5" s="5" t="s">
-        <v>258</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>259</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>412</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>413</v>
-      </c>
-      <c r="F5" s="5">
+      <c r="B5" s="9" t="s">
+        <v>260</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>261</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>414</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>415</v>
+      </c>
+      <c r="F5" s="9">
         <v>2024</v>
       </c>
-      <c r="G5" s="5" t="s">
-        <v>414</v>
+      <c r="G5" s="9" t="s">
+        <v>416</v>
       </c>
     </row>
     <row r="6" ht="25.5">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="B6" s="5" t="s">
-        <v>175</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>176</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>415</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>416</v>
-      </c>
-      <c r="F6" s="5">
+      <c r="B6" s="9" t="s">
+        <v>177</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>417</v>
+      </c>
+      <c r="E6" s="9" t="s">
+        <v>418</v>
+      </c>
+      <c r="F6" s="9">
         <v>2030</v>
       </c>
-      <c r="G6" s="5" t="s">
-        <v>417</v>
+      <c r="G6" s="9" t="s">
+        <v>419</v>
       </c>
     </row>
     <row r="7" ht="25.5">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="B7" s="5" t="s">
-        <v>247</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>248</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>252</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>418</v>
-      </c>
-      <c r="F7" s="5">
+      <c r="B7" s="9" t="s">
+        <v>249</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>250</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>254</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>420</v>
+      </c>
+      <c r="F7" s="9">
         <v>2028</v>
       </c>
-      <c r="G7" s="5" t="s">
-        <v>419</v>
+      <c r="G7" s="9" t="s">
+        <v>421</v>
       </c>
     </row>
   </sheetData>
@@ -3183,144 +3221,144 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col bestFit="1" min="1" max="1" style="5" width="10.7109375"/>
-    <col min="2" max="2" style="5" width="9.140625"/>
-    <col customWidth="1" min="3" max="3" style="5" width="10.7109375"/>
-    <col min="4" max="5" style="5" width="9.140625"/>
-    <col customWidth="1" min="6" max="6" style="5" width="11.57421875"/>
-    <col min="7" max="7" style="5" width="9.140625"/>
-    <col customWidth="1" min="8" max="8" style="5" width="10.8515625"/>
-    <col min="9" max="16384" style="5" width="9.140625"/>
+    <col bestFit="1" min="1" max="1" style="9" width="10.7109375"/>
+    <col min="2" max="2" style="9" width="9.140625"/>
+    <col customWidth="1" min="3" max="3" style="9" width="10.7109375"/>
+    <col min="4" max="5" style="9" width="9.140625"/>
+    <col customWidth="1" min="6" max="6" style="9" width="11.57421875"/>
+    <col min="7" max="7" style="9" width="9.140625"/>
+    <col customWidth="1" min="8" max="8" style="9" width="10.8515625"/>
+    <col min="9" max="16384" style="9" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="s">
-        <v>420</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>421</v>
-      </c>
-      <c r="E1" s="5" t="s">
+      <c r="A1" s="9" t="s">
         <v>422</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="B1" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="D1" s="9" t="s">
         <v>423</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="E1" s="9" t="s">
         <v>424</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="F1" s="9" t="s">
         <v>425</v>
       </c>
+      <c r="G1" s="9" t="s">
+        <v>426</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>427</v>
+      </c>
     </row>
     <row r="2" ht="25.5">
-      <c r="A2" s="15">
+      <c r="A2" s="19">
         <v>45306</v>
       </c>
-      <c r="B2" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>162</v>
-      </c>
-      <c r="D2" s="5">
+      <c r="B2" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="D2" s="9">
         <v>0.20000000000000001</v>
       </c>
-      <c r="E2" s="5">
+      <c r="E2" s="9">
         <v>0.22</v>
       </c>
-      <c r="F2" s="5" t="s">
-        <v>426</v>
-      </c>
-      <c r="G2" s="5" t="s">
-        <v>405</v>
-      </c>
-      <c r="H2" s="5" t="s">
-        <v>427</v>
+      <c r="F2" s="9" t="s">
+        <v>428</v>
+      </c>
+      <c r="G2" s="9" t="s">
+        <v>407</v>
+      </c>
+      <c r="H2" s="9" t="s">
+        <v>429</v>
       </c>
     </row>
     <row r="3" ht="25.5">
-      <c r="A3" s="15">
+      <c r="A3" s="19">
         <v>45301</v>
       </c>
-      <c r="B3" s="5" t="s">
-        <v>187</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>188</v>
-      </c>
-      <c r="D3" s="5">
+      <c r="B3" s="9" t="s">
+        <v>189</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>190</v>
+      </c>
+      <c r="D3" s="9">
         <v>0.12</v>
       </c>
-      <c r="E3" s="5">
+      <c r="E3" s="9">
         <v>0.14999999999999999</v>
       </c>
-      <c r="F3" s="5" t="s">
-        <v>428</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>429</v>
-      </c>
-      <c r="H3" s="5" t="s">
+      <c r="F3" s="9" t="s">
         <v>430</v>
       </c>
+      <c r="G3" s="9" t="s">
+        <v>431</v>
+      </c>
+      <c r="H3" s="9" t="s">
+        <v>432</v>
+      </c>
     </row>
     <row r="4" ht="25.5">
-      <c r="A4" s="15">
+      <c r="A4" s="19">
         <v>45265</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>207</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>208</v>
-      </c>
-      <c r="D4" s="5">
+      <c r="B4" s="9" t="s">
+        <v>209</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>210</v>
+      </c>
+      <c r="D4" s="9">
         <v>150</v>
       </c>
-      <c r="E4" s="5">
+      <c r="E4" s="9">
         <v>180</v>
       </c>
-      <c r="F4" s="5" t="s">
-        <v>431</v>
-      </c>
-      <c r="G4" s="5" t="s">
-        <v>432</v>
-      </c>
-      <c r="H4" s="5" t="s">
+      <c r="F4" s="9" t="s">
         <v>433</v>
       </c>
+      <c r="G4" s="9" t="s">
+        <v>434</v>
+      </c>
+      <c r="H4" s="9" t="s">
+        <v>435</v>
+      </c>
     </row>
     <row r="5" ht="38.25">
-      <c r="A5" s="15">
+      <c r="A5" s="19">
         <v>45250</v>
       </c>
-      <c r="B5" s="5" t="s">
-        <v>258</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>259</v>
-      </c>
-      <c r="D5" s="5">
+      <c r="B5" s="9" t="s">
+        <v>260</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>261</v>
+      </c>
+      <c r="D5" s="9">
         <v>0.080000000000000002</v>
       </c>
-      <c r="E5" s="5">
+      <c r="E5" s="9">
         <v>0.10000000000000001</v>
       </c>
-      <c r="F5" s="5" t="s">
-        <v>434</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>414</v>
-      </c>
-      <c r="H5" s="5" t="s">
-        <v>435</v>
+      <c r="F5" s="9" t="s">
+        <v>436</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>416</v>
+      </c>
+      <c r="H5" s="9" t="s">
+        <v>437</v>
       </c>
     </row>
   </sheetData>
@@ -3335,112 +3373,112 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="3" style="5" width="9.140625"/>
-    <col customWidth="1" min="4" max="4" style="5" width="13.421875"/>
-    <col customWidth="1" min="5" max="5" style="5" width="12.8515625"/>
-    <col min="6" max="16384" style="5" width="9.140625"/>
+    <col min="1" max="3" style="9" width="9.140625"/>
+    <col customWidth="1" min="4" max="4" style="9" width="13.421875"/>
+    <col customWidth="1" min="5" max="5" style="9" width="12.8515625"/>
+    <col min="6" max="16384" style="9" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="s">
-        <v>436</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>437</v>
-      </c>
-      <c r="C1" s="5" t="s">
+      <c r="A1" s="9" t="s">
         <v>438</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="B1" s="9" t="s">
         <v>439</v>
       </c>
-      <c r="E1" s="5" t="s">
-        <v>303</v>
+      <c r="C1" s="9" t="s">
+        <v>440</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>441</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>305</v>
       </c>
     </row>
     <row r="2" ht="38.25">
-      <c r="A2" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="C2" s="5">
+      <c r="A2" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="C2" s="9">
         <v>0.84999999999999998</v>
       </c>
-      <c r="D2" s="5" t="s">
-        <v>440</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>441</v>
+      <c r="D2" s="9" t="s">
+        <v>442</v>
+      </c>
+      <c r="E2" s="9" t="s">
+        <v>443</v>
       </c>
     </row>
     <row r="3" ht="38.25">
-      <c r="A3" s="5" t="s">
-        <v>181</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>187</v>
-      </c>
-      <c r="C3" s="5">
+      <c r="A3" s="9" t="s">
+        <v>183</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>189</v>
+      </c>
+      <c r="C3" s="9">
         <v>0.59999999999999998</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="9" t="s">
+        <v>444</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="4" ht="38.25">
+      <c r="A4" s="9" t="s">
+        <v>209</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>232</v>
+      </c>
+      <c r="C4" s="9">
+        <v>0.75</v>
+      </c>
+      <c r="D4" s="9" t="s">
         <v>442</v>
       </c>
-      <c r="E3" s="5" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="4" ht="38.25">
-      <c r="A4" s="5" t="s">
-        <v>207</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>230</v>
-      </c>
-      <c r="C4" s="5">
-        <v>0.75</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>440</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>444</v>
+      <c r="E4" s="9" t="s">
+        <v>446</v>
       </c>
     </row>
     <row r="5" ht="38.25">
-      <c r="A5" s="5" t="s">
-        <v>236</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>242</v>
-      </c>
-      <c r="C5" s="5">
+      <c r="A5" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>244</v>
+      </c>
+      <c r="C5" s="9">
         <v>0.40000000000000002</v>
       </c>
-      <c r="D5" s="5" t="s">
-        <v>445</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>446</v>
+      <c r="D5" s="9" t="s">
+        <v>447</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>448</v>
       </c>
     </row>
     <row r="6" ht="38.25">
-      <c r="A6" s="5" t="s">
-        <v>258</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>270</v>
-      </c>
-      <c r="C6" s="5">
+      <c r="A6" s="9" t="s">
+        <v>260</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>272</v>
+      </c>
+      <c r="C6" s="9">
         <v>-0.69999999999999996</v>
       </c>
-      <c r="D6" s="5" t="s">
-        <v>447</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>448</v>
+      <c r="D6" s="9" t="s">
+        <v>449</v>
+      </c>
+      <c r="E6" s="9" t="s">
+        <v>450</v>
       </c>
     </row>
   </sheetData>
@@ -3455,87 +3493,87 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
   <sheetFormatPr baseColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" style="5" width="10.28125"/>
-    <col customWidth="1" min="2" max="2" style="5" width="12.00390625"/>
-    <col customWidth="1" min="3" max="3" style="5" width="11.140625"/>
-    <col min="4" max="16384" style="5" width="10.28125"/>
+    <col min="1" max="1" style="9" width="10.28125"/>
+    <col customWidth="1" min="2" max="2" style="9" width="12.00390625"/>
+    <col customWidth="1" min="3" max="3" style="9" width="11.140625"/>
+    <col min="4" max="16384" style="9" width="10.28125"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="C1" s="5" t="s">
+      <c r="A1" s="9" t="s">
         <v>124</v>
       </c>
+      <c r="B1" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>126</v>
+      </c>
     </row>
     <row r="2" ht="25.5">
-      <c r="A2" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="C2" s="5" t="s">
+      <c r="A2" s="9" t="s">
         <v>127</v>
       </c>
+      <c r="B2" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>129</v>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="s">
-        <v>128</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="C3" s="6">
+      <c r="A3" s="9" t="s">
+        <v>130</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="C3" s="10">
         <v>1</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>131</v>
-      </c>
-      <c r="C4" s="5">
+      <c r="A4" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="C4" s="9">
         <v>2024</v>
       </c>
     </row>
     <row r="5" ht="38.25">
-      <c r="A5" s="5" t="s">
-        <v>132</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="C5" s="5" t="s">
+      <c r="A5" s="9" t="s">
         <v>134</v>
       </c>
+      <c r="B5" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>136</v>
+      </c>
     </row>
     <row r="6" ht="25.5">
-      <c r="A6" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>136</v>
-      </c>
-      <c r="C6" s="5" t="s">
+      <c r="A6" s="9" t="s">
         <v>137</v>
       </c>
+      <c r="B6" s="9" t="s">
+        <v>138</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>139</v>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>139</v>
-      </c>
-      <c r="C7" s="5" t="s">
+      <c r="A7" s="9" t="s">
         <v>140</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>141</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>142</v>
       </c>
     </row>
   </sheetData>
@@ -3550,200 +3588,200 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
   <sheetFormatPr baseColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="3" style="5" width="10.28125"/>
-    <col customWidth="1" min="4" max="4" style="5" width="12.8515625"/>
-    <col bestFit="1" customWidth="1" min="5" max="6" style="5" width="9"/>
-    <col min="7" max="16384" style="5" width="10.28125"/>
+    <col min="1" max="3" style="9" width="10.28125"/>
+    <col customWidth="1" min="4" max="4" style="9" width="12.8515625"/>
+    <col bestFit="1" customWidth="1" min="5" max="6" style="9" width="9"/>
+    <col min="7" max="16384" style="9" width="10.28125"/>
   </cols>
   <sheetData>
     <row r="1" ht="14.25">
-      <c r="A1" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="C1" s="5" t="s">
+      <c r="A1" s="9" t="s">
         <v>143</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="B1" s="9" t="s">
         <v>144</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="C1" s="9" t="s">
         <v>145</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="D1" s="9" t="s">
         <v>146</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="E1" s="9" t="s">
         <v>147</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="F1" s="9" t="s">
         <v>148</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="G1" s="9" t="s">
         <v>149</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="H1" s="9" t="s">
+        <v>150</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="J1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="K1" s="5" t="s">
-        <v>150</v>
+      <c r="K1" s="9" t="s">
+        <v>152</v>
       </c>
     </row>
     <row r="2" ht="51">
-      <c r="A2" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>152</v>
-      </c>
-      <c r="C2" s="5" t="s">
+      <c r="A2" s="9" t="s">
         <v>153</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="B2" s="9" t="s">
         <v>154</v>
       </c>
-      <c r="E2" s="7">
+      <c r="C2" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="E2" s="11">
         <v>0.0001</v>
       </c>
-      <c r="F2" s="5" t="s">
-        <v>155</v>
-      </c>
-      <c r="G2" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="H2" s="5" t="s">
+      <c r="F2" s="9" t="s">
+        <v>157</v>
+      </c>
+      <c r="G2" s="9" t="s">
+        <v>158</v>
+      </c>
+      <c r="H2" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="I2" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="J2" s="5" t="s">
+      <c r="I2" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="J2" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="K2" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="L2" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="M2" s="9" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="3" ht="51">
+      <c r="A3" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="E3" s="12">
+        <v>0.22</v>
+      </c>
+      <c r="F3" s="12">
+        <v>0.25</v>
+      </c>
+      <c r="G3" s="9" t="s">
         <v>158</v>
       </c>
-      <c r="K2" s="5" t="s">
+      <c r="H3" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="I3" s="9" t="s">
         <v>159</v>
       </c>
-      <c r="L2" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="M2" s="5" t="s">
+      <c r="J3" s="9" t="s">
         <v>160</v>
       </c>
-    </row>
-    <row r="3" ht="51">
-      <c r="A3" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>162</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>163</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>164</v>
-      </c>
-      <c r="E3" s="8">
-        <v>0.22</v>
-      </c>
-      <c r="F3" s="8">
-        <v>0.25</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="H3" s="5" t="s">
+      <c r="K3" s="9" t="s">
+        <v>167</v>
+      </c>
+      <c r="M3" s="13" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="4" ht="38.25">
+      <c r="A4" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>171</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="E4" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="F4" s="10">
+        <v>0.80000000000000004</v>
+      </c>
+      <c r="G4" s="9" t="s">
+        <v>158</v>
+      </c>
+      <c r="H4" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="I3" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="J3" s="5" t="s">
+      <c r="I4" s="9" t="s">
+        <v>173</v>
+      </c>
+      <c r="J4" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="K4" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="L4" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="M4" s="9" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="5" ht="25.5">
+      <c r="A5" s="9" t="s">
+        <v>177</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>179</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="E5" s="14">
+        <v>1.0000000000000001e-15</v>
+      </c>
+      <c r="F5" s="14">
+        <v>1e-10</v>
+      </c>
+      <c r="G5" s="9" t="s">
         <v>158</v>
       </c>
-      <c r="K3" s="5" t="s">
-        <v>165</v>
-      </c>
-      <c r="M3" s="9" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="4" ht="38.25">
-      <c r="A4" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>168</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>169</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>170</v>
-      </c>
-      <c r="E4" s="6">
-        <v>0.5</v>
-      </c>
-      <c r="F4" s="6">
-        <v>0.80000000000000004</v>
-      </c>
-      <c r="G4" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="H4" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="I4" s="5" t="s">
-        <v>171</v>
-      </c>
-      <c r="J4" s="5" t="s">
-        <v>158</v>
-      </c>
-      <c r="K4" s="5" t="s">
-        <v>172</v>
-      </c>
-      <c r="L4" s="5" t="s">
-        <v>173</v>
-      </c>
-      <c r="M4" s="5" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="5" ht="25.5">
-      <c r="A5" s="5" t="s">
-        <v>175</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>176</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>177</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>178</v>
-      </c>
-      <c r="E5" s="10">
-        <v>1.0000000000000001e-15</v>
-      </c>
-      <c r="F5" s="10">
-        <v>1e-10</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="H5" s="5" t="s">
+      <c r="H5" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="I5" s="5" t="s">
-        <v>179</v>
-      </c>
-      <c r="J5" s="5" t="s">
-        <v>158</v>
-      </c>
-      <c r="K5" s="5" t="s">
-        <v>180</v>
+      <c r="I5" s="9" t="s">
+        <v>181</v>
+      </c>
+      <c r="J5" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="K5" s="9" t="s">
+        <v>182</v>
       </c>
     </row>
   </sheetData>
@@ -3758,207 +3796,207 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
   <sheetFormatPr baseColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="3" style="5" width="10.28125"/>
-    <col customWidth="1" min="4" max="4" style="5" width="14.57421875"/>
-    <col min="5" max="16384" style="5" width="10.28125"/>
+    <col min="1" max="3" style="9" width="10.28125"/>
+    <col customWidth="1" min="4" max="4" style="9" width="14.57421875"/>
+    <col min="5" max="16384" style="9" width="10.28125"/>
   </cols>
   <sheetData>
     <row r="1" ht="14.25">
-      <c r="A1" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="C1" s="5" t="s">
+      <c r="A1" s="9" t="s">
         <v>143</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="B1" s="9" t="s">
         <v>144</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="C1" s="9" t="s">
         <v>145</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="D1" s="9" t="s">
         <v>146</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="E1" s="9" t="s">
         <v>147</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="F1" s="9" t="s">
         <v>148</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="G1" s="9" t="s">
         <v>149</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="H1" s="9" t="s">
+        <v>150</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="J1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="K1" s="5" t="s">
-        <v>150</v>
-      </c>
-      <c r="L1" s="5"/>
+      <c r="K1" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="L1" s="9"/>
     </row>
     <row r="2" ht="51">
-      <c r="A2" s="5" t="s">
-        <v>181</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>182</v>
-      </c>
-      <c r="C2" s="5" t="s">
+      <c r="A2" s="9" t="s">
         <v>183</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="B2" s="9" t="s">
         <v>184</v>
       </c>
-      <c r="E2" s="11">
+      <c r="C2" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>186</v>
+      </c>
+      <c r="E2" s="15">
         <v>0.012</v>
       </c>
-      <c r="F2" s="11">
+      <c r="F2" s="15">
         <v>0.014999999999999999</v>
       </c>
-      <c r="G2" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="H2" s="5" t="s">
+      <c r="G2" s="9" t="s">
+        <v>158</v>
+      </c>
+      <c r="H2" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="I2" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="J2" s="5" t="s">
-        <v>185</v>
-      </c>
-      <c r="K2" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="L2" s="5" t="s">
+      <c r="I2" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="J2" s="9" t="s">
+        <v>187</v>
+      </c>
+      <c r="K2" s="9" t="s">
+        <v>188</v>
+      </c>
+      <c r="L2" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="M2" s="5" t="s">
-        <v>160</v>
+      <c r="M2" s="9" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="3" ht="51">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="9" t="s">
+        <v>189</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>190</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>191</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>192</v>
+      </c>
+      <c r="E3" s="12">
+        <v>0.14999999999999999</v>
+      </c>
+      <c r="F3" s="12">
+        <v>0.29999999999999999</v>
+      </c>
+      <c r="G3" s="9" t="s">
+        <v>158</v>
+      </c>
+      <c r="H3" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="I3" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="J3" s="9" t="s">
         <v>187</v>
       </c>
-      <c r="B3" s="5" t="s">
-        <v>188</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>189</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>190</v>
-      </c>
-      <c r="E3" s="8">
-        <v>0.14999999999999999</v>
-      </c>
-      <c r="F3" s="8">
+      <c r="K3" s="9" t="s">
+        <v>193</v>
+      </c>
+      <c r="L3" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="M3" s="9" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="4" ht="51">
+      <c r="A4" s="9" t="s">
+        <v>195</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>196</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>197</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>198</v>
+      </c>
+      <c r="E4" s="10">
         <v>0.29999999999999999</v>
       </c>
-      <c r="G3" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="H3" s="5" t="s">
+      <c r="F4" s="10">
+        <v>0.90000000000000002</v>
+      </c>
+      <c r="G4" s="9" t="s">
+        <v>158</v>
+      </c>
+      <c r="H4" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="I4" s="9" t="s">
+        <v>199</v>
+      </c>
+      <c r="J4" s="9" t="s">
+        <v>187</v>
+      </c>
+      <c r="K4" s="9" t="s">
+        <v>200</v>
+      </c>
+      <c r="L4" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="M4" s="9" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="5" s="16" customFormat="1" ht="38.25">
+      <c r="A5" s="16" t="s">
+        <v>202</v>
+      </c>
+      <c r="B5" s="16" t="s">
+        <v>203</v>
+      </c>
+      <c r="C5" s="16" t="s">
+        <v>204</v>
+      </c>
+      <c r="D5" s="16" t="s">
+        <v>205</v>
+      </c>
+      <c r="E5" s="16">
+        <v>10</v>
+      </c>
+      <c r="F5" s="16">
+        <v>5</v>
+      </c>
+      <c r="G5" s="16" t="s">
+        <v>206</v>
+      </c>
+      <c r="H5" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="I3" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="J3" s="5" t="s">
-        <v>185</v>
-      </c>
-      <c r="K3" s="5" t="s">
-        <v>191</v>
-      </c>
-      <c r="L3" s="5" t="s">
+      <c r="I5" s="16" t="s">
         <v>173</v>
       </c>
-      <c r="M3" s="5" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="4" ht="51">
-      <c r="A4" s="5" t="s">
-        <v>193</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>194</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>196</v>
-      </c>
-      <c r="E4" s="6">
-        <v>0.29999999999999999</v>
-      </c>
-      <c r="F4" s="6">
-        <v>0.90000000000000002</v>
-      </c>
-      <c r="G4" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="H4" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="I4" s="5" t="s">
-        <v>197</v>
-      </c>
-      <c r="J4" s="5" t="s">
-        <v>185</v>
-      </c>
-      <c r="K4" s="5" t="s">
-        <v>198</v>
-      </c>
-      <c r="L4" s="5" t="s">
-        <v>173</v>
-      </c>
-      <c r="M4" s="5" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="5" s="12" customFormat="1" ht="38.25">
-      <c r="A5" s="12" t="s">
-        <v>200</v>
-      </c>
-      <c r="B5" s="12" t="s">
-        <v>201</v>
-      </c>
-      <c r="C5" s="12" t="s">
-        <v>202</v>
-      </c>
-      <c r="D5" s="12" t="s">
-        <v>203</v>
-      </c>
-      <c r="E5" s="12">
-        <v>10</v>
-      </c>
-      <c r="F5" s="12">
-        <v>5</v>
-      </c>
-      <c r="G5" s="12" t="s">
-        <v>204</v>
-      </c>
-      <c r="H5" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="I5" s="12" t="s">
-        <v>171</v>
-      </c>
-      <c r="J5" s="12" t="s">
-        <v>185</v>
-      </c>
-      <c r="K5" s="12" t="s">
-        <v>205</v>
-      </c>
-      <c r="L5" s="12"/>
-      <c r="M5" s="9" t="s">
-        <v>206</v>
+      <c r="J5" s="16" t="s">
+        <v>187</v>
+      </c>
+      <c r="K5" s="16" t="s">
+        <v>207</v>
+      </c>
+      <c r="L5" s="16"/>
+      <c r="M5" s="13" t="s">
+        <v>208</v>
       </c>
     </row>
   </sheetData>
@@ -3973,201 +4011,201 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
   <sheetFormatPr baseColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="3" style="5" width="10.28125"/>
-    <col customWidth="1" min="4" max="4" style="5" width="14.421875"/>
-    <col min="5" max="6" style="5" width="10.28125"/>
-    <col customWidth="1" min="7" max="7" style="5" width="14.00390625"/>
-    <col min="8" max="16384" style="5" width="10.28125"/>
+    <col min="1" max="3" style="9" width="10.28125"/>
+    <col customWidth="1" min="4" max="4" style="9" width="14.421875"/>
+    <col min="5" max="6" style="9" width="10.28125"/>
+    <col customWidth="1" min="7" max="7" style="9" width="14.00390625"/>
+    <col min="8" max="16384" style="9" width="10.28125"/>
   </cols>
   <sheetData>
     <row r="1" ht="14.25">
-      <c r="A1" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="C1" s="5" t="s">
+      <c r="A1" s="9" t="s">
         <v>143</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="B1" s="9" t="s">
         <v>144</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="C1" s="9" t="s">
         <v>145</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="D1" s="9" t="s">
         <v>146</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="E1" s="9" t="s">
         <v>147</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="F1" s="9" t="s">
         <v>148</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="G1" s="9" t="s">
         <v>149</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="H1" s="9" t="s">
+        <v>150</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="J1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="K1" s="5" t="s">
-        <v>150</v>
+      <c r="K1" s="9" t="s">
+        <v>152</v>
       </c>
     </row>
     <row r="2" ht="63.75">
-      <c r="A2" s="5" t="s">
-        <v>207</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>208</v>
-      </c>
-      <c r="C2" s="5" t="s">
+      <c r="A2" s="9" t="s">
         <v>209</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="B2" s="9" t="s">
         <v>210</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="C2" s="9" t="s">
         <v>211</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="D2" s="9" t="s">
         <v>212</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="E2" s="9" t="s">
         <v>213</v>
       </c>
-      <c r="H2" s="5">
+      <c r="F2" s="9" t="s">
+        <v>214</v>
+      </c>
+      <c r="G2" s="9" t="s">
+        <v>215</v>
+      </c>
+      <c r="H2" s="9">
         <v>180</v>
       </c>
-      <c r="I2" s="5">
+      <c r="I2" s="9">
         <v>3650</v>
       </c>
-      <c r="J2" s="5" t="s">
-        <v>214</v>
-      </c>
-      <c r="K2" s="5" t="s">
+      <c r="J2" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="K2" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="L2" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="M2" s="5" t="s">
-        <v>215</v>
-      </c>
-      <c r="N2" s="5" t="s">
-        <v>216</v>
-      </c>
-      <c r="O2" s="5" t="s">
+      <c r="L2" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="M2" s="9" t="s">
         <v>217</v>
       </c>
-      <c r="P2" s="5" t="s">
+      <c r="N2" s="9" t="s">
         <v>218</v>
       </c>
+      <c r="O2" s="9" t="s">
+        <v>219</v>
+      </c>
+      <c r="P2" s="9" t="s">
+        <v>220</v>
+      </c>
     </row>
     <row r="3" ht="51">
-      <c r="A3" s="5" t="s">
-        <v>219</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>220</v>
-      </c>
-      <c r="C3" s="5" t="s">
+      <c r="A3" s="9" t="s">
         <v>221</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="B3" s="9" t="s">
         <v>222</v>
       </c>
-      <c r="E3" s="8">
+      <c r="C3" s="9" t="s">
+        <v>223</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>224</v>
+      </c>
+      <c r="E3" s="12">
         <v>0.84999999999999998</v>
       </c>
-      <c r="F3" s="8">
+      <c r="F3" s="12">
         <v>0.98999999999999999</v>
       </c>
-      <c r="G3" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="H3" s="5" t="s">
+      <c r="G3" s="9" t="s">
+        <v>158</v>
+      </c>
+      <c r="H3" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="I3" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="J3" s="5" t="s">
-        <v>215</v>
-      </c>
-      <c r="K3" s="5" t="s">
-        <v>223</v>
+      <c r="I3" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="J3" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="K3" s="9" t="s">
+        <v>225</v>
       </c>
     </row>
     <row r="4" ht="38.25">
-      <c r="A4" s="5" t="s">
-        <v>224</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>225</v>
-      </c>
-      <c r="C4" s="5" t="s">
+      <c r="A4" s="9" t="s">
         <v>226</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="B4" s="9" t="s">
         <v>227</v>
       </c>
-      <c r="E4" s="6">
+      <c r="C4" s="9" t="s">
+        <v>228</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>229</v>
+      </c>
+      <c r="E4" s="10">
         <v>1.5</v>
       </c>
-      <c r="F4" s="6">
+      <c r="F4" s="10">
         <v>2.5</v>
       </c>
-      <c r="G4" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="H4" s="5" t="s">
+      <c r="G4" s="9" t="s">
+        <v>158</v>
+      </c>
+      <c r="H4" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="I4" s="5" t="s">
-        <v>228</v>
-      </c>
-      <c r="J4" s="5" t="s">
-        <v>215</v>
-      </c>
-      <c r="K4" s="5" t="s">
-        <v>229</v>
+      <c r="I4" s="9" t="s">
+        <v>230</v>
+      </c>
+      <c r="J4" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="K4" s="9" t="s">
+        <v>231</v>
       </c>
     </row>
     <row r="5" ht="51">
-      <c r="A5" s="5" t="s">
-        <v>230</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>231</v>
-      </c>
-      <c r="C5" s="5" t="s">
+      <c r="A5" s="9" t="s">
         <v>232</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="B5" s="9" t="s">
         <v>233</v>
       </c>
-      <c r="E5" s="6">
+      <c r="C5" s="9" t="s">
+        <v>234</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>235</v>
+      </c>
+      <c r="E5" s="10">
         <v>0.69999999999999996</v>
       </c>
-      <c r="F5" s="8">
+      <c r="F5" s="12">
         <v>1.05</v>
       </c>
-      <c r="G5" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="H5" s="5" t="s">
+      <c r="G5" s="9" t="s">
+        <v>158</v>
+      </c>
+      <c r="H5" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="I5" s="5" t="s">
-        <v>234</v>
-      </c>
-      <c r="J5" s="5" t="s">
-        <v>215</v>
-      </c>
-      <c r="K5" s="5" t="s">
-        <v>235</v>
+      <c r="I5" s="9" t="s">
+        <v>236</v>
+      </c>
+      <c r="J5" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="K5" s="9" t="s">
+        <v>237</v>
       </c>
     </row>
   </sheetData>
@@ -4182,184 +4220,184 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
   <sheetFormatPr baseColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="3" style="5" width="10.28125"/>
-    <col customWidth="1" min="4" max="4" style="5" width="18.28125"/>
-    <col min="5" max="16384" style="5" width="10.28125"/>
+    <col min="1" max="3" style="9" width="10.28125"/>
+    <col customWidth="1" min="4" max="4" style="9" width="18.28125"/>
+    <col min="5" max="16384" style="9" width="10.28125"/>
   </cols>
   <sheetData>
     <row r="1" ht="14.25">
-      <c r="A1" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="C1" s="5" t="s">
+      <c r="A1" s="9" t="s">
         <v>143</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="B1" s="9" t="s">
         <v>144</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="C1" s="9" t="s">
         <v>145</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="D1" s="9" t="s">
         <v>146</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="E1" s="9" t="s">
         <v>147</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="F1" s="9" t="s">
         <v>148</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="G1" s="9" t="s">
         <v>149</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="H1" s="9" t="s">
+        <v>150</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="J1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="K1" s="5" t="s">
-        <v>150</v>
+      <c r="K1" s="9" t="s">
+        <v>152</v>
       </c>
     </row>
     <row r="2" ht="38.25">
-      <c r="A2" s="5" t="s">
-        <v>236</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>237</v>
-      </c>
-      <c r="C2" s="5" t="s">
+      <c r="A2" s="9" t="s">
         <v>238</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="B2" s="9" t="s">
         <v>239</v>
       </c>
-      <c r="E2" s="8">
+      <c r="C2" s="9" t="s">
+        <v>240</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>241</v>
+      </c>
+      <c r="E2" s="12">
         <v>0.25</v>
       </c>
-      <c r="F2" s="8">
+      <c r="F2" s="12">
         <v>0.90000000000000002</v>
       </c>
-      <c r="G2" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="H2" s="5" t="s">
+      <c r="G2" s="9" t="s">
+        <v>158</v>
+      </c>
+      <c r="H2" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="I2" s="5" t="s">
-        <v>197</v>
-      </c>
-      <c r="J2" s="5" t="s">
-        <v>240</v>
-      </c>
-      <c r="K2" s="5" t="s">
-        <v>241</v>
+      <c r="I2" s="9" t="s">
+        <v>199</v>
+      </c>
+      <c r="J2" s="9" t="s">
+        <v>242</v>
+      </c>
+      <c r="K2" s="9" t="s">
+        <v>243</v>
       </c>
     </row>
     <row r="3" ht="63.75">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="9" t="s">
+        <v>244</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>245</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>246</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>247</v>
+      </c>
+      <c r="E3" s="10">
+        <v>1.5</v>
+      </c>
+      <c r="F3" s="17">
+        <v>10</v>
+      </c>
+      <c r="G3" s="9" t="s">
+        <v>158</v>
+      </c>
+      <c r="H3" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="I3" s="9" t="s">
+        <v>173</v>
+      </c>
+      <c r="J3" s="9" t="s">
         <v>242</v>
       </c>
-      <c r="B3" s="5" t="s">
-        <v>243</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>244</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>245</v>
-      </c>
-      <c r="E3" s="6">
-        <v>1.5</v>
-      </c>
-      <c r="F3" s="13">
-        <v>10</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="H3" s="5" t="s">
+      <c r="K3" s="9" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="4" ht="25.5">
+      <c r="A4" s="9" t="s">
+        <v>249</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>250</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>251</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>252</v>
+      </c>
+      <c r="E4" s="12">
+        <v>0.01</v>
+      </c>
+      <c r="F4" s="12">
+        <v>0.10000000000000001</v>
+      </c>
+      <c r="G4" s="9" t="s">
+        <v>253</v>
+      </c>
+      <c r="H4" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="I3" s="5" t="s">
-        <v>171</v>
-      </c>
-      <c r="J3" s="5" t="s">
-        <v>240</v>
-      </c>
-      <c r="K3" s="5" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="4" ht="25.5">
-      <c r="A4" s="5" t="s">
-        <v>247</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>248</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>249</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>250</v>
-      </c>
-      <c r="E4" s="8">
-        <v>0.01</v>
-      </c>
-      <c r="F4" s="8">
-        <v>0.10000000000000001</v>
-      </c>
-      <c r="G4" s="5" t="s">
-        <v>251</v>
-      </c>
-      <c r="H4" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="I4" s="5" t="s">
-        <v>179</v>
-      </c>
-      <c r="J4" s="5" t="s">
-        <v>240</v>
-      </c>
-      <c r="K4" s="5" t="s">
-        <v>252</v>
+      <c r="I4" s="9" t="s">
+        <v>181</v>
+      </c>
+      <c r="J4" s="9" t="s">
+        <v>242</v>
+      </c>
+      <c r="K4" s="9" t="s">
+        <v>254</v>
       </c>
     </row>
     <row r="5" ht="38.25">
-      <c r="A5" s="5" t="s">
-        <v>253</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>254</v>
-      </c>
-      <c r="C5" s="5" t="s">
+      <c r="A5" s="9" t="s">
         <v>255</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="B5" s="9" t="s">
         <v>256</v>
       </c>
-      <c r="E5" s="8">
+      <c r="C5" s="9" t="s">
+        <v>257</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="E5" s="12">
         <v>0.29999999999999999</v>
       </c>
-      <c r="F5" s="8">
+      <c r="F5" s="12">
         <v>0.80000000000000004</v>
       </c>
-      <c r="G5" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="H5" s="5" t="s">
+      <c r="G5" s="9" t="s">
+        <v>158</v>
+      </c>
+      <c r="H5" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="I5" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="J5" s="5" t="s">
-        <v>240</v>
-      </c>
-      <c r="K5" s="5" t="s">
-        <v>257</v>
+      <c r="I5" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="J5" s="9" t="s">
+        <v>242</v>
+      </c>
+      <c r="K5" s="9" t="s">
+        <v>259</v>
       </c>
     </row>
   </sheetData>
@@ -4374,186 +4412,186 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" style="5" width="9.140625"/>
-    <col customWidth="1" min="2" max="2" style="5" width="11.57421875"/>
-    <col customWidth="1" min="3" max="3" style="5" width="12.421875"/>
-    <col customWidth="1" min="4" max="4" style="5" width="14.421875"/>
-    <col min="5" max="16384" style="5" width="9.140625"/>
+    <col min="1" max="1" style="9" width="9.140625"/>
+    <col customWidth="1" min="2" max="2" style="9" width="11.57421875"/>
+    <col customWidth="1" min="3" max="3" style="9" width="12.421875"/>
+    <col customWidth="1" min="4" max="4" style="9" width="14.421875"/>
+    <col min="5" max="16384" style="9" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="C1" s="5" t="s">
+      <c r="A1" s="9" t="s">
         <v>143</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="B1" s="9" t="s">
         <v>144</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="C1" s="9" t="s">
         <v>145</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="D1" s="9" t="s">
         <v>146</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="E1" s="9" t="s">
         <v>147</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="F1" s="9" t="s">
         <v>148</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="G1" s="9" t="s">
         <v>149</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="H1" s="9" t="s">
+        <v>150</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="J1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="K1" s="5" t="s">
-        <v>150</v>
+      <c r="K1" s="9" t="s">
+        <v>152</v>
       </c>
     </row>
     <row r="2" ht="38.25">
-      <c r="A2" s="5" t="s">
-        <v>258</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>259</v>
-      </c>
-      <c r="C2" s="5" t="s">
+      <c r="A2" s="9" t="s">
         <v>260</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="B2" s="9" t="s">
         <v>261</v>
       </c>
-      <c r="E2" s="5">
+      <c r="C2" s="9" t="s">
+        <v>262</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>263</v>
+      </c>
+      <c r="E2" s="9">
         <v>0.10000000000000001</v>
       </c>
-      <c r="F2" s="5">
+      <c r="F2" s="9">
         <v>0.94999999999999996</v>
       </c>
-      <c r="G2" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="H2" s="5" t="s">
+      <c r="G2" s="9" t="s">
+        <v>158</v>
+      </c>
+      <c r="H2" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="I2" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="J2" s="5" t="s">
-        <v>262</v>
-      </c>
-      <c r="K2" s="5" t="s">
-        <v>263</v>
+      <c r="I2" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="J2" s="9" t="s">
+        <v>264</v>
+      </c>
+      <c r="K2" s="9" t="s">
+        <v>265</v>
       </c>
     </row>
     <row r="3" ht="51">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="9" t="s">
+        <v>266</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>267</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>268</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>269</v>
+      </c>
+      <c r="E3" s="9">
+        <v>100</v>
+      </c>
+      <c r="F3" s="9">
+        <v>1</v>
+      </c>
+      <c r="G3" s="9" t="s">
+        <v>270</v>
+      </c>
+      <c r="H3" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="I3" s="9" t="s">
+        <v>199</v>
+      </c>
+      <c r="J3" s="9" t="s">
         <v>264</v>
       </c>
-      <c r="B3" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>266</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>267</v>
-      </c>
-      <c r="E3" s="5">
-        <v>100</v>
-      </c>
-      <c r="F3" s="5">
-        <v>1</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>268</v>
-      </c>
-      <c r="H3" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="I3" s="5" t="s">
-        <v>197</v>
-      </c>
-      <c r="J3" s="5" t="s">
-        <v>262</v>
-      </c>
-      <c r="K3" s="5" t="s">
-        <v>269</v>
+      <c r="K3" s="9" t="s">
+        <v>271</v>
       </c>
     </row>
     <row r="4" ht="51">
-      <c r="A4" s="5" t="s">
-        <v>270</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>271</v>
-      </c>
-      <c r="C4" s="5" t="s">
+      <c r="A4" s="9" t="s">
         <v>272</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="B4" s="9" t="s">
         <v>273</v>
       </c>
-      <c r="E4" s="5">
+      <c r="C4" s="9" t="s">
+        <v>274</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>275</v>
+      </c>
+      <c r="E4" s="9">
         <v>0.10000000000000001</v>
       </c>
-      <c r="F4" s="5">
+      <c r="F4" s="9">
         <v>0.001</v>
       </c>
-      <c r="G4" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="H4" s="5" t="s">
+      <c r="G4" s="9" t="s">
+        <v>158</v>
+      </c>
+      <c r="H4" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="I4" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="J4" s="5" t="s">
-        <v>262</v>
-      </c>
-      <c r="K4" s="5" t="s">
-        <v>274</v>
+      <c r="I4" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="J4" s="9" t="s">
+        <v>264</v>
+      </c>
+      <c r="K4" s="9" t="s">
+        <v>276</v>
       </c>
     </row>
     <row r="5" ht="51">
-      <c r="A5" s="5" t="s">
-        <v>275</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>276</v>
-      </c>
-      <c r="C5" s="5" t="s">
+      <c r="A5" s="9" t="s">
         <v>277</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="B5" s="9" t="s">
         <v>278</v>
       </c>
-      <c r="E5" s="5">
+      <c r="C5" s="9" t="s">
+        <v>279</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>280</v>
+      </c>
+      <c r="E5" s="9">
         <v>0.69999999999999996</v>
       </c>
-      <c r="F5" s="5">
+      <c r="F5" s="9">
         <v>0.98999999999999999</v>
       </c>
-      <c r="G5" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="H5" s="5" t="s">
+      <c r="G5" s="9" t="s">
+        <v>158</v>
+      </c>
+      <c r="H5" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="I5" s="5" t="s">
-        <v>279</v>
-      </c>
-      <c r="J5" s="5" t="s">
-        <v>262</v>
-      </c>
-      <c r="K5" s="5" t="s">
-        <v>280</v>
+      <c r="I5" s="9" t="s">
+        <v>281</v>
+      </c>
+      <c r="J5" s="9" t="s">
+        <v>264</v>
+      </c>
+      <c r="K5" s="9" t="s">
+        <v>282</v>
       </c>
     </row>
   </sheetData>
@@ -4568,192 +4606,192 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="3" style="5" width="9.140625"/>
-    <col customWidth="1" min="4" max="4" style="5" width="14.28125"/>
-    <col min="5" max="5" style="5" width="9.140625"/>
-    <col customWidth="1" min="6" max="6" style="5" width="13.7109375"/>
-    <col min="7" max="16384" style="5" width="9.140625"/>
+    <col min="1" max="3" style="9" width="9.140625"/>
+    <col customWidth="1" min="4" max="4" style="9" width="14.28125"/>
+    <col min="5" max="5" style="9" width="9.140625"/>
+    <col customWidth="1" min="6" max="6" style="9" width="13.7109375"/>
+    <col min="7" max="16384" style="9" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="C1" s="5" t="s">
+      <c r="A1" s="9" t="s">
         <v>143</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="B1" s="9" t="s">
         <v>144</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="C1" s="9" t="s">
         <v>145</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="D1" s="9" t="s">
         <v>146</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="E1" s="9" t="s">
         <v>147</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="F1" s="9" t="s">
         <v>148</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="G1" s="9" t="s">
         <v>149</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="H1" s="9" t="s">
+        <v>150</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="J1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="K1" s="5" t="s">
-        <v>150</v>
+      <c r="K1" s="9" t="s">
+        <v>152</v>
       </c>
     </row>
     <row r="2" ht="38.25">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="5" t="s">
-        <v>281</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>282</v>
-      </c>
-      <c r="D2" s="5" t="s">
+      <c r="B2" s="9" t="s">
         <v>283</v>
       </c>
-      <c r="E2" s="5">
+      <c r="C2" s="9" t="s">
+        <v>284</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>285</v>
+      </c>
+      <c r="E2" s="9">
         <v>10000</v>
       </c>
-      <c r="F2" s="5">
+      <c r="F2" s="9">
         <v>100</v>
       </c>
-      <c r="G2" s="5" t="s">
-        <v>284</v>
-      </c>
-      <c r="H2" s="5" t="s">
+      <c r="G2" s="9" t="s">
+        <v>286</v>
+      </c>
+      <c r="H2" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="I2" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="J2" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="K2" s="5" t="s">
-        <v>285</v>
+      <c r="I2" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="J2" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="K2" s="9" t="s">
+        <v>287</v>
       </c>
     </row>
     <row r="3" ht="51">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="B3" s="5" t="s">
-        <v>286</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>287</v>
-      </c>
-      <c r="D3" s="5" t="s">
+      <c r="B3" s="9" t="s">
         <v>288</v>
       </c>
-      <c r="E3" s="5">
+      <c r="C3" s="9" t="s">
+        <v>289</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>290</v>
+      </c>
+      <c r="E3" s="9">
         <v>100</v>
       </c>
-      <c r="F3" s="5">
+      <c r="F3" s="9">
         <v>10</v>
       </c>
-      <c r="G3" s="5" t="s">
-        <v>289</v>
-      </c>
-      <c r="H3" s="5" t="s">
+      <c r="G3" s="9" t="s">
+        <v>291</v>
+      </c>
+      <c r="H3" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="I3" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="J3" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="K3" s="5" t="s">
-        <v>290</v>
+      <c r="I3" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="J3" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="K3" s="9" t="s">
+        <v>292</v>
       </c>
     </row>
     <row r="4" ht="51">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>291</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>292</v>
-      </c>
-      <c r="D4" s="5" t="s">
+      <c r="B4" s="9" t="s">
         <v>293</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="C4" s="9" t="s">
         <v>294</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="D4" s="9" t="s">
         <v>295</v>
       </c>
-      <c r="G4" s="5">
+      <c r="E4" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>297</v>
+      </c>
+      <c r="G4" s="9">
         <v>10</v>
       </c>
-      <c r="H4" s="5">
+      <c r="H4" s="9">
         <v>2</v>
       </c>
-      <c r="I4" s="5" t="s">
-        <v>296</v>
-      </c>
-      <c r="J4" s="5" t="s">
+      <c r="I4" s="9" t="s">
+        <v>298</v>
+      </c>
+      <c r="J4" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="K4" s="5" t="s">
-        <v>171</v>
-      </c>
-      <c r="L4" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="M4" s="5" t="s">
-        <v>297</v>
+      <c r="K4" s="9" t="s">
+        <v>173</v>
+      </c>
+      <c r="L4" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="M4" s="9" t="s">
+        <v>299</v>
       </c>
     </row>
     <row r="5" ht="51">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="B5" s="5" t="s">
-        <v>298</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>299</v>
-      </c>
-      <c r="D5" s="5" t="s">
+      <c r="B5" s="9" t="s">
         <v>300</v>
       </c>
-      <c r="E5" s="5">
+      <c r="C5" s="9" t="s">
+        <v>301</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>302</v>
+      </c>
+      <c r="E5" s="9">
         <v>0.80000000000000004</v>
       </c>
-      <c r="F5" s="5">
+      <c r="F5" s="9">
         <v>0.59999999999999998</v>
       </c>
-      <c r="G5" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="H5" s="5" t="s">
+      <c r="G5" s="9" t="s">
+        <v>158</v>
+      </c>
+      <c r="H5" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="I5" s="5" t="s">
-        <v>179</v>
-      </c>
-      <c r="J5" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="K5" s="5" t="s">
-        <v>301</v>
+      <c r="I5" s="9" t="s">
+        <v>181</v>
+      </c>
+      <c r="J5" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="K5" s="9" t="s">
+        <v>303</v>
       </c>
     </row>
   </sheetData>
@@ -4768,264 +4806,264 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" min="1" max="1" style="5" width="12.57421875"/>
-    <col customWidth="1" min="2" max="2" style="5" width="13.8515625"/>
-    <col min="3" max="4" style="5" width="9.140625"/>
-    <col customWidth="1" min="5" max="5" style="5" width="12.8515625"/>
-    <col customWidth="1" min="6" max="6" style="5" width="12.421875"/>
-    <col min="7" max="16384" style="5" width="9.140625"/>
+    <col customWidth="1" min="1" max="1" style="9" width="12.57421875"/>
+    <col customWidth="1" min="2" max="2" style="9" width="13.8515625"/>
+    <col min="3" max="4" style="9" width="9.140625"/>
+    <col customWidth="1" min="5" max="5" style="9" width="12.8515625"/>
+    <col customWidth="1" min="6" max="6" style="9" width="12.421875"/>
+    <col min="7" max="16384" style="9" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1" ht="28.5">
-      <c r="A1" s="5" t="s">
-        <v>302</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>303</v>
-      </c>
-      <c r="C1" s="5" t="s">
+      <c r="A1" s="9" t="s">
         <v>304</v>
       </c>
-      <c r="D1" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="E1" s="5" t="s">
+      <c r="B1" s="9" t="s">
         <v>305</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="C1" s="9" t="s">
+        <v>306</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>307</v>
+      </c>
+      <c r="F1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="5" t="s">
-        <v>148</v>
+      <c r="G1" s="9" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="2" ht="25.5">
-      <c r="A2" s="5" t="s">
-        <v>306</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>307</v>
-      </c>
-      <c r="C2" s="10">
+      <c r="A2" s="9" t="s">
+        <v>308</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>309</v>
+      </c>
+      <c r="C2" s="14">
         <v>200000000000</v>
       </c>
-      <c r="D2" s="5" t="s">
-        <v>308</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>309</v>
-      </c>
-      <c r="F2" s="5" t="s">
+      <c r="D2" s="9" t="s">
+        <v>310</v>
+      </c>
+      <c r="E2" s="9" t="s">
+        <v>311</v>
+      </c>
+      <c r="F2" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="G2" s="9" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" ht="42.75">
+      <c r="A3" s="9" t="s">
+        <v>312</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>313</v>
+      </c>
+      <c r="C3" s="9">
+        <v>5500</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>310</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>314</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="G3" s="9" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" ht="28.5">
+      <c r="A4" s="9" t="s">
+        <v>315</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>316</v>
+      </c>
+      <c r="C4" s="9">
+        <v>24</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>310</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>317</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="G4" s="9" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="5" ht="25.5">
+      <c r="A5" s="9" t="s">
+        <v>318</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>319</v>
+      </c>
+      <c r="C5" s="14">
+        <v>4540000000</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>298</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>320</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>321</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" ht="28.5">
+      <c r="A6" s="9" t="s">
+        <v>322</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>323</v>
+      </c>
+      <c r="C6" s="14">
+        <v>500000000</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>298</v>
+      </c>
+      <c r="E6" s="9" t="s">
+        <v>324</v>
+      </c>
+      <c r="F6" s="9" t="s">
+        <v>321</v>
+      </c>
+      <c r="G6" s="9" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="7" ht="28.5">
+      <c r="A7" s="9" t="s">
+        <v>325</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>326</v>
+      </c>
+      <c r="C7" s="9">
+        <v>230</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>327</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>328</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>329</v>
+      </c>
+      <c r="G7" s="9" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" ht="28.5">
+      <c r="A8" s="9" t="s">
+        <v>330</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>331</v>
+      </c>
+      <c r="C8" s="9">
+        <v>0.01</v>
+      </c>
+      <c r="D8" s="9" t="s">
         <v>158</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="E8" s="9" t="s">
+        <v>332</v>
+      </c>
+      <c r="F8" s="9" t="s">
+        <v>329</v>
+      </c>
+      <c r="G8" s="9" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="9" ht="25.5">
+      <c r="A9" s="9" t="s">
+        <v>333</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>334</v>
+      </c>
+      <c r="C9" s="9">
+        <v>1366</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>335</v>
+      </c>
+      <c r="E9" s="9" t="s">
+        <v>336</v>
+      </c>
+      <c r="F9" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="G9" s="9" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="3" ht="42.75">
-      <c r="A3" s="5" t="s">
-        <v>310</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>311</v>
-      </c>
-      <c r="C3" s="5">
-        <v>5500</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>308</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>312</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>158</v>
-      </c>
-      <c r="G3" s="5" t="s">
+    <row r="10" ht="25.5">
+      <c r="A10" s="9" t="s">
+        <v>337</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>338</v>
+      </c>
+      <c r="C10" s="9">
+        <v>587</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>335</v>
+      </c>
+      <c r="E10" s="9" t="s">
+        <v>339</v>
+      </c>
+      <c r="F10" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="G10" s="9" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="4" ht="28.5">
-      <c r="A4" s="5" t="s">
-        <v>313</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>314</v>
-      </c>
-      <c r="C4" s="5">
-        <v>24</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>308</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>315</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>158</v>
-      </c>
-      <c r="G4" s="5" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="5" ht="25.5">
-      <c r="A5" s="5" t="s">
-        <v>316</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>317</v>
-      </c>
-      <c r="C5" s="10">
-        <v>4540000000</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>296</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>318</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>319</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" ht="28.5">
-      <c r="A6" s="5" t="s">
-        <v>320</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>321</v>
-      </c>
-      <c r="C6" s="10">
-        <v>500000000</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>296</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>322</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>319</v>
-      </c>
-      <c r="G6" s="5" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="7" ht="28.5">
-      <c r="A7" s="5" t="s">
-        <v>323</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>324</v>
-      </c>
-      <c r="C7" s="5">
-        <v>230</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>325</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>326</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>327</v>
-      </c>
-      <c r="G7" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" ht="28.5">
-      <c r="A8" s="5" t="s">
-        <v>328</v>
-      </c>
-      <c r="B8" s="5" t="s">
+    <row r="11" ht="25.5">
+      <c r="A11" s="9" t="s">
+        <v>340</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>341</v>
+      </c>
+      <c r="C11" s="9">
+        <v>101.325</v>
+      </c>
+      <c r="D11" s="9" t="s">
+        <v>342</v>
+      </c>
+      <c r="E11" s="9" t="s">
+        <v>336</v>
+      </c>
+      <c r="F11" s="9" t="s">
         <v>329</v>
       </c>
-      <c r="C8" s="5">
-        <v>0.01</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>330</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>327</v>
-      </c>
-      <c r="G8" s="5" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="9" ht="25.5">
-      <c r="A9" s="5" t="s">
-        <v>331</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>332</v>
-      </c>
-      <c r="C9" s="5">
-        <v>1366</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>333</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>334</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="G9" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="10" ht="25.5">
-      <c r="A10" s="5" t="s">
-        <v>335</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>336</v>
-      </c>
-      <c r="C10" s="5">
-        <v>587</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>333</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>337</v>
-      </c>
-      <c r="F10" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="G10" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="11" ht="25.5">
-      <c r="A11" s="5" t="s">
-        <v>338</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>339</v>
-      </c>
-      <c r="C11" s="5">
-        <v>101.325</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>340</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>334</v>
-      </c>
-      <c r="F11" s="5" t="s">
-        <v>327</v>
-      </c>
-      <c r="G11" s="5" t="s">
+      <c r="G11" s="9" t="s">
         <v>12</v>
       </c>
     </row>

--- a/tasklist/生命・生態系関連.xlsx
+++ b/tasklist/生命・生態系関連.xlsx
@@ -7,19 +7,20 @@
   </bookViews>
   <sheets>
     <sheet name="核心課題" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="基本情報" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="生命普遍性確率 " sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="光合成・エネルギー変換" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="閉鎖生態系" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="遺伝子改変・適応" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="探査・検出" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="生態系構築コスト" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="入力パラメータ" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="定数定義" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="集計指標 " sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="優先順位 (" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="更新履歴 " sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="関連性マトリクス" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="antiaging" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="基本情報" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="生命普遍性確率 " sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="光合成・エネルギー変換" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="閉鎖生態系" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="遺伝子改変・適応" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="探査・検出" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="生態系構築コスト" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="入力パラメータ" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="定数定義" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="集計指標 " sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="優先順位 (" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="更新履歴 " sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="関連性マトリクス" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">核心課題!$A$1:$I$29</definedName>
@@ -32,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="451" uniqueCount="451">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="492" uniqueCount="492">
   <si>
     <t>課題ID</t>
   </si>
@@ -121,7 +122,7 @@
     <t>放射線耐性・低重力適応遺伝子の活性化確率</t>
   </si>
   <si>
-    <t>maxim+python</t>
+    <t>maxima+python</t>
   </si>
   <si>
     <t>26.04.23</t>
@@ -205,6 +206,9 @@
     <t>テロメア延長・細胞修復機構の持続確率</t>
   </si>
   <si>
+    <t>26.06.10</t>
+  </si>
+  <si>
     <t>BIO-508</t>
   </si>
   <si>
@@ -406,6 +410,129 @@
     <t xml:space="preserve"> 完全肉体再生確率</t>
   </si>
   <si>
+    <t xml:space="preserve">Task ID</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Category</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Core Task</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Calculation Content</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Necessity of Coupling</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Urgency</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Expected Resolution Year</t>
+  </si>
+  <si>
+    <t>BIO-507-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Aging Suppression</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Telomere Extension Probability</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Probability of maintaining telomere length via telomerase activation</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Essential</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> High</t>
+  </si>
+  <si>
+    <t>BIO-507-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Mitochondrial Function Preservation Rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Probability of maintaining mitochondrial efficiency and reducing ROS production</t>
+  </si>
+  <si>
+    <t>BIO-507-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Epigenetic Clock Reset Probability</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Probability of reversing DNA methylation age pattern</t>
+  </si>
+  <si>
+    <t>BIO-507-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Autophagy Activation Rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Probability of maintaining cellular cleanup mechanism efficiency</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Medium</t>
+  </si>
+  <si>
+    <t>BIO-507-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Proteostasis Maintenance Probability</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Probability of preventing protein misfolding and aggregation</t>
+  </si>
+  <si>
+    <t>BIO-507-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Stem Cell Exhaustion Prevention Rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Probability of maintaining tissue regeneration capacity</t>
+  </si>
+  <si>
+    <t>BIO-507-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Cellular Senescence Clearance Rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Probability of removing senescent cells (senolytics)</t>
+  </si>
+  <si>
+    <t>BIO-507-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> mTOR Signaling Optimization Rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Probability of optimal nutrient sensing and metabolic regulation</t>
+  </si>
+  <si>
+    <t>BIO-507-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> DNA Damage Repair Efficiency</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Probability of maintaining genome integrity and repair mechanisms</t>
+  </si>
+  <si>
+    <t>BIO-507-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Intercellular Communication Restoration Rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Probability of reducing chronic inflammation and improving hormonal signaling</t>
+  </si>
+  <si>
     <t>category</t>
   </si>
   <si>
@@ -557,9 +684,6 @@
   </si>
   <si>
     <t>実験室データから推定</t>
-  </si>
-  <si>
-    <t>maxima+python</t>
   </si>
   <si>
     <t>26.04.18</t>
@@ -1461,7 +1585,7 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="22">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -1474,6 +1598,9 @@
     </xf>
     <xf fontId="3" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf fontId="2" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1" quotePrefix="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1" quotePrefix="1">
       <alignment vertical="top" wrapText="1"/>
@@ -1488,6 +1615,9 @@
     <xf fontId="0" fillId="2" borderId="0" numFmtId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
       <protection hidden="0" locked="1"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf fontId="4" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -2267,19 +2397,23 @@
       <c r="G11" s="3">
         <v>2030</v>
       </c>
+      <c r="H11" s="5"/>
+      <c r="I11" s="3" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="12" ht="42.75">
       <c r="A12" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>11</v>
@@ -2293,19 +2427,19 @@
     </row>
     <row r="13" ht="57">
       <c r="A13" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>12</v>
@@ -2316,16 +2450,16 @@
     </row>
     <row r="14" s="3" customFormat="1" ht="42.75">
       <c r="A14" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>11</v>
@@ -2339,16 +2473,16 @@
     </row>
     <row r="15" ht="42.75">
       <c r="A15" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>11</v>
@@ -2362,16 +2496,16 @@
     </row>
     <row r="16" ht="42.75">
       <c r="A16" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>11</v>
@@ -2385,16 +2519,16 @@
     </row>
     <row r="17" ht="42.75">
       <c r="A17" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>11</v>
@@ -2408,22 +2542,22 @@
     </row>
     <row r="18" ht="42.75">
       <c r="A18" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G18" s="1">
         <v>2100</v>
@@ -2431,22 +2565,22 @@
     </row>
     <row r="19" ht="42.75">
       <c r="A19" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="F19" s="1" t="s">
         <v>87</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="F19" s="1" t="s">
-        <v>86</v>
       </c>
       <c r="G19" s="1">
         <v>2110</v>
@@ -2454,16 +2588,16 @@
     </row>
     <row r="20" ht="42.75">
       <c r="A20" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>11</v>
@@ -2477,16 +2611,16 @@
     </row>
     <row r="21" ht="42.75">
       <c r="A21" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E21" s="1" t="s">
         <v>11</v>
@@ -2500,19 +2634,19 @@
     </row>
     <row r="22" ht="42.75">
       <c r="A22" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>12</v>
@@ -2520,25 +2654,25 @@
       <c r="G22" s="1">
         <v>2040</v>
       </c>
-      <c r="H22" s="5" t="s">
-        <v>103</v>
+      <c r="H22" s="6" t="s">
+        <v>104</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="23" ht="42.75">
       <c r="A23" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E23" s="1" t="s">
         <v>11</v>
@@ -2552,16 +2686,16 @@
     </row>
     <row r="24" ht="42.75">
       <c r="A24" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>11</v>
@@ -2574,57 +2708,60 @@
       </c>
     </row>
     <row r="25" ht="28.5">
-      <c r="A25" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="B25" s="6" t="s">
+      <c r="A25" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="C25" s="6"/>
+      <c r="B25" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="C25" s="7"/>
       <c r="D25" s="1"/>
       <c r="H25" s="1" t="s">
         <v>13</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="26" s="7" customFormat="1" ht="28.5">
-      <c r="A26" s="8" t="s">
         <v>116</v>
       </c>
-      <c r="B26" s="8" t="s">
+    </row>
+    <row r="26" s="8" customFormat="1" ht="28.5">
+      <c r="A26" s="9" t="s">
         <v>117</v>
       </c>
-      <c r="C26" s="8"/>
-      <c r="D26" s="7"/>
+      <c r="B26" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="C26" s="9"/>
+      <c r="D26" s="8"/>
     </row>
     <row r="27" ht="42.75">
-      <c r="A27" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="B27" s="6" t="s">
+      <c r="A27" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="C27" s="6"/>
+      <c r="B27" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="C27" s="7"/>
     </row>
     <row r="28" ht="42.75">
-      <c r="A28" s="6" t="s">
-        <v>120</v>
-      </c>
-      <c r="B28" s="6" t="s">
+      <c r="A28" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="C28" s="6"/>
+      <c r="B28" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="C28" s="7"/>
+      <c r="I28" s="10" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="29" ht="28.5">
-      <c r="A29" s="6" t="s">
-        <v>122</v>
-      </c>
-      <c r="B29" s="6" t="s">
+      <c r="A29" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="C29" s="6"/>
+      <c r="B29" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="C29" s="7"/>
     </row>
   </sheetData>
   <printOptions headings="0" gridLines="0"/>
@@ -2638,188 +2775,265 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" min="2" max="2" width="14.7109375"/>
-    <col customWidth="1" min="5" max="5" width="11.28125"/>
+    <col customWidth="1" min="1" max="1" style="11" width="12.57421875"/>
+    <col customWidth="1" min="2" max="2" style="11" width="13.8515625"/>
+    <col min="3" max="4" style="11" width="9.140625"/>
+    <col customWidth="1" min="5" max="5" style="11" width="12.8515625"/>
+    <col customWidth="1" min="6" max="6" style="11" width="12.421875"/>
+    <col min="7" max="16384" style="11" width="9.140625"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="9" t="s">
-        <v>343</v>
-      </c>
-      <c r="B1" s="9" t="s">
-        <v>305</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>306</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="E1" s="9" t="s">
+    <row r="1" ht="28.5">
+      <c r="A1" s="11" t="s">
+        <v>345</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>346</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>347</v>
+      </c>
+      <c r="D1" s="11" t="s">
+        <v>191</v>
+      </c>
+      <c r="E1" s="11" t="s">
+        <v>348</v>
+      </c>
+      <c r="F1" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="9" t="s">
-        <v>307</v>
+      <c r="G1" s="11" t="s">
+        <v>192</v>
       </c>
     </row>
     <row r="2" ht="25.5">
-      <c r="A2" s="9" t="s">
-        <v>344</v>
-      </c>
-      <c r="B2" s="9" t="s">
-        <v>345</v>
-      </c>
-      <c r="C2" s="14">
-        <v>6.0220000000000003e+23</v>
-      </c>
-      <c r="D2" s="9" t="s">
-        <v>346</v>
-      </c>
-      <c r="E2" s="9" t="s">
-        <v>347</v>
-      </c>
-      <c r="F2" s="9" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="3" ht="25.5">
-      <c r="A3" s="9" t="s">
+      <c r="A2" s="11" t="s">
         <v>349</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="B2" s="11" t="s">
         <v>350</v>
       </c>
-      <c r="C3" s="18">
-        <v>46244</v>
-      </c>
-      <c r="D3" s="9" t="s">
+      <c r="C2" s="16">
+        <v>200000000000</v>
+      </c>
+      <c r="D2" s="11" t="s">
         <v>351</v>
       </c>
-      <c r="E3" s="9" t="s">
-        <v>187</v>
-      </c>
-      <c r="F3" s="9" t="s">
+      <c r="E2" s="11" t="s">
         <v>352</v>
       </c>
-    </row>
-    <row r="4" ht="25.5">
-      <c r="A4" s="9" t="s">
+      <c r="F2" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="G2" s="11" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" ht="42.75">
+      <c r="A3" s="11" t="s">
         <v>353</v>
       </c>
-      <c r="B4" s="9" t="s">
-        <v>341</v>
-      </c>
-      <c r="C4" s="9">
+      <c r="B3" s="11" t="s">
+        <v>354</v>
+      </c>
+      <c r="C3" s="11">
+        <v>5500</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>351</v>
+      </c>
+      <c r="E3" s="11" t="s">
+        <v>355</v>
+      </c>
+      <c r="F3" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="G3" s="11" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" ht="28.5">
+      <c r="A4" s="11" t="s">
+        <v>356</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>357</v>
+      </c>
+      <c r="C4" s="11">
+        <v>24</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>351</v>
+      </c>
+      <c r="E4" s="11" t="s">
+        <v>358</v>
+      </c>
+      <c r="F4" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="G4" s="11" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="5" ht="25.5">
+      <c r="A5" s="11" t="s">
+        <v>359</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>360</v>
+      </c>
+      <c r="C5" s="16">
+        <v>4540000000</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>339</v>
+      </c>
+      <c r="E5" s="11" t="s">
+        <v>361</v>
+      </c>
+      <c r="F5" s="11" t="s">
+        <v>362</v>
+      </c>
+      <c r="G5" s="11" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" ht="28.5">
+      <c r="A6" s="11" t="s">
+        <v>363</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>364</v>
+      </c>
+      <c r="C6" s="16">
+        <v>500000000</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>339</v>
+      </c>
+      <c r="E6" s="11" t="s">
+        <v>365</v>
+      </c>
+      <c r="F6" s="11" t="s">
+        <v>362</v>
+      </c>
+      <c r="G6" s="11" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="7" ht="28.5">
+      <c r="A7" s="11" t="s">
+        <v>366</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>367</v>
+      </c>
+      <c r="C7" s="11">
+        <v>230</v>
+      </c>
+      <c r="D7" s="11" t="s">
+        <v>368</v>
+      </c>
+      <c r="E7" s="11" t="s">
+        <v>369</v>
+      </c>
+      <c r="F7" s="11" t="s">
+        <v>370</v>
+      </c>
+      <c r="G7" s="11" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" ht="28.5">
+      <c r="A8" s="11" t="s">
+        <v>371</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>372</v>
+      </c>
+      <c r="C8" s="11">
+        <v>0.01</v>
+      </c>
+      <c r="D8" s="11" t="s">
+        <v>200</v>
+      </c>
+      <c r="E8" s="11" t="s">
+        <v>373</v>
+      </c>
+      <c r="F8" s="11" t="s">
+        <v>370</v>
+      </c>
+      <c r="G8" s="11" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="9" ht="25.5">
+      <c r="A9" s="11" t="s">
+        <v>374</v>
+      </c>
+      <c r="B9" s="11" t="s">
+        <v>375</v>
+      </c>
+      <c r="C9" s="11">
+        <v>1366</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>376</v>
+      </c>
+      <c r="E9" s="11" t="s">
+        <v>377</v>
+      </c>
+      <c r="F9" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="G9" s="11" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" ht="25.5">
+      <c r="A10" s="11" t="s">
+        <v>378</v>
+      </c>
+      <c r="B10" s="11" t="s">
+        <v>379</v>
+      </c>
+      <c r="C10" s="11">
+        <v>587</v>
+      </c>
+      <c r="D10" s="11" t="s">
+        <v>376</v>
+      </c>
+      <c r="E10" s="11" t="s">
+        <v>380</v>
+      </c>
+      <c r="F10" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="G10" s="11" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" ht="25.5">
+      <c r="A11" s="11" t="s">
+        <v>381</v>
+      </c>
+      <c r="B11" s="11" t="s">
+        <v>382</v>
+      </c>
+      <c r="C11" s="11">
         <v>101.325</v>
       </c>
-      <c r="D4" s="9" t="s">
-        <v>342</v>
-      </c>
-      <c r="E4" s="9" t="s">
-        <v>329</v>
-      </c>
-      <c r="F4" s="9" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="5" ht="25.5">
-      <c r="A5" s="9" t="s">
-        <v>355</v>
-      </c>
-      <c r="B5" s="9" t="s">
-        <v>356</v>
-      </c>
-      <c r="C5" s="9">
-        <v>1366</v>
-      </c>
-      <c r="D5" s="9" t="s">
-        <v>335</v>
-      </c>
-      <c r="E5" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="F5" s="9" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="6" ht="25.5">
-      <c r="A6" s="9" t="s">
-        <v>358</v>
-      </c>
-      <c r="B6" s="9" t="s">
-        <v>359</v>
-      </c>
-      <c r="C6" s="9">
-        <v>587</v>
-      </c>
-      <c r="D6" s="9" t="s">
-        <v>335</v>
-      </c>
-      <c r="E6" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="F6" s="9" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="7" ht="25.5">
-      <c r="A7" s="9" t="s">
-        <v>360</v>
-      </c>
-      <c r="B7" s="9" t="s">
-        <v>361</v>
-      </c>
-      <c r="C7" s="14">
-        <v>299800000</v>
-      </c>
-      <c r="D7" s="9" t="s">
-        <v>362</v>
-      </c>
-      <c r="E7" s="9" t="s">
-        <v>363</v>
-      </c>
-      <c r="F7" s="9" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="8" ht="25.5">
-      <c r="A8" s="9" t="s">
-        <v>364</v>
-      </c>
-      <c r="B8" s="9" t="s">
-        <v>365</v>
-      </c>
-      <c r="C8" s="14">
-        <v>6.6259999999999998e-34</v>
-      </c>
-      <c r="D8" s="9" t="s">
-        <v>366</v>
-      </c>
-      <c r="E8" s="9" t="s">
-        <v>363</v>
-      </c>
-      <c r="F8" s="9" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="9" ht="25.5">
-      <c r="A9" s="9" t="s">
-        <v>367</v>
-      </c>
-      <c r="B9" s="9" t="s">
-        <v>368</v>
-      </c>
-      <c r="C9" s="14">
-        <v>1.3809999999999999e-23</v>
-      </c>
-      <c r="D9" s="9" t="s">
-        <v>369</v>
-      </c>
-      <c r="E9" s="9" t="s">
-        <v>363</v>
-      </c>
-      <c r="F9" s="9" t="s">
-        <v>348</v>
+      <c r="D11" s="11" t="s">
+        <v>383</v>
+      </c>
+      <c r="E11" s="11" t="s">
+        <v>377</v>
+      </c>
+      <c r="F11" s="11" t="s">
+        <v>370</v>
+      </c>
+      <c r="G11" s="11" t="s">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -2834,200 +3048,189 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" min="2" max="2" width="11.28125"/>
-    <col customWidth="1" min="3" max="3" width="14.00390625"/>
-    <col customWidth="1" min="5" max="5" width="12.7109375"/>
+    <col customWidth="1" min="2" max="2" width="14.7109375"/>
+    <col customWidth="1" min="5" max="5" width="11.28125"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="11" t="s">
+        <v>384</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>346</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>347</v>
+      </c>
+      <c r="D1" s="11" t="s">
+        <v>191</v>
+      </c>
+      <c r="E1" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="11" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="2" ht="25.5">
+      <c r="A2" s="11" t="s">
+        <v>385</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>386</v>
+      </c>
+      <c r="C2" s="16">
+        <v>6.0220000000000003e+23</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>387</v>
+      </c>
+      <c r="E2" s="11" t="s">
+        <v>388</v>
+      </c>
+      <c r="F2" s="11" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="3" ht="25.5">
+      <c r="A3" s="11" t="s">
+        <v>390</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>391</v>
+      </c>
+      <c r="C3" s="20">
+        <v>46244</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>392</v>
+      </c>
+      <c r="E3" s="11" t="s">
+        <v>228</v>
+      </c>
+      <c r="F3" s="11" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="4" ht="25.5">
+      <c r="A4" s="11" t="s">
+        <v>394</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>382</v>
+      </c>
+      <c r="C4" s="11">
+        <v>101.325</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>383</v>
+      </c>
+      <c r="E4" s="11" t="s">
         <v>370</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>371</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>372</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>147</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>373</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>374</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>375</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="I1" s="9" t="s">
+      <c r="F4" s="11" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="5" ht="25.5">
+      <c r="A5" s="11" t="s">
+        <v>396</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>397</v>
+      </c>
+      <c r="C5" s="11">
+        <v>1366</v>
+      </c>
+      <c r="D5" s="11" t="s">
         <v>376</v>
       </c>
-      <c r="J1" s="9"/>
-      <c r="K1" s="9"/>
-    </row>
-    <row r="2" ht="25.5">
-      <c r="A2" s="9" t="s">
-        <v>377</v>
-      </c>
-      <c r="B2" s="9" t="s">
-        <v>378</v>
-      </c>
-      <c r="C2" s="9" t="s">
-        <v>379</v>
-      </c>
-      <c r="D2" s="9" t="s">
+      <c r="E5" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="F5" s="11" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="6" ht="25.5">
+      <c r="A6" s="11" t="s">
+        <v>399</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>400</v>
+      </c>
+      <c r="C6" s="11">
+        <v>587</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>376</v>
+      </c>
+      <c r="E6" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="F6" s="11" t="s">
         <v>380</v>
       </c>
-      <c r="E2" s="9" t="s">
-        <v>381</v>
-      </c>
-      <c r="F2" s="9">
-        <v>0.23999999999999999</v>
-      </c>
-      <c r="G2" s="9" t="s">
-        <v>382</v>
-      </c>
-      <c r="H2" s="9">
-        <v>0.22</v>
-      </c>
-      <c r="I2" s="9">
-        <v>0.089999999999999997</v>
-      </c>
-      <c r="J2" s="9" t="s">
-        <v>383</v>
-      </c>
-      <c r="K2" s="9">
-        <v>0.29999999999999999</v>
-      </c>
-    </row>
-    <row r="3" ht="25.5">
-      <c r="A3" s="9" t="s">
-        <v>384</v>
-      </c>
-      <c r="B3" s="9" t="s">
-        <v>385</v>
-      </c>
-      <c r="C3" s="9" t="s">
-        <v>386</v>
-      </c>
-      <c r="D3" s="9">
-        <v>0.45000000000000001</v>
-      </c>
-      <c r="E3" s="9" t="s">
-        <v>387</v>
-      </c>
-      <c r="F3" s="9">
-        <v>0.42999999999999999</v>
-      </c>
-      <c r="G3" s="9">
-        <v>0.050000000000000003</v>
-      </c>
-      <c r="H3" s="9" t="s">
-        <v>388</v>
-      </c>
-      <c r="I3" s="9">
-        <v>0.25</v>
-      </c>
-      <c r="J3" s="9"/>
-      <c r="K3" s="9"/>
-    </row>
-    <row r="4" ht="25.5">
-      <c r="A4" s="9" t="s">
+    </row>
+    <row r="7" ht="25.5">
+      <c r="A7" s="11" t="s">
+        <v>401</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>402</v>
+      </c>
+      <c r="C7" s="16">
+        <v>299800000</v>
+      </c>
+      <c r="D7" s="11" t="s">
+        <v>403</v>
+      </c>
+      <c r="E7" s="11" t="s">
+        <v>404</v>
+      </c>
+      <c r="F7" s="11" t="s">
         <v>389</v>
       </c>
-      <c r="B4" s="9" t="s">
-        <v>390</v>
-      </c>
-      <c r="C4" s="9" t="s">
-        <v>391</v>
-      </c>
-      <c r="D4" s="9">
-        <v>0.59999999999999998</v>
-      </c>
-      <c r="E4" s="9" t="s">
-        <v>392</v>
-      </c>
-      <c r="F4" s="9">
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="G4" s="9">
-        <v>0.089999999999999997</v>
-      </c>
-      <c r="H4" s="9" t="s">
-        <v>264</v>
-      </c>
-      <c r="I4" s="9">
-        <v>0.25</v>
-      </c>
-      <c r="J4" s="9"/>
-      <c r="K4" s="9"/>
-    </row>
-    <row r="5" ht="25.5">
-      <c r="A5" s="9" t="s">
-        <v>393</v>
-      </c>
-      <c r="B5" s="9" t="s">
-        <v>394</v>
-      </c>
-      <c r="C5" s="9" t="s">
-        <v>395</v>
-      </c>
-      <c r="D5" s="9">
-        <v>0.29999999999999999</v>
-      </c>
-      <c r="E5" s="9" t="s">
-        <v>396</v>
-      </c>
-      <c r="F5" s="9">
-        <v>0.29999999999999999</v>
-      </c>
-      <c r="G5" s="9">
-        <v>0</v>
-      </c>
-      <c r="H5" s="9" t="s">
-        <v>397</v>
-      </c>
-      <c r="I5" s="9">
-        <v>0.20000000000000001</v>
-      </c>
-      <c r="J5" s="9"/>
-      <c r="K5" s="9"/>
-    </row>
-    <row r="6" ht="25.5">
-      <c r="A6" s="9" t="s">
-        <v>398</v>
-      </c>
-      <c r="B6" s="9" t="s">
-        <v>399</v>
-      </c>
-      <c r="C6" s="9" t="s">
-        <v>400</v>
-      </c>
-      <c r="D6" s="9">
-        <v>0.46999999999999997</v>
-      </c>
-      <c r="E6" s="9" t="s">
-        <v>382</v>
-      </c>
-      <c r="F6" s="9">
-        <v>0.45000000000000001</v>
-      </c>
-      <c r="G6" s="9">
-        <v>0.040000000000000001</v>
-      </c>
-      <c r="H6" s="9" t="s">
-        <v>388</v>
-      </c>
-      <c r="I6" s="9">
-        <v>0.14999999999999999</v>
-      </c>
-      <c r="J6" s="9"/>
-      <c r="K6" s="9"/>
+    </row>
+    <row r="8" ht="25.5">
+      <c r="A8" s="11" t="s">
+        <v>405</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>406</v>
+      </c>
+      <c r="C8" s="16">
+        <v>6.6259999999999998e-34</v>
+      </c>
+      <c r="D8" s="11" t="s">
+        <v>407</v>
+      </c>
+      <c r="E8" s="11" t="s">
+        <v>404</v>
+      </c>
+      <c r="F8" s="11" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="9" ht="25.5">
+      <c r="A9" s="11" t="s">
+        <v>408</v>
+      </c>
+      <c r="B9" s="11" t="s">
+        <v>409</v>
+      </c>
+      <c r="C9" s="16">
+        <v>1.3809999999999999e-23</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>410</v>
+      </c>
+      <c r="E9" s="11" t="s">
+        <v>404</v>
+      </c>
+      <c r="F9" s="11" t="s">
+        <v>389</v>
+      </c>
     </row>
   </sheetData>
   <printOptions headings="0" gridLines="0"/>
@@ -3041,173 +3244,200 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="2" style="9" width="9.140625"/>
-    <col customWidth="1" min="3" max="3" style="9" width="11.421875"/>
-    <col customWidth="1" min="4" max="4" style="9" width="10.8515625"/>
-    <col customWidth="1" min="5" max="5" style="9" width="14.140625"/>
-    <col min="6" max="16384" style="9" width="9.140625"/>
+    <col customWidth="1" min="2" max="2" width="11.28125"/>
+    <col customWidth="1" min="3" max="3" width="14.00390625"/>
+    <col customWidth="1" min="5" max="5" width="12.7109375"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="9" t="s">
-        <v>401</v>
-      </c>
-      <c r="B1" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>144</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>402</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>403</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>404</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>405</v>
-      </c>
+      <c r="A1" s="11" t="s">
+        <v>411</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>412</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>413</v>
+      </c>
+      <c r="D1" s="11" t="s">
+        <v>189</v>
+      </c>
+      <c r="E1" s="11" t="s">
+        <v>414</v>
+      </c>
+      <c r="F1" s="11" t="s">
+        <v>415</v>
+      </c>
+      <c r="G1" s="11" t="s">
+        <v>416</v>
+      </c>
+      <c r="H1" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="I1" s="11" t="s">
+        <v>417</v>
+      </c>
+      <c r="J1" s="11"/>
+      <c r="K1" s="11"/>
     </row>
     <row r="2" ht="25.5">
-      <c r="A2" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="B2" s="9" t="s">
-        <v>153</v>
-      </c>
-      <c r="C2" s="9" t="s">
-        <v>154</v>
-      </c>
-      <c r="D2" s="9" t="s">
-        <v>161</v>
-      </c>
-      <c r="E2" s="9" t="s">
-        <v>406</v>
-      </c>
-      <c r="F2" s="9">
-        <v>2025</v>
-      </c>
-      <c r="G2" s="9" t="s">
-        <v>407</v>
+      <c r="A2" s="11" t="s">
+        <v>418</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>419</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>420</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>421</v>
+      </c>
+      <c r="E2" s="11" t="s">
+        <v>422</v>
+      </c>
+      <c r="F2" s="11">
+        <v>0.23999999999999999</v>
+      </c>
+      <c r="G2" s="11" t="s">
+        <v>423</v>
+      </c>
+      <c r="H2" s="11">
+        <v>0.22</v>
+      </c>
+      <c r="I2" s="11">
+        <v>0.089999999999999997</v>
+      </c>
+      <c r="J2" s="11" t="s">
+        <v>424</v>
+      </c>
+      <c r="K2" s="11">
+        <v>0.29999999999999999</v>
       </c>
     </row>
     <row r="3" ht="25.5">
-      <c r="A3" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3" s="9" t="s">
-        <v>238</v>
-      </c>
-      <c r="C3" s="9" t="s">
-        <v>239</v>
-      </c>
-      <c r="D3" s="9" t="s">
-        <v>408</v>
-      </c>
-      <c r="E3" s="9" t="s">
-        <v>409</v>
-      </c>
-      <c r="F3" s="9">
-        <v>2026</v>
-      </c>
-      <c r="G3" s="9" t="s">
-        <v>410</v>
-      </c>
+      <c r="A3" s="11" t="s">
+        <v>425</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>426</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>427</v>
+      </c>
+      <c r="D3" s="11">
+        <v>0.45000000000000001</v>
+      </c>
+      <c r="E3" s="11" t="s">
+        <v>428</v>
+      </c>
+      <c r="F3" s="11">
+        <v>0.42999999999999999</v>
+      </c>
+      <c r="G3" s="11">
+        <v>0.050000000000000003</v>
+      </c>
+      <c r="H3" s="11" t="s">
+        <v>429</v>
+      </c>
+      <c r="I3" s="11">
+        <v>0.25</v>
+      </c>
+      <c r="J3" s="11"/>
+      <c r="K3" s="11"/>
     </row>
     <row r="4" ht="25.5">
-      <c r="A4" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="B4" s="9" t="s">
-        <v>183</v>
-      </c>
-      <c r="C4" s="9" t="s">
-        <v>184</v>
-      </c>
-      <c r="D4" s="9" t="s">
-        <v>411</v>
-      </c>
-      <c r="E4" s="9" t="s">
-        <v>412</v>
-      </c>
-      <c r="F4" s="9">
-        <v>2024</v>
-      </c>
-      <c r="G4" s="9" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="5" ht="38.25">
-      <c r="A5" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="B5" s="9" t="s">
-        <v>260</v>
-      </c>
-      <c r="C5" s="9" t="s">
-        <v>261</v>
-      </c>
-      <c r="D5" s="9" t="s">
-        <v>414</v>
-      </c>
-      <c r="E5" s="9" t="s">
-        <v>415</v>
-      </c>
-      <c r="F5" s="9">
-        <v>2024</v>
-      </c>
-      <c r="G5" s="9" t="s">
-        <v>416</v>
-      </c>
+      <c r="A4" s="11" t="s">
+        <v>430</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>431</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>432</v>
+      </c>
+      <c r="D4" s="11">
+        <v>0.59999999999999998</v>
+      </c>
+      <c r="E4" s="11" t="s">
+        <v>433</v>
+      </c>
+      <c r="F4" s="11">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="G4" s="11">
+        <v>0.089999999999999997</v>
+      </c>
+      <c r="H4" s="11" t="s">
+        <v>305</v>
+      </c>
+      <c r="I4" s="11">
+        <v>0.25</v>
+      </c>
+      <c r="J4" s="11"/>
+      <c r="K4" s="11"/>
+    </row>
+    <row r="5" ht="25.5">
+      <c r="A5" s="11" t="s">
+        <v>434</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>435</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>436</v>
+      </c>
+      <c r="D5" s="11">
+        <v>0.29999999999999999</v>
+      </c>
+      <c r="E5" s="11" t="s">
+        <v>437</v>
+      </c>
+      <c r="F5" s="11">
+        <v>0.29999999999999999</v>
+      </c>
+      <c r="G5" s="11">
+        <v>0</v>
+      </c>
+      <c r="H5" s="11" t="s">
+        <v>438</v>
+      </c>
+      <c r="I5" s="11">
+        <v>0.20000000000000001</v>
+      </c>
+      <c r="J5" s="11"/>
+      <c r="K5" s="11"/>
     </row>
     <row r="6" ht="25.5">
-      <c r="A6" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="B6" s="9" t="s">
-        <v>177</v>
-      </c>
-      <c r="C6" s="9" t="s">
-        <v>178</v>
-      </c>
-      <c r="D6" s="9" t="s">
-        <v>417</v>
-      </c>
-      <c r="E6" s="9" t="s">
-        <v>418</v>
-      </c>
-      <c r="F6" s="9">
-        <v>2030</v>
-      </c>
-      <c r="G6" s="9" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="7" ht="25.5">
-      <c r="A7" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="B7" s="9" t="s">
-        <v>249</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>250</v>
-      </c>
-      <c r="D7" s="9" t="s">
-        <v>254</v>
-      </c>
-      <c r="E7" s="9" t="s">
-        <v>420</v>
-      </c>
-      <c r="F7" s="9">
-        <v>2028</v>
-      </c>
-      <c r="G7" s="9" t="s">
-        <v>421</v>
-      </c>
+      <c r="A6" s="11" t="s">
+        <v>439</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>440</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>441</v>
+      </c>
+      <c r="D6" s="11">
+        <v>0.46999999999999997</v>
+      </c>
+      <c r="E6" s="11" t="s">
+        <v>423</v>
+      </c>
+      <c r="F6" s="11">
+        <v>0.45000000000000001</v>
+      </c>
+      <c r="G6" s="11">
+        <v>0.040000000000000001</v>
+      </c>
+      <c r="H6" s="11" t="s">
+        <v>429</v>
+      </c>
+      <c r="I6" s="11">
+        <v>0.14999999999999999</v>
+      </c>
+      <c r="J6" s="11"/>
+      <c r="K6" s="11"/>
     </row>
   </sheetData>
   <printOptions headings="0" gridLines="0"/>
@@ -3221,144 +3451,172 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col bestFit="1" min="1" max="1" style="9" width="10.7109375"/>
-    <col min="2" max="2" style="9" width="9.140625"/>
-    <col customWidth="1" min="3" max="3" style="9" width="10.7109375"/>
-    <col min="4" max="5" style="9" width="9.140625"/>
-    <col customWidth="1" min="6" max="6" style="9" width="11.57421875"/>
-    <col min="7" max="7" style="9" width="9.140625"/>
-    <col customWidth="1" min="8" max="8" style="9" width="10.8515625"/>
-    <col min="9" max="16384" style="9" width="9.140625"/>
+    <col min="1" max="2" style="11" width="9.140625"/>
+    <col customWidth="1" min="3" max="3" style="11" width="11.421875"/>
+    <col customWidth="1" min="4" max="4" style="11" width="10.8515625"/>
+    <col customWidth="1" min="5" max="5" style="11" width="14.140625"/>
+    <col min="6" max="16384" style="11" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="9" t="s">
-        <v>422</v>
-      </c>
-      <c r="B1" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>144</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>423</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>424</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>425</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>426</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>427</v>
+      <c r="A1" s="11" t="s">
+        <v>442</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>185</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="D1" s="11" t="s">
+        <v>443</v>
+      </c>
+      <c r="E1" s="11" t="s">
+        <v>444</v>
+      </c>
+      <c r="F1" s="11" t="s">
+        <v>445</v>
+      </c>
+      <c r="G1" s="11" t="s">
+        <v>446</v>
       </c>
     </row>
     <row r="2" ht="25.5">
-      <c r="A2" s="19">
-        <v>45306</v>
-      </c>
-      <c r="B2" s="9" t="s">
-        <v>163</v>
-      </c>
-      <c r="C2" s="9" t="s">
-        <v>164</v>
-      </c>
-      <c r="D2" s="9">
-        <v>0.20000000000000001</v>
-      </c>
-      <c r="E2" s="9">
-        <v>0.22</v>
-      </c>
-      <c r="F2" s="9" t="s">
-        <v>428</v>
-      </c>
-      <c r="G2" s="9" t="s">
-        <v>407</v>
-      </c>
-      <c r="H2" s="9" t="s">
-        <v>429</v>
+      <c r="A2" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>196</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>203</v>
+      </c>
+      <c r="E2" s="11" t="s">
+        <v>447</v>
+      </c>
+      <c r="F2" s="11">
+        <v>2025</v>
+      </c>
+      <c r="G2" s="11" t="s">
+        <v>448</v>
       </c>
     </row>
     <row r="3" ht="25.5">
-      <c r="A3" s="19">
-        <v>45301</v>
-      </c>
-      <c r="B3" s="9" t="s">
-        <v>189</v>
-      </c>
-      <c r="C3" s="9" t="s">
-        <v>190</v>
-      </c>
-      <c r="D3" s="9">
-        <v>0.12</v>
-      </c>
-      <c r="E3" s="9">
-        <v>0.14999999999999999</v>
-      </c>
-      <c r="F3" s="9" t="s">
-        <v>430</v>
-      </c>
-      <c r="G3" s="9" t="s">
-        <v>431</v>
-      </c>
-      <c r="H3" s="9" t="s">
-        <v>432</v>
+      <c r="A3" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>279</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>280</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>449</v>
+      </c>
+      <c r="E3" s="11" t="s">
+        <v>450</v>
+      </c>
+      <c r="F3" s="11">
+        <v>2026</v>
+      </c>
+      <c r="G3" s="11" t="s">
+        <v>451</v>
       </c>
     </row>
     <row r="4" ht="25.5">
-      <c r="A4" s="19">
-        <v>45265</v>
-      </c>
-      <c r="B4" s="9" t="s">
-        <v>209</v>
-      </c>
-      <c r="C4" s="9" t="s">
-        <v>210</v>
-      </c>
-      <c r="D4" s="9">
-        <v>150</v>
-      </c>
-      <c r="E4" s="9">
-        <v>180</v>
-      </c>
-      <c r="F4" s="9" t="s">
-        <v>433</v>
-      </c>
-      <c r="G4" s="9" t="s">
-        <v>434</v>
-      </c>
-      <c r="H4" s="9" t="s">
-        <v>435</v>
+      <c r="A4" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>224</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>225</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>452</v>
+      </c>
+      <c r="E4" s="11" t="s">
+        <v>453</v>
+      </c>
+      <c r="F4" s="11">
+        <v>2024</v>
+      </c>
+      <c r="G4" s="11" t="s">
+        <v>454</v>
       </c>
     </row>
     <row r="5" ht="38.25">
-      <c r="A5" s="19">
-        <v>45250</v>
-      </c>
-      <c r="B5" s="9" t="s">
-        <v>260</v>
-      </c>
-      <c r="C5" s="9" t="s">
-        <v>261</v>
-      </c>
-      <c r="D5" s="9">
-        <v>0.080000000000000002</v>
-      </c>
-      <c r="E5" s="9">
-        <v>0.10000000000000001</v>
-      </c>
-      <c r="F5" s="9" t="s">
-        <v>436</v>
-      </c>
-      <c r="G5" s="9" t="s">
-        <v>416</v>
-      </c>
-      <c r="H5" s="9" t="s">
-        <v>437</v>
+      <c r="A5" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>301</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>302</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>455</v>
+      </c>
+      <c r="E5" s="11" t="s">
+        <v>456</v>
+      </c>
+      <c r="F5" s="11">
+        <v>2024</v>
+      </c>
+      <c r="G5" s="11" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="6" ht="25.5">
+      <c r="A6" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>218</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>219</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>458</v>
+      </c>
+      <c r="E6" s="11" t="s">
+        <v>459</v>
+      </c>
+      <c r="F6" s="11">
+        <v>2030</v>
+      </c>
+      <c r="G6" s="11" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="7" ht="25.5">
+      <c r="A7" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>290</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>291</v>
+      </c>
+      <c r="D7" s="11" t="s">
+        <v>295</v>
+      </c>
+      <c r="E7" s="11" t="s">
+        <v>461</v>
+      </c>
+      <c r="F7" s="11">
+        <v>2028</v>
+      </c>
+      <c r="G7" s="11" t="s">
+        <v>462</v>
       </c>
     </row>
   </sheetData>
@@ -3371,114 +3629,266 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="3" style="9" width="9.140625"/>
-    <col customWidth="1" min="4" max="4" style="9" width="13.421875"/>
-    <col customWidth="1" min="5" max="5" style="9" width="12.8515625"/>
-    <col min="6" max="16384" style="9" width="9.140625"/>
+    <col bestFit="1" min="1" max="1" style="11" width="10.7109375"/>
+    <col min="2" max="2" style="11" width="9.140625"/>
+    <col customWidth="1" min="3" max="3" style="11" width="10.7109375"/>
+    <col min="4" max="5" style="11" width="9.140625"/>
+    <col customWidth="1" min="6" max="6" style="11" width="11.57421875"/>
+    <col min="7" max="7" style="11" width="9.140625"/>
+    <col customWidth="1" min="8" max="8" style="11" width="10.8515625"/>
+    <col min="9" max="16384" style="11" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="9" t="s">
-        <v>438</v>
-      </c>
-      <c r="B1" s="9" t="s">
-        <v>439</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>440</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>441</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>305</v>
+      <c r="A1" s="11" t="s">
+        <v>463</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>185</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="D1" s="11" t="s">
+        <v>464</v>
+      </c>
+      <c r="E1" s="11" t="s">
+        <v>465</v>
+      </c>
+      <c r="F1" s="11" t="s">
+        <v>466</v>
+      </c>
+      <c r="G1" s="11" t="s">
+        <v>467</v>
+      </c>
+      <c r="H1" s="11" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="2" ht="25.5">
+      <c r="A2" s="21">
+        <v>45306</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>205</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>206</v>
+      </c>
+      <c r="D2" s="11">
+        <v>0.20000000000000001</v>
+      </c>
+      <c r="E2" s="11">
+        <v>0.22</v>
+      </c>
+      <c r="F2" s="11" t="s">
+        <v>469</v>
+      </c>
+      <c r="G2" s="11" t="s">
+        <v>448</v>
+      </c>
+      <c r="H2" s="11" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="3" ht="25.5">
+      <c r="A3" s="21">
+        <v>45301</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>230</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>231</v>
+      </c>
+      <c r="D3" s="11">
+        <v>0.12</v>
+      </c>
+      <c r="E3" s="11">
+        <v>0.14999999999999999</v>
+      </c>
+      <c r="F3" s="11" t="s">
+        <v>471</v>
+      </c>
+      <c r="G3" s="11" t="s">
+        <v>472</v>
+      </c>
+      <c r="H3" s="11" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="4" ht="25.5">
+      <c r="A4" s="21">
+        <v>45265</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>250</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>251</v>
+      </c>
+      <c r="D4" s="11">
+        <v>150</v>
+      </c>
+      <c r="E4" s="11">
+        <v>180</v>
+      </c>
+      <c r="F4" s="11" t="s">
+        <v>474</v>
+      </c>
+      <c r="G4" s="11" t="s">
+        <v>475</v>
+      </c>
+      <c r="H4" s="11" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="5" ht="38.25">
+      <c r="A5" s="21">
+        <v>45250</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>301</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>302</v>
+      </c>
+      <c r="D5" s="11">
+        <v>0.080000000000000002</v>
+      </c>
+      <c r="E5" s="11">
+        <v>0.10000000000000001</v>
+      </c>
+      <c r="F5" s="11" t="s">
+        <v>477</v>
+      </c>
+      <c r="G5" s="11" t="s">
+        <v>457</v>
+      </c>
+      <c r="H5" s="11" t="s">
+        <v>478</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="0" gridLines="0"/>
+  <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+  <sheetFormatPr defaultRowHeight="14.25"/>
+  <cols>
+    <col min="1" max="3" style="11" width="9.140625"/>
+    <col customWidth="1" min="4" max="4" style="11" width="13.421875"/>
+    <col customWidth="1" min="5" max="5" style="11" width="12.8515625"/>
+    <col min="6" max="16384" style="11" width="9.140625"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="11" t="s">
+        <v>479</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>480</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>481</v>
+      </c>
+      <c r="D1" s="11" t="s">
+        <v>482</v>
+      </c>
+      <c r="E1" s="11" t="s">
+        <v>346</v>
       </c>
     </row>
     <row r="2" ht="38.25">
-      <c r="A2" s="9" t="s">
-        <v>153</v>
-      </c>
-      <c r="B2" s="9" t="s">
-        <v>163</v>
-      </c>
-      <c r="C2" s="9">
+      <c r="A2" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>205</v>
+      </c>
+      <c r="C2" s="11">
         <v>0.84999999999999998</v>
       </c>
-      <c r="D2" s="9" t="s">
-        <v>442</v>
-      </c>
-      <c r="E2" s="9" t="s">
-        <v>443</v>
+      <c r="D2" s="11" t="s">
+        <v>483</v>
+      </c>
+      <c r="E2" s="11" t="s">
+        <v>484</v>
       </c>
     </row>
     <row r="3" ht="38.25">
-      <c r="A3" s="9" t="s">
-        <v>183</v>
-      </c>
-      <c r="B3" s="9" t="s">
-        <v>189</v>
-      </c>
-      <c r="C3" s="9">
+      <c r="A3" s="11" t="s">
+        <v>224</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>230</v>
+      </c>
+      <c r="C3" s="11">
         <v>0.59999999999999998</v>
       </c>
-      <c r="D3" s="9" t="s">
-        <v>444</v>
-      </c>
-      <c r="E3" s="9" t="s">
-        <v>445</v>
+      <c r="D3" s="11" t="s">
+        <v>485</v>
+      </c>
+      <c r="E3" s="11" t="s">
+        <v>486</v>
       </c>
     </row>
     <row r="4" ht="38.25">
-      <c r="A4" s="9" t="s">
-        <v>209</v>
-      </c>
-      <c r="B4" s="9" t="s">
-        <v>232</v>
-      </c>
-      <c r="C4" s="9">
+      <c r="A4" s="11" t="s">
+        <v>250</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>273</v>
+      </c>
+      <c r="C4" s="11">
         <v>0.75</v>
       </c>
-      <c r="D4" s="9" t="s">
-        <v>442</v>
-      </c>
-      <c r="E4" s="9" t="s">
-        <v>446</v>
+      <c r="D4" s="11" t="s">
+        <v>483</v>
+      </c>
+      <c r="E4" s="11" t="s">
+        <v>487</v>
       </c>
     </row>
     <row r="5" ht="38.25">
-      <c r="A5" s="9" t="s">
-        <v>238</v>
-      </c>
-      <c r="B5" s="9" t="s">
-        <v>244</v>
-      </c>
-      <c r="C5" s="9">
+      <c r="A5" s="11" t="s">
+        <v>279</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>285</v>
+      </c>
+      <c r="C5" s="11">
         <v>0.40000000000000002</v>
       </c>
-      <c r="D5" s="9" t="s">
-        <v>447</v>
-      </c>
-      <c r="E5" s="9" t="s">
-        <v>448</v>
+      <c r="D5" s="11" t="s">
+        <v>488</v>
+      </c>
+      <c r="E5" s="11" t="s">
+        <v>489</v>
       </c>
     </row>
     <row r="6" ht="38.25">
-      <c r="A6" s="9" t="s">
-        <v>260</v>
-      </c>
-      <c r="B6" s="9" t="s">
-        <v>272</v>
-      </c>
-      <c r="C6" s="9">
+      <c r="A6" s="11" t="s">
+        <v>301</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>313</v>
+      </c>
+      <c r="C6" s="11">
         <v>-0.69999999999999996</v>
       </c>
-      <c r="D6" s="9" t="s">
-        <v>449</v>
-      </c>
-      <c r="E6" s="9" t="s">
-        <v>450</v>
+      <c r="D6" s="11" t="s">
+        <v>490</v>
+      </c>
+      <c r="E6" s="11" t="s">
+        <v>491</v>
       </c>
     </row>
   </sheetData>
@@ -3491,89 +3901,266 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr baseColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" style="9" width="10.28125"/>
-    <col customWidth="1" min="2" max="2" style="9" width="12.00390625"/>
-    <col customWidth="1" min="3" max="3" style="9" width="11.140625"/>
-    <col min="4" max="16384" style="9" width="10.28125"/>
+    <col min="1" max="16384" style="1" width="10.28125"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="9" t="s">
-        <v>124</v>
-      </c>
-      <c r="B1" s="9" t="s">
+    <row r="1" ht="42.75">
+      <c r="A1" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="B1" s="1" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="2" ht="25.5">
-      <c r="A2" s="9" t="s">
+      <c r="C1" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="D1" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="E1" s="1" t="s">
         <v>129</v>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="9" t="s">
+      <c r="F1" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="G1" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="C3" s="10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="9" t="s">
+    </row>
+    <row r="2" ht="114">
+      <c r="A2" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="B2" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="C4" s="9">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="5" ht="38.25">
-      <c r="A5" s="9" t="s">
+      <c r="C2" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="D2" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="E2" s="1" t="s">
         <v>136</v>
       </c>
-    </row>
-    <row r="6" ht="25.5">
-      <c r="A6" s="9" t="s">
+      <c r="F2" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="B6" s="9" t="s">
+      <c r="G2" s="1">
+        <v>2030</v>
+      </c>
+      <c r="H2" s="6"/>
+      <c r="I2" s="10" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="3" ht="171">
+      <c r="A3" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="C6" s="9" t="s">
+      <c r="B3" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>139</v>
       </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="9" t="s">
+      <c r="D3" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="B7" s="9" t="s">
+      <c r="E3" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="G3" s="1">
+        <v>2035</v>
+      </c>
+    </row>
+    <row r="4" ht="114">
+      <c r="A4" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="C7" s="9" t="s">
+      <c r="B4" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>142</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="G4" s="1">
+        <v>2040</v>
+      </c>
+    </row>
+    <row r="5" ht="128.25">
+      <c r="A5" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="G5" s="1">
+        <v>2035</v>
+      </c>
+    </row>
+    <row r="6" ht="128.25">
+      <c r="A6" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="G6" s="1">
+        <v>2035</v>
+      </c>
+    </row>
+    <row r="7" ht="114">
+      <c r="A7" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="G7" s="1">
+        <v>2040</v>
+      </c>
+    </row>
+    <row r="8" ht="99.75">
+      <c r="A8" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="G8" s="1">
+        <v>2030</v>
+      </c>
+    </row>
+    <row r="9" ht="114">
+      <c r="A9" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="G9" s="1">
+        <v>2035</v>
+      </c>
+    </row>
+    <row r="10" ht="128.25">
+      <c r="A10" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="G10" s="1">
+        <v>2030</v>
+      </c>
+    </row>
+    <row r="11" ht="128.25">
+      <c r="A11" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="G11" s="1">
+        <v>2040</v>
       </c>
     </row>
   </sheetData>
@@ -3586,202 +4173,89 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr baseColWidth="9" defaultRowHeight="14.25"/>
+  <sheetFormatPr baseColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="3" style="9" width="10.28125"/>
-    <col customWidth="1" min="4" max="4" style="9" width="12.8515625"/>
-    <col bestFit="1" customWidth="1" min="5" max="6" style="9" width="9"/>
-    <col min="7" max="16384" style="9" width="10.28125"/>
+    <col min="1" max="1" style="11" width="10.28125"/>
+    <col customWidth="1" min="2" max="2" style="11" width="12.00390625"/>
+    <col customWidth="1" min="3" max="3" style="11" width="11.140625"/>
+    <col min="4" max="16384" style="11" width="10.28125"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.25">
-      <c r="A1" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="B1" s="9" t="s">
-        <v>144</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>145</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>146</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>147</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>148</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>150</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>151</v>
-      </c>
-      <c r="J1" s="9" t="s">
+    <row r="1">
+      <c r="A1" s="11" t="s">
+        <v>166</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>167</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="2" ht="25.5">
+      <c r="A2" s="11" t="s">
+        <v>169</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>170</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="11" t="s">
+        <v>172</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>173</v>
+      </c>
+      <c r="C3" s="12">
         <v>1</v>
       </c>
-      <c r="K1" s="9" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="2" ht="51">
-      <c r="A2" s="9" t="s">
-        <v>153</v>
-      </c>
-      <c r="B2" s="9" t="s">
-        <v>154</v>
-      </c>
-      <c r="C2" s="9" t="s">
-        <v>155</v>
-      </c>
-      <c r="D2" s="9" t="s">
-        <v>156</v>
-      </c>
-      <c r="E2" s="11">
-        <v>0.0001</v>
-      </c>
-      <c r="F2" s="9" t="s">
-        <v>157</v>
-      </c>
-      <c r="G2" s="9" t="s">
-        <v>158</v>
-      </c>
-      <c r="H2" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="I2" s="9" t="s">
-        <v>159</v>
-      </c>
-      <c r="J2" s="9" t="s">
-        <v>160</v>
-      </c>
-      <c r="K2" s="9" t="s">
-        <v>161</v>
-      </c>
-      <c r="L2" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="M2" s="9" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="3" ht="51">
-      <c r="A3" s="9" t="s">
-        <v>163</v>
-      </c>
-      <c r="B3" s="9" t="s">
-        <v>164</v>
-      </c>
-      <c r="C3" s="9" t="s">
-        <v>165</v>
-      </c>
-      <c r="D3" s="9" t="s">
-        <v>166</v>
-      </c>
-      <c r="E3" s="12">
-        <v>0.22</v>
-      </c>
-      <c r="F3" s="12">
-        <v>0.25</v>
-      </c>
-      <c r="G3" s="9" t="s">
-        <v>158</v>
-      </c>
-      <c r="H3" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="I3" s="9" t="s">
-        <v>159</v>
-      </c>
-      <c r="J3" s="9" t="s">
-        <v>160</v>
-      </c>
-      <c r="K3" s="9" t="s">
-        <v>167</v>
-      </c>
-      <c r="M3" s="13" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="4" ht="38.25">
-      <c r="A4" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="B4" s="9" t="s">
-        <v>170</v>
-      </c>
-      <c r="C4" s="9" t="s">
-        <v>171</v>
-      </c>
-      <c r="D4" s="9" t="s">
-        <v>172</v>
-      </c>
-      <c r="E4" s="10">
-        <v>0.5</v>
-      </c>
-      <c r="F4" s="10">
-        <v>0.80000000000000004</v>
-      </c>
-      <c r="G4" s="9" t="s">
-        <v>158</v>
-      </c>
-      <c r="H4" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="I4" s="9" t="s">
-        <v>173</v>
-      </c>
-      <c r="J4" s="9" t="s">
-        <v>160</v>
-      </c>
-      <c r="K4" s="9" t="s">
+    </row>
+    <row r="4">
+      <c r="A4" s="11" t="s">
         <v>174</v>
       </c>
-      <c r="L4" s="9" t="s">
+      <c r="B4" s="11" t="s">
         <v>175</v>
       </c>
-      <c r="M4" s="9" t="s">
+      <c r="C4" s="11">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="5" ht="38.25">
+      <c r="A5" s="11" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="5" ht="25.5">
-      <c r="A5" s="9" t="s">
+      <c r="B5" s="11" t="s">
         <v>177</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="C5" s="11" t="s">
         <v>178</v>
       </c>
-      <c r="C5" s="9" t="s">
+    </row>
+    <row r="6" ht="25.5">
+      <c r="A6" s="11" t="s">
         <v>179</v>
       </c>
-      <c r="D5" s="9" t="s">
+      <c r="B6" s="11" t="s">
         <v>180</v>
       </c>
-      <c r="E5" s="14">
-        <v>1.0000000000000001e-15</v>
-      </c>
-      <c r="F5" s="14">
-        <v>1e-10</v>
-      </c>
-      <c r="G5" s="9" t="s">
-        <v>158</v>
-      </c>
-      <c r="H5" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="I5" s="9" t="s">
+      <c r="C6" s="11" t="s">
         <v>181</v>
       </c>
-      <c r="J5" s="9" t="s">
-        <v>160</v>
-      </c>
-      <c r="K5" s="9" t="s">
+    </row>
+    <row r="7">
+      <c r="A7" s="11" t="s">
         <v>182</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>183</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>184</v>
       </c>
     </row>
   </sheetData>
@@ -3796,207 +4270,200 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
   <sheetFormatPr baseColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="3" style="9" width="10.28125"/>
-    <col customWidth="1" min="4" max="4" style="9" width="14.57421875"/>
-    <col min="5" max="16384" style="9" width="10.28125"/>
+    <col min="1" max="3" style="11" width="10.28125"/>
+    <col customWidth="1" min="4" max="4" style="11" width="12.8515625"/>
+    <col bestFit="1" customWidth="1" min="5" max="6" style="11" width="9"/>
+    <col min="7" max="16384" style="11" width="10.28125"/>
   </cols>
   <sheetData>
     <row r="1" ht="14.25">
-      <c r="A1" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="B1" s="9" t="s">
-        <v>144</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>145</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>146</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>147</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>148</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>150</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>151</v>
-      </c>
-      <c r="J1" s="9" t="s">
+      <c r="A1" s="11" t="s">
+        <v>185</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>187</v>
+      </c>
+      <c r="D1" s="11" t="s">
+        <v>188</v>
+      </c>
+      <c r="E1" s="11" t="s">
+        <v>189</v>
+      </c>
+      <c r="F1" s="11" t="s">
+        <v>190</v>
+      </c>
+      <c r="G1" s="11" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1" s="11" t="s">
+        <v>192</v>
+      </c>
+      <c r="I1" s="11" t="s">
+        <v>193</v>
+      </c>
+      <c r="J1" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="K1" s="9" t="s">
-        <v>152</v>
-      </c>
-      <c r="L1" s="9"/>
+      <c r="K1" s="11" t="s">
+        <v>194</v>
+      </c>
     </row>
     <row r="2" ht="51">
-      <c r="A2" s="9" t="s">
-        <v>183</v>
-      </c>
-      <c r="B2" s="9" t="s">
-        <v>184</v>
-      </c>
-      <c r="C2" s="9" t="s">
-        <v>185</v>
-      </c>
-      <c r="D2" s="9" t="s">
-        <v>186</v>
-      </c>
-      <c r="E2" s="15">
-        <v>0.012</v>
-      </c>
-      <c r="F2" s="15">
-        <v>0.014999999999999999</v>
-      </c>
-      <c r="G2" s="9" t="s">
-        <v>158</v>
-      </c>
-      <c r="H2" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="I2" s="9" t="s">
-        <v>159</v>
-      </c>
-      <c r="J2" s="9" t="s">
-        <v>187</v>
-      </c>
-      <c r="K2" s="9" t="s">
-        <v>188</v>
-      </c>
-      <c r="L2" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="M2" s="9" t="s">
-        <v>162</v>
+      <c r="A2" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>196</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>197</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>198</v>
+      </c>
+      <c r="E2" s="13">
+        <v>0.0001</v>
+      </c>
+      <c r="F2" s="11" t="s">
+        <v>199</v>
+      </c>
+      <c r="G2" s="11" t="s">
+        <v>200</v>
+      </c>
+      <c r="H2" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="I2" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="J2" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="K2" s="11" t="s">
+        <v>203</v>
+      </c>
+      <c r="L2" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="M2" s="11" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="3" ht="51">
-      <c r="A3" s="9" t="s">
-        <v>189</v>
-      </c>
-      <c r="B3" s="9" t="s">
-        <v>190</v>
-      </c>
-      <c r="C3" s="9" t="s">
-        <v>191</v>
-      </c>
-      <c r="D3" s="9" t="s">
-        <v>192</v>
-      </c>
-      <c r="E3" s="12">
-        <v>0.14999999999999999</v>
-      </c>
-      <c r="F3" s="12">
-        <v>0.29999999999999999</v>
-      </c>
-      <c r="G3" s="9" t="s">
-        <v>158</v>
-      </c>
-      <c r="H3" s="9" t="s">
+      <c r="A3" s="11" t="s">
+        <v>205</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>206</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>207</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>208</v>
+      </c>
+      <c r="E3" s="14">
+        <v>0.22</v>
+      </c>
+      <c r="F3" s="14">
+        <v>0.25</v>
+      </c>
+      <c r="G3" s="11" t="s">
+        <v>200</v>
+      </c>
+      <c r="H3" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="I3" s="9" t="s">
-        <v>159</v>
-      </c>
-      <c r="J3" s="9" t="s">
-        <v>187</v>
-      </c>
-      <c r="K3" s="9" t="s">
-        <v>193</v>
-      </c>
-      <c r="L3" s="9" t="s">
-        <v>175</v>
-      </c>
-      <c r="M3" s="9" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="4" ht="51">
-      <c r="A4" s="9" t="s">
-        <v>195</v>
-      </c>
-      <c r="B4" s="9" t="s">
-        <v>196</v>
-      </c>
-      <c r="C4" s="9" t="s">
-        <v>197</v>
-      </c>
-      <c r="D4" s="9" t="s">
-        <v>198</v>
-      </c>
-      <c r="E4" s="10">
-        <v>0.29999999999999999</v>
-      </c>
-      <c r="F4" s="10">
-        <v>0.90000000000000002</v>
-      </c>
-      <c r="G4" s="9" t="s">
-        <v>158</v>
-      </c>
-      <c r="H4" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="I4" s="9" t="s">
-        <v>199</v>
-      </c>
-      <c r="J4" s="9" t="s">
-        <v>187</v>
-      </c>
-      <c r="K4" s="9" t="s">
+      <c r="I3" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="J3" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="K3" s="11" t="s">
+        <v>209</v>
+      </c>
+      <c r="M3" s="15" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="4" ht="38.25">
+      <c r="A4" s="11" t="s">
+        <v>211</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>212</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>213</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>214</v>
+      </c>
+      <c r="E4" s="12">
+        <v>0.5</v>
+      </c>
+      <c r="F4" s="12">
+        <v>0.80000000000000004</v>
+      </c>
+      <c r="G4" s="11" t="s">
         <v>200</v>
       </c>
-      <c r="L4" s="9" t="s">
-        <v>175</v>
-      </c>
-      <c r="M4" s="9" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="5" s="16" customFormat="1" ht="38.25">
-      <c r="A5" s="16" t="s">
+      <c r="H4" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="I4" s="11" t="s">
+        <v>215</v>
+      </c>
+      <c r="J4" s="11" t="s">
         <v>202</v>
       </c>
-      <c r="B5" s="16" t="s">
-        <v>203</v>
-      </c>
-      <c r="C5" s="16" t="s">
-        <v>204</v>
-      </c>
-      <c r="D5" s="16" t="s">
-        <v>205</v>
+      <c r="K4" s="11" t="s">
+        <v>216</v>
+      </c>
+      <c r="L4" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="M4" s="11" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="5" ht="25.5">
+      <c r="A5" s="11" t="s">
+        <v>218</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>219</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>220</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>221</v>
       </c>
       <c r="E5" s="16">
-        <v>10</v>
+        <v>1.0000000000000001e-15</v>
       </c>
       <c r="F5" s="16">
-        <v>5</v>
-      </c>
-      <c r="G5" s="16" t="s">
-        <v>206</v>
-      </c>
-      <c r="H5" s="16" t="s">
-        <v>47</v>
-      </c>
-      <c r="I5" s="16" t="s">
-        <v>173</v>
-      </c>
-      <c r="J5" s="16" t="s">
-        <v>187</v>
-      </c>
-      <c r="K5" s="16" t="s">
-        <v>207</v>
-      </c>
-      <c r="L5" s="16"/>
-      <c r="M5" s="13" t="s">
-        <v>208</v>
+        <v>1e-10</v>
+      </c>
+      <c r="G5" s="11" t="s">
+        <v>200</v>
+      </c>
+      <c r="H5" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="I5" s="11" t="s">
+        <v>222</v>
+      </c>
+      <c r="J5" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="K5" s="11" t="s">
+        <v>223</v>
       </c>
     </row>
   </sheetData>
@@ -4011,201 +4478,207 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
   <sheetFormatPr baseColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="3" style="9" width="10.28125"/>
-    <col customWidth="1" min="4" max="4" style="9" width="14.421875"/>
-    <col min="5" max="6" style="9" width="10.28125"/>
-    <col customWidth="1" min="7" max="7" style="9" width="14.00390625"/>
-    <col min="8" max="16384" style="9" width="10.28125"/>
+    <col min="1" max="3" style="11" width="10.28125"/>
+    <col customWidth="1" min="4" max="4" style="11" width="14.57421875"/>
+    <col min="5" max="16384" style="11" width="10.28125"/>
   </cols>
   <sheetData>
     <row r="1" ht="14.25">
-      <c r="A1" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="B1" s="9" t="s">
-        <v>144</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>145</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>146</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>147</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>148</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>150</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>151</v>
-      </c>
-      <c r="J1" s="9" t="s">
+      <c r="A1" s="11" t="s">
+        <v>185</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>187</v>
+      </c>
+      <c r="D1" s="11" t="s">
+        <v>188</v>
+      </c>
+      <c r="E1" s="11" t="s">
+        <v>189</v>
+      </c>
+      <c r="F1" s="11" t="s">
+        <v>190</v>
+      </c>
+      <c r="G1" s="11" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1" s="11" t="s">
+        <v>192</v>
+      </c>
+      <c r="I1" s="11" t="s">
+        <v>193</v>
+      </c>
+      <c r="J1" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="K1" s="9" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="2" ht="63.75">
-      <c r="A2" s="9" t="s">
-        <v>209</v>
-      </c>
-      <c r="B2" s="9" t="s">
-        <v>210</v>
-      </c>
-      <c r="C2" s="9" t="s">
-        <v>211</v>
-      </c>
-      <c r="D2" s="9" t="s">
-        <v>212</v>
-      </c>
-      <c r="E2" s="9" t="s">
-        <v>213</v>
-      </c>
-      <c r="F2" s="9" t="s">
-        <v>214</v>
-      </c>
-      <c r="G2" s="9" t="s">
+      <c r="K1" s="11" t="s">
+        <v>194</v>
+      </c>
+      <c r="L1" s="11"/>
+    </row>
+    <row r="2" ht="51">
+      <c r="A2" s="11" t="s">
+        <v>224</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>225</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>226</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>227</v>
+      </c>
+      <c r="E2" s="17">
+        <v>0.012</v>
+      </c>
+      <c r="F2" s="17">
+        <v>0.014999999999999999</v>
+      </c>
+      <c r="G2" s="11" t="s">
+        <v>200</v>
+      </c>
+      <c r="H2" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="I2" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="J2" s="11" t="s">
+        <v>228</v>
+      </c>
+      <c r="K2" s="11" t="s">
+        <v>229</v>
+      </c>
+      <c r="L2" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="M2" s="11" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="3" ht="51">
+      <c r="A3" s="11" t="s">
+        <v>230</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>231</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>232</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>233</v>
+      </c>
+      <c r="E3" s="14">
+        <v>0.14999999999999999</v>
+      </c>
+      <c r="F3" s="14">
+        <v>0.29999999999999999</v>
+      </c>
+      <c r="G3" s="11" t="s">
+        <v>200</v>
+      </c>
+      <c r="H3" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="I3" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="J3" s="11" t="s">
+        <v>228</v>
+      </c>
+      <c r="K3" s="11" t="s">
+        <v>234</v>
+      </c>
+      <c r="L3" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="M3" s="11" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="4" ht="51">
+      <c r="A4" s="11" t="s">
+        <v>236</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>237</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>238</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>239</v>
+      </c>
+      <c r="E4" s="12">
+        <v>0.29999999999999999</v>
+      </c>
+      <c r="F4" s="12">
+        <v>0.90000000000000002</v>
+      </c>
+      <c r="G4" s="11" t="s">
+        <v>200</v>
+      </c>
+      <c r="H4" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="I4" s="11" t="s">
+        <v>240</v>
+      </c>
+      <c r="J4" s="11" t="s">
+        <v>228</v>
+      </c>
+      <c r="K4" s="11" t="s">
+        <v>241</v>
+      </c>
+      <c r="L4" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="M4" s="11" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="5" s="18" customFormat="1" ht="38.25">
+      <c r="A5" s="18" t="s">
+        <v>243</v>
+      </c>
+      <c r="B5" s="18" t="s">
+        <v>244</v>
+      </c>
+      <c r="C5" s="18" t="s">
+        <v>245</v>
+      </c>
+      <c r="D5" s="18" t="s">
+        <v>246</v>
+      </c>
+      <c r="E5" s="18">
+        <v>10</v>
+      </c>
+      <c r="F5" s="18">
+        <v>5</v>
+      </c>
+      <c r="G5" s="18" t="s">
+        <v>247</v>
+      </c>
+      <c r="H5" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="I5" s="18" t="s">
         <v>215</v>
       </c>
-      <c r="H2" s="9">
-        <v>180</v>
-      </c>
-      <c r="I2" s="9">
-        <v>3650</v>
-      </c>
-      <c r="J2" s="9" t="s">
-        <v>216</v>
-      </c>
-      <c r="K2" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="L2" s="9" t="s">
-        <v>159</v>
-      </c>
-      <c r="M2" s="9" t="s">
-        <v>217</v>
-      </c>
-      <c r="N2" s="9" t="s">
-        <v>218</v>
-      </c>
-      <c r="O2" s="9" t="s">
-        <v>219</v>
-      </c>
-      <c r="P2" s="9" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="3" ht="51">
-      <c r="A3" s="9" t="s">
-        <v>221</v>
-      </c>
-      <c r="B3" s="9" t="s">
-        <v>222</v>
-      </c>
-      <c r="C3" s="9" t="s">
-        <v>223</v>
-      </c>
-      <c r="D3" s="9" t="s">
-        <v>224</v>
-      </c>
-      <c r="E3" s="12">
-        <v>0.84999999999999998</v>
-      </c>
-      <c r="F3" s="12">
-        <v>0.98999999999999999</v>
-      </c>
-      <c r="G3" s="9" t="s">
-        <v>158</v>
-      </c>
-      <c r="H3" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="I3" s="9" t="s">
-        <v>159</v>
-      </c>
-      <c r="J3" s="9" t="s">
-        <v>217</v>
-      </c>
-      <c r="K3" s="9" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="4" ht="38.25">
-      <c r="A4" s="9" t="s">
-        <v>226</v>
-      </c>
-      <c r="B4" s="9" t="s">
-        <v>227</v>
-      </c>
-      <c r="C4" s="9" t="s">
+      <c r="J5" s="18" t="s">
         <v>228</v>
       </c>
-      <c r="D4" s="9" t="s">
-        <v>229</v>
-      </c>
-      <c r="E4" s="10">
-        <v>1.5</v>
-      </c>
-      <c r="F4" s="10">
-        <v>2.5</v>
-      </c>
-      <c r="G4" s="9" t="s">
-        <v>158</v>
-      </c>
-      <c r="H4" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="I4" s="9" t="s">
-        <v>230</v>
-      </c>
-      <c r="J4" s="9" t="s">
-        <v>217</v>
-      </c>
-      <c r="K4" s="9" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="5" ht="51">
-      <c r="A5" s="9" t="s">
-        <v>232</v>
-      </c>
-      <c r="B5" s="9" t="s">
-        <v>233</v>
-      </c>
-      <c r="C5" s="9" t="s">
-        <v>234</v>
-      </c>
-      <c r="D5" s="9" t="s">
-        <v>235</v>
-      </c>
-      <c r="E5" s="10">
-        <v>0.69999999999999996</v>
-      </c>
-      <c r="F5" s="12">
-        <v>1.05</v>
-      </c>
-      <c r="G5" s="9" t="s">
-        <v>158</v>
-      </c>
-      <c r="H5" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="I5" s="9" t="s">
-        <v>236</v>
-      </c>
-      <c r="J5" s="9" t="s">
-        <v>217</v>
-      </c>
-      <c r="K5" s="9" t="s">
-        <v>237</v>
+      <c r="K5" s="18" t="s">
+        <v>248</v>
+      </c>
+      <c r="L5" s="18"/>
+      <c r="M5" s="15" t="s">
+        <v>249</v>
       </c>
     </row>
   </sheetData>
@@ -4220,184 +4693,201 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
   <sheetFormatPr baseColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="3" style="9" width="10.28125"/>
-    <col customWidth="1" min="4" max="4" style="9" width="18.28125"/>
-    <col min="5" max="16384" style="9" width="10.28125"/>
+    <col min="1" max="3" style="11" width="10.28125"/>
+    <col customWidth="1" min="4" max="4" style="11" width="14.421875"/>
+    <col min="5" max="6" style="11" width="10.28125"/>
+    <col customWidth="1" min="7" max="7" style="11" width="14.00390625"/>
+    <col min="8" max="16384" style="11" width="10.28125"/>
   </cols>
   <sheetData>
     <row r="1" ht="14.25">
-      <c r="A1" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="B1" s="9" t="s">
-        <v>144</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>145</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>146</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>147</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>148</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>150</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>151</v>
-      </c>
-      <c r="J1" s="9" t="s">
+      <c r="A1" s="11" t="s">
+        <v>185</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>187</v>
+      </c>
+      <c r="D1" s="11" t="s">
+        <v>188</v>
+      </c>
+      <c r="E1" s="11" t="s">
+        <v>189</v>
+      </c>
+      <c r="F1" s="11" t="s">
+        <v>190</v>
+      </c>
+      <c r="G1" s="11" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1" s="11" t="s">
+        <v>192</v>
+      </c>
+      <c r="I1" s="11" t="s">
+        <v>193</v>
+      </c>
+      <c r="J1" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="K1" s="9" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="2" ht="38.25">
-      <c r="A2" s="9" t="s">
-        <v>238</v>
-      </c>
-      <c r="B2" s="9" t="s">
-        <v>239</v>
-      </c>
-      <c r="C2" s="9" t="s">
-        <v>240</v>
-      </c>
-      <c r="D2" s="9" t="s">
-        <v>241</v>
-      </c>
-      <c r="E2" s="12">
-        <v>0.25</v>
-      </c>
-      <c r="F2" s="12">
-        <v>0.90000000000000002</v>
-      </c>
-      <c r="G2" s="9" t="s">
-        <v>158</v>
-      </c>
-      <c r="H2" s="9" t="s">
+      <c r="K1" s="11" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="2" ht="63.75">
+      <c r="A2" s="11" t="s">
+        <v>250</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>251</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>252</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>253</v>
+      </c>
+      <c r="E2" s="11" t="s">
+        <v>254</v>
+      </c>
+      <c r="F2" s="11" t="s">
+        <v>255</v>
+      </c>
+      <c r="G2" s="11" t="s">
+        <v>256</v>
+      </c>
+      <c r="H2" s="11">
+        <v>180</v>
+      </c>
+      <c r="I2" s="11">
+        <v>3650</v>
+      </c>
+      <c r="J2" s="11" t="s">
+        <v>257</v>
+      </c>
+      <c r="K2" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="I2" s="9" t="s">
-        <v>199</v>
-      </c>
-      <c r="J2" s="9" t="s">
-        <v>242</v>
-      </c>
-      <c r="K2" s="9" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="3" ht="63.75">
-      <c r="A3" s="9" t="s">
-        <v>244</v>
-      </c>
-      <c r="B3" s="9" t="s">
-        <v>245</v>
-      </c>
-      <c r="C3" s="9" t="s">
-        <v>246</v>
-      </c>
-      <c r="D3" s="9" t="s">
-        <v>247</v>
-      </c>
-      <c r="E3" s="10">
+      <c r="L2" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="M2" s="11" t="s">
+        <v>258</v>
+      </c>
+      <c r="N2" s="11" t="s">
+        <v>259</v>
+      </c>
+      <c r="O2" s="11" t="s">
+        <v>260</v>
+      </c>
+      <c r="P2" s="11" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="3" ht="51">
+      <c r="A3" s="11" t="s">
+        <v>262</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>263</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>264</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>265</v>
+      </c>
+      <c r="E3" s="14">
+        <v>0.84999999999999998</v>
+      </c>
+      <c r="F3" s="14">
+        <v>0.98999999999999999</v>
+      </c>
+      <c r="G3" s="11" t="s">
+        <v>200</v>
+      </c>
+      <c r="H3" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="I3" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="J3" s="11" t="s">
+        <v>258</v>
+      </c>
+      <c r="K3" s="11" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="4" ht="38.25">
+      <c r="A4" s="11" t="s">
+        <v>267</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>268</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>269</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>270</v>
+      </c>
+      <c r="E4" s="12">
         <v>1.5</v>
       </c>
-      <c r="F3" s="17">
-        <v>10</v>
-      </c>
-      <c r="G3" s="9" t="s">
-        <v>158</v>
-      </c>
-      <c r="H3" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="I3" s="9" t="s">
-        <v>173</v>
-      </c>
-      <c r="J3" s="9" t="s">
-        <v>242</v>
-      </c>
-      <c r="K3" s="9" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="4" ht="25.5">
-      <c r="A4" s="9" t="s">
-        <v>249</v>
-      </c>
-      <c r="B4" s="9" t="s">
-        <v>250</v>
-      </c>
-      <c r="C4" s="9" t="s">
-        <v>251</v>
-      </c>
-      <c r="D4" s="9" t="s">
-        <v>252</v>
-      </c>
-      <c r="E4" s="12">
-        <v>0.01</v>
-      </c>
       <c r="F4" s="12">
-        <v>0.10000000000000001</v>
-      </c>
-      <c r="G4" s="9" t="s">
-        <v>253</v>
-      </c>
-      <c r="H4" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="I4" s="9" t="s">
-        <v>181</v>
-      </c>
-      <c r="J4" s="9" t="s">
-        <v>242</v>
-      </c>
-      <c r="K4" s="9" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="5" ht="38.25">
-      <c r="A5" s="9" t="s">
-        <v>255</v>
-      </c>
-      <c r="B5" s="9" t="s">
-        <v>256</v>
-      </c>
-      <c r="C5" s="9" t="s">
-        <v>257</v>
-      </c>
-      <c r="D5" s="9" t="s">
+        <v>2.5</v>
+      </c>
+      <c r="G4" s="11" t="s">
+        <v>200</v>
+      </c>
+      <c r="H4" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="I4" s="11" t="s">
+        <v>271</v>
+      </c>
+      <c r="J4" s="11" t="s">
         <v>258</v>
       </c>
+      <c r="K4" s="11" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="5" ht="51">
+      <c r="A5" s="11" t="s">
+        <v>273</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>274</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>275</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>276</v>
+      </c>
       <c r="E5" s="12">
-        <v>0.29999999999999999</v>
-      </c>
-      <c r="F5" s="12">
-        <v>0.80000000000000004</v>
-      </c>
-      <c r="G5" s="9" t="s">
-        <v>158</v>
-      </c>
-      <c r="H5" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="I5" s="9" t="s">
-        <v>159</v>
-      </c>
-      <c r="J5" s="9" t="s">
-        <v>242</v>
-      </c>
-      <c r="K5" s="9" t="s">
-        <v>259</v>
+        <v>0.69999999999999996</v>
+      </c>
+      <c r="F5" s="14">
+        <v>1.05</v>
+      </c>
+      <c r="G5" s="11" t="s">
+        <v>200</v>
+      </c>
+      <c r="H5" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="I5" s="11" t="s">
+        <v>277</v>
+      </c>
+      <c r="J5" s="11" t="s">
+        <v>258</v>
+      </c>
+      <c r="K5" s="11" t="s">
+        <v>278</v>
       </c>
     </row>
   </sheetData>
@@ -4410,188 +4900,186 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" style="9" width="9.140625"/>
-    <col customWidth="1" min="2" max="2" style="9" width="11.57421875"/>
-    <col customWidth="1" min="3" max="3" style="9" width="12.421875"/>
-    <col customWidth="1" min="4" max="4" style="9" width="14.421875"/>
-    <col min="5" max="16384" style="9" width="9.140625"/>
+    <col min="1" max="3" style="11" width="10.28125"/>
+    <col customWidth="1" min="4" max="4" style="11" width="18.28125"/>
+    <col min="5" max="16384" style="11" width="10.28125"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="B1" s="9" t="s">
-        <v>144</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>145</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>146</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>147</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>148</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>150</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>151</v>
-      </c>
-      <c r="J1" s="9" t="s">
+    <row r="1" ht="14.25">
+      <c r="A1" s="11" t="s">
+        <v>185</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>187</v>
+      </c>
+      <c r="D1" s="11" t="s">
+        <v>188</v>
+      </c>
+      <c r="E1" s="11" t="s">
+        <v>189</v>
+      </c>
+      <c r="F1" s="11" t="s">
+        <v>190</v>
+      </c>
+      <c r="G1" s="11" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1" s="11" t="s">
+        <v>192</v>
+      </c>
+      <c r="I1" s="11" t="s">
+        <v>193</v>
+      </c>
+      <c r="J1" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="K1" s="9" t="s">
-        <v>152</v>
+      <c r="K1" s="11" t="s">
+        <v>194</v>
       </c>
     </row>
     <row r="2" ht="38.25">
-      <c r="A2" s="9" t="s">
-        <v>260</v>
-      </c>
-      <c r="B2" s="9" t="s">
-        <v>261</v>
-      </c>
-      <c r="C2" s="9" t="s">
-        <v>262</v>
-      </c>
-      <c r="D2" s="9" t="s">
-        <v>263</v>
-      </c>
-      <c r="E2" s="9">
+      <c r="A2" s="11" t="s">
+        <v>279</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>280</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>281</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>282</v>
+      </c>
+      <c r="E2" s="14">
+        <v>0.25</v>
+      </c>
+      <c r="F2" s="14">
+        <v>0.90000000000000002</v>
+      </c>
+      <c r="G2" s="11" t="s">
+        <v>200</v>
+      </c>
+      <c r="H2" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="I2" s="11" t="s">
+        <v>240</v>
+      </c>
+      <c r="J2" s="11" t="s">
+        <v>283</v>
+      </c>
+      <c r="K2" s="11" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="3" ht="63.75">
+      <c r="A3" s="11" t="s">
+        <v>285</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>286</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>287</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>288</v>
+      </c>
+      <c r="E3" s="12">
+        <v>1.5</v>
+      </c>
+      <c r="F3" s="19">
+        <v>10</v>
+      </c>
+      <c r="G3" s="11" t="s">
+        <v>200</v>
+      </c>
+      <c r="H3" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="I3" s="11" t="s">
+        <v>215</v>
+      </c>
+      <c r="J3" s="11" t="s">
+        <v>283</v>
+      </c>
+      <c r="K3" s="11" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="4" ht="25.5">
+      <c r="A4" s="11" t="s">
+        <v>290</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>291</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>292</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>293</v>
+      </c>
+      <c r="E4" s="14">
+        <v>0.01</v>
+      </c>
+      <c r="F4" s="14">
         <v>0.10000000000000001</v>
       </c>
-      <c r="F2" s="9">
-        <v>0.94999999999999996</v>
-      </c>
-      <c r="G2" s="9" t="s">
-        <v>158</v>
-      </c>
-      <c r="H2" s="9" t="s">
+      <c r="G4" s="11" t="s">
+        <v>294</v>
+      </c>
+      <c r="H4" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="I4" s="11" t="s">
+        <v>222</v>
+      </c>
+      <c r="J4" s="11" t="s">
+        <v>283</v>
+      </c>
+      <c r="K4" s="11" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="5" ht="38.25">
+      <c r="A5" s="11" t="s">
+        <v>296</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>297</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>298</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>299</v>
+      </c>
+      <c r="E5" s="14">
+        <v>0.29999999999999999</v>
+      </c>
+      <c r="F5" s="14">
+        <v>0.80000000000000004</v>
+      </c>
+      <c r="G5" s="11" t="s">
+        <v>200</v>
+      </c>
+      <c r="H5" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="I2" s="9" t="s">
-        <v>159</v>
-      </c>
-      <c r="J2" s="9" t="s">
-        <v>264</v>
-      </c>
-      <c r="K2" s="9" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="3" ht="51">
-      <c r="A3" s="9" t="s">
-        <v>266</v>
-      </c>
-      <c r="B3" s="9" t="s">
-        <v>267</v>
-      </c>
-      <c r="C3" s="9" t="s">
-        <v>268</v>
-      </c>
-      <c r="D3" s="9" t="s">
-        <v>269</v>
-      </c>
-      <c r="E3" s="9">
-        <v>100</v>
-      </c>
-      <c r="F3" s="9">
-        <v>1</v>
-      </c>
-      <c r="G3" s="9" t="s">
-        <v>270</v>
-      </c>
-      <c r="H3" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="I3" s="9" t="s">
-        <v>199</v>
-      </c>
-      <c r="J3" s="9" t="s">
-        <v>264</v>
-      </c>
-      <c r="K3" s="9" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="4" ht="51">
-      <c r="A4" s="9" t="s">
-        <v>272</v>
-      </c>
-      <c r="B4" s="9" t="s">
-        <v>273</v>
-      </c>
-      <c r="C4" s="9" t="s">
-        <v>274</v>
-      </c>
-      <c r="D4" s="9" t="s">
-        <v>275</v>
-      </c>
-      <c r="E4" s="9">
-        <v>0.10000000000000001</v>
-      </c>
-      <c r="F4" s="9">
-        <v>0.001</v>
-      </c>
-      <c r="G4" s="9" t="s">
-        <v>158</v>
-      </c>
-      <c r="H4" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="I4" s="9" t="s">
-        <v>159</v>
-      </c>
-      <c r="J4" s="9" t="s">
-        <v>264</v>
-      </c>
-      <c r="K4" s="9" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="5" ht="51">
-      <c r="A5" s="9" t="s">
-        <v>277</v>
-      </c>
-      <c r="B5" s="9" t="s">
-        <v>278</v>
-      </c>
-      <c r="C5" s="9" t="s">
-        <v>279</v>
-      </c>
-      <c r="D5" s="9" t="s">
-        <v>280</v>
-      </c>
-      <c r="E5" s="9">
-        <v>0.69999999999999996</v>
-      </c>
-      <c r="F5" s="9">
-        <v>0.98999999999999999</v>
-      </c>
-      <c r="G5" s="9" t="s">
-        <v>158</v>
-      </c>
-      <c r="H5" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="I5" s="9" t="s">
-        <v>281</v>
-      </c>
-      <c r="J5" s="9" t="s">
-        <v>264</v>
-      </c>
-      <c r="K5" s="9" t="s">
-        <v>282</v>
+      <c r="I5" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="J5" s="11" t="s">
+        <v>283</v>
+      </c>
+      <c r="K5" s="11" t="s">
+        <v>300</v>
       </c>
     </row>
   </sheetData>
@@ -4606,192 +5094,186 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="3" style="9" width="9.140625"/>
-    <col customWidth="1" min="4" max="4" style="9" width="14.28125"/>
-    <col min="5" max="5" style="9" width="9.140625"/>
-    <col customWidth="1" min="6" max="6" style="9" width="13.7109375"/>
-    <col min="7" max="16384" style="9" width="9.140625"/>
+    <col min="1" max="1" style="11" width="9.140625"/>
+    <col customWidth="1" min="2" max="2" style="11" width="11.57421875"/>
+    <col customWidth="1" min="3" max="3" style="11" width="12.421875"/>
+    <col customWidth="1" min="4" max="4" style="11" width="14.421875"/>
+    <col min="5" max="16384" style="11" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="9" t="s">
-        <v>143</v>
-      </c>
-      <c r="B1" s="9" t="s">
-        <v>144</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>145</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>146</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>147</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>148</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>150</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>151</v>
-      </c>
-      <c r="J1" s="9" t="s">
+      <c r="A1" s="11" t="s">
+        <v>185</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>187</v>
+      </c>
+      <c r="D1" s="11" t="s">
+        <v>188</v>
+      </c>
+      <c r="E1" s="11" t="s">
+        <v>189</v>
+      </c>
+      <c r="F1" s="11" t="s">
+        <v>190</v>
+      </c>
+      <c r="G1" s="11" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1" s="11" t="s">
+        <v>192</v>
+      </c>
+      <c r="I1" s="11" t="s">
+        <v>193</v>
+      </c>
+      <c r="J1" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="K1" s="9" t="s">
-        <v>152</v>
+      <c r="K1" s="11" t="s">
+        <v>194</v>
       </c>
     </row>
     <row r="2" ht="38.25">
-      <c r="A2" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" s="9" t="s">
-        <v>283</v>
-      </c>
-      <c r="C2" s="9" t="s">
-        <v>284</v>
-      </c>
-      <c r="D2" s="9" t="s">
-        <v>285</v>
-      </c>
-      <c r="E2" s="9">
-        <v>10000</v>
-      </c>
-      <c r="F2" s="9">
+      <c r="A2" s="11" t="s">
+        <v>301</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>302</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>303</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>304</v>
+      </c>
+      <c r="E2" s="11">
+        <v>0.10000000000000001</v>
+      </c>
+      <c r="F2" s="11">
+        <v>0.94999999999999996</v>
+      </c>
+      <c r="G2" s="11" t="s">
+        <v>200</v>
+      </c>
+      <c r="H2" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="I2" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="J2" s="11" t="s">
+        <v>305</v>
+      </c>
+      <c r="K2" s="11" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="3" ht="51">
+      <c r="A3" s="11" t="s">
+        <v>307</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>308</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>309</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>310</v>
+      </c>
+      <c r="E3" s="11">
         <v>100</v>
       </c>
-      <c r="G2" s="9" t="s">
-        <v>286</v>
-      </c>
-      <c r="H2" s="9" t="s">
+      <c r="F3" s="11">
+        <v>1</v>
+      </c>
+      <c r="G3" s="11" t="s">
+        <v>311</v>
+      </c>
+      <c r="H3" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="I3" s="11" t="s">
+        <v>240</v>
+      </c>
+      <c r="J3" s="11" t="s">
+        <v>305</v>
+      </c>
+      <c r="K3" s="11" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="4" ht="51">
+      <c r="A4" s="11" t="s">
+        <v>313</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>314</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>315</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>316</v>
+      </c>
+      <c r="E4" s="11">
+        <v>0.10000000000000001</v>
+      </c>
+      <c r="F4" s="11">
+        <v>0.001</v>
+      </c>
+      <c r="G4" s="11" t="s">
+        <v>200</v>
+      </c>
+      <c r="H4" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="I2" s="9" t="s">
-        <v>159</v>
-      </c>
-      <c r="J2" s="9" t="s">
-        <v>106</v>
-      </c>
-      <c r="K2" s="9" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="3" ht="51">
-      <c r="A3" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" s="9" t="s">
-        <v>288</v>
-      </c>
-      <c r="C3" s="9" t="s">
-        <v>289</v>
-      </c>
-      <c r="D3" s="9" t="s">
-        <v>290</v>
-      </c>
-      <c r="E3" s="9">
-        <v>100</v>
-      </c>
-      <c r="F3" s="9">
-        <v>10</v>
-      </c>
-      <c r="G3" s="9" t="s">
-        <v>291</v>
-      </c>
-      <c r="H3" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="I3" s="9" t="s">
-        <v>159</v>
-      </c>
-      <c r="J3" s="9" t="s">
-        <v>106</v>
-      </c>
-      <c r="K3" s="9" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="4" ht="51">
-      <c r="A4" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="B4" s="9" t="s">
-        <v>293</v>
-      </c>
-      <c r="C4" s="9" t="s">
-        <v>294</v>
-      </c>
-      <c r="D4" s="9" t="s">
-        <v>295</v>
-      </c>
-      <c r="E4" s="9" t="s">
-        <v>296</v>
-      </c>
-      <c r="F4" s="9" t="s">
-        <v>297</v>
-      </c>
-      <c r="G4" s="9">
-        <v>10</v>
-      </c>
-      <c r="H4" s="9">
-        <v>2</v>
-      </c>
-      <c r="I4" s="9" t="s">
-        <v>298</v>
-      </c>
-      <c r="J4" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="K4" s="9" t="s">
-        <v>173</v>
-      </c>
-      <c r="L4" s="9" t="s">
-        <v>106</v>
-      </c>
-      <c r="M4" s="9" t="s">
-        <v>299</v>
+      <c r="I4" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="J4" s="11" t="s">
+        <v>305</v>
+      </c>
+      <c r="K4" s="11" t="s">
+        <v>317</v>
       </c>
     </row>
     <row r="5" ht="51">
-      <c r="A5" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="B5" s="9" t="s">
-        <v>300</v>
-      </c>
-      <c r="C5" s="9" t="s">
-        <v>301</v>
-      </c>
-      <c r="D5" s="9" t="s">
-        <v>302</v>
-      </c>
-      <c r="E5" s="9">
-        <v>0.80000000000000004</v>
-      </c>
-      <c r="F5" s="9">
-        <v>0.59999999999999998</v>
-      </c>
-      <c r="G5" s="9" t="s">
-        <v>158</v>
-      </c>
-      <c r="H5" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="I5" s="9" t="s">
-        <v>181</v>
-      </c>
-      <c r="J5" s="9" t="s">
-        <v>106</v>
-      </c>
-      <c r="K5" s="9" t="s">
-        <v>303</v>
+      <c r="A5" s="11" t="s">
+        <v>318</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>319</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>321</v>
+      </c>
+      <c r="E5" s="11">
+        <v>0.69999999999999996</v>
+      </c>
+      <c r="F5" s="11">
+        <v>0.98999999999999999</v>
+      </c>
+      <c r="G5" s="11" t="s">
+        <v>200</v>
+      </c>
+      <c r="H5" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="I5" s="11" t="s">
+        <v>322</v>
+      </c>
+      <c r="J5" s="11" t="s">
+        <v>305</v>
+      </c>
+      <c r="K5" s="11" t="s">
+        <v>323</v>
       </c>
     </row>
   </sheetData>
@@ -4806,265 +5288,192 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" min="1" max="1" style="9" width="12.57421875"/>
-    <col customWidth="1" min="2" max="2" style="9" width="13.8515625"/>
-    <col min="3" max="4" style="9" width="9.140625"/>
-    <col customWidth="1" min="5" max="5" style="9" width="12.8515625"/>
-    <col customWidth="1" min="6" max="6" style="9" width="12.421875"/>
-    <col min="7" max="16384" style="9" width="9.140625"/>
+    <col min="1" max="3" style="11" width="9.140625"/>
+    <col customWidth="1" min="4" max="4" style="11" width="14.28125"/>
+    <col min="5" max="5" style="11" width="9.140625"/>
+    <col customWidth="1" min="6" max="6" style="11" width="13.7109375"/>
+    <col min="7" max="16384" style="11" width="9.140625"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28.5">
-      <c r="A1" s="9" t="s">
-        <v>304</v>
-      </c>
-      <c r="B1" s="9" t="s">
-        <v>305</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>306</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>307</v>
-      </c>
-      <c r="F1" s="9" t="s">
+    <row r="1">
+      <c r="A1" s="11" t="s">
+        <v>185</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>187</v>
+      </c>
+      <c r="D1" s="11" t="s">
+        <v>188</v>
+      </c>
+      <c r="E1" s="11" t="s">
+        <v>189</v>
+      </c>
+      <c r="F1" s="11" t="s">
+        <v>190</v>
+      </c>
+      <c r="G1" s="11" t="s">
+        <v>191</v>
+      </c>
+      <c r="H1" s="11" t="s">
+        <v>192</v>
+      </c>
+      <c r="I1" s="11" t="s">
+        <v>193</v>
+      </c>
+      <c r="J1" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="9" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="2" ht="25.5">
-      <c r="A2" s="9" t="s">
-        <v>308</v>
-      </c>
-      <c r="B2" s="9" t="s">
-        <v>309</v>
-      </c>
-      <c r="C2" s="14">
-        <v>200000000000</v>
-      </c>
-      <c r="D2" s="9" t="s">
-        <v>310</v>
-      </c>
-      <c r="E2" s="9" t="s">
-        <v>311</v>
-      </c>
-      <c r="F2" s="9" t="s">
-        <v>160</v>
-      </c>
-      <c r="G2" s="9" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" ht="42.75">
-      <c r="A3" s="9" t="s">
-        <v>312</v>
-      </c>
-      <c r="B3" s="9" t="s">
-        <v>313</v>
-      </c>
-      <c r="C3" s="9">
-        <v>5500</v>
-      </c>
-      <c r="D3" s="9" t="s">
-        <v>310</v>
-      </c>
-      <c r="E3" s="9" t="s">
-        <v>314</v>
-      </c>
-      <c r="F3" s="9" t="s">
-        <v>160</v>
-      </c>
-      <c r="G3" s="9" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" ht="28.5">
-      <c r="A4" s="9" t="s">
-        <v>315</v>
-      </c>
-      <c r="B4" s="9" t="s">
-        <v>316</v>
-      </c>
-      <c r="C4" s="9">
-        <v>24</v>
-      </c>
-      <c r="D4" s="9" t="s">
-        <v>310</v>
-      </c>
-      <c r="E4" s="9" t="s">
-        <v>317</v>
-      </c>
-      <c r="F4" s="9" t="s">
-        <v>160</v>
-      </c>
-      <c r="G4" s="9" t="s">
+      <c r="K1" s="11" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="2" ht="38.25">
+      <c r="A2" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>324</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>325</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>326</v>
+      </c>
+      <c r="E2" s="11">
+        <v>10000</v>
+      </c>
+      <c r="F2" s="11">
+        <v>100</v>
+      </c>
+      <c r="G2" s="11" t="s">
+        <v>327</v>
+      </c>
+      <c r="H2" s="11" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="5" ht="25.5">
-      <c r="A5" s="9" t="s">
-        <v>318</v>
-      </c>
-      <c r="B5" s="9" t="s">
-        <v>319</v>
-      </c>
-      <c r="C5" s="14">
-        <v>4540000000</v>
-      </c>
-      <c r="D5" s="9" t="s">
-        <v>298</v>
-      </c>
-      <c r="E5" s="9" t="s">
-        <v>320</v>
-      </c>
-      <c r="F5" s="9" t="s">
-        <v>321</v>
-      </c>
-      <c r="G5" s="9" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" ht="28.5">
-      <c r="A6" s="9" t="s">
-        <v>322</v>
-      </c>
-      <c r="B6" s="9" t="s">
-        <v>323</v>
-      </c>
-      <c r="C6" s="14">
-        <v>500000000</v>
-      </c>
-      <c r="D6" s="9" t="s">
-        <v>298</v>
-      </c>
-      <c r="E6" s="9" t="s">
-        <v>324</v>
-      </c>
-      <c r="F6" s="9" t="s">
-        <v>321</v>
-      </c>
-      <c r="G6" s="9" t="s">
+      <c r="I2" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="J2" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="K2" s="11" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="3" ht="51">
+      <c r="A3" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>329</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>330</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>331</v>
+      </c>
+      <c r="E3" s="11">
+        <v>100</v>
+      </c>
+      <c r="F3" s="11">
+        <v>10</v>
+      </c>
+      <c r="G3" s="11" t="s">
+        <v>332</v>
+      </c>
+      <c r="H3" s="11" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="7" ht="28.5">
-      <c r="A7" s="9" t="s">
-        <v>325</v>
-      </c>
-      <c r="B7" s="9" t="s">
-        <v>326</v>
-      </c>
-      <c r="C7" s="9">
-        <v>230</v>
-      </c>
-      <c r="D7" s="9" t="s">
-        <v>327</v>
-      </c>
-      <c r="E7" s="9" t="s">
-        <v>328</v>
-      </c>
-      <c r="F7" s="9" t="s">
-        <v>329</v>
-      </c>
-      <c r="G7" s="9" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" ht="28.5">
-      <c r="A8" s="9" t="s">
-        <v>330</v>
-      </c>
-      <c r="B8" s="9" t="s">
-        <v>331</v>
-      </c>
-      <c r="C8" s="9">
-        <v>0.01</v>
-      </c>
-      <c r="D8" s="9" t="s">
-        <v>158</v>
-      </c>
-      <c r="E8" s="9" t="s">
-        <v>332</v>
-      </c>
-      <c r="F8" s="9" t="s">
-        <v>329</v>
-      </c>
-      <c r="G8" s="9" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="9" ht="25.5">
-      <c r="A9" s="9" t="s">
+      <c r="I3" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="J3" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="K3" s="11" t="s">
         <v>333</v>
       </c>
-      <c r="B9" s="9" t="s">
+    </row>
+    <row r="4" ht="51">
+      <c r="A4" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" s="11" t="s">
         <v>334</v>
       </c>
-      <c r="C9" s="9">
-        <v>1366</v>
-      </c>
-      <c r="D9" s="9" t="s">
+      <c r="C4" s="11" t="s">
         <v>335</v>
       </c>
-      <c r="E9" s="9" t="s">
+      <c r="D4" s="11" t="s">
         <v>336</v>
       </c>
-      <c r="F9" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="G9" s="9" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="10" ht="25.5">
-      <c r="A10" s="9" t="s">
+      <c r="E4" s="11" t="s">
         <v>337</v>
       </c>
-      <c r="B10" s="9" t="s">
+      <c r="F4" s="11" t="s">
         <v>338</v>
       </c>
-      <c r="C10" s="9">
-        <v>587</v>
-      </c>
-      <c r="D10" s="9" t="s">
-        <v>335</v>
-      </c>
-      <c r="E10" s="9" t="s">
+      <c r="G4" s="11">
+        <v>10</v>
+      </c>
+      <c r="H4" s="11">
+        <v>2</v>
+      </c>
+      <c r="I4" s="11" t="s">
         <v>339</v>
       </c>
-      <c r="F10" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="G10" s="9" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="11" ht="25.5">
-      <c r="A11" s="9" t="s">
+      <c r="J4" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="K4" s="11" t="s">
+        <v>215</v>
+      </c>
+      <c r="L4" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="M4" s="11" t="s">
         <v>340</v>
       </c>
-      <c r="B11" s="9" t="s">
+    </row>
+    <row r="5" ht="51">
+      <c r="A5" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="B5" s="11" t="s">
         <v>341</v>
       </c>
-      <c r="C11" s="9">
-        <v>101.325</v>
-      </c>
-      <c r="D11" s="9" t="s">
+      <c r="C5" s="11" t="s">
         <v>342</v>
       </c>
-      <c r="E11" s="9" t="s">
-        <v>336</v>
-      </c>
-      <c r="F11" s="9" t="s">
-        <v>329</v>
-      </c>
-      <c r="G11" s="9" t="s">
-        <v>12</v>
+      <c r="D5" s="11" t="s">
+        <v>343</v>
+      </c>
+      <c r="E5" s="11">
+        <v>0.80000000000000004</v>
+      </c>
+      <c r="F5" s="11">
+        <v>0.59999999999999998</v>
+      </c>
+      <c r="G5" s="11" t="s">
+        <v>200</v>
+      </c>
+      <c r="H5" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="I5" s="11" t="s">
+        <v>222</v>
+      </c>
+      <c r="J5" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="K5" s="11" t="s">
+        <v>344</v>
       </c>
     </row>
   </sheetData>

--- a/tasklist/生命・生態系関連.xlsx
+++ b/tasklist/生命・生態系関連.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="1"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="核心課題" sheetId="1" state="visible" r:id="rId1"/>
@@ -232,7 +232,9 @@
     <t>26.06.21</t>
   </si>
   <si>
-    <t xml:space="preserve">理性は論理構造として転送可能だが、感情との統合が課題 </t>
+    <t xml:space="preserve">理性は論理構造として転送可能だが、感情との統合が課題 
+minduploadとの関連
+更にDNA管理(HZ)との絡み</t>
   </si>
   <si>
     <t>BIO-509</t>
@@ -1624,7 +1626,7 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="22">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -1645,9 +1647,6 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
       <protection hidden="0" locked="1"/>
     </xf>
@@ -1657,9 +1656,6 @@
     <xf fontId="0" fillId="2" borderId="0" numFmtId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
       <protection hidden="0" locked="1"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf fontId="5" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -2165,7 +2161,9 @@
     <col customWidth="1" min="2" max="2" style="1" width="12.421875"/>
     <col customWidth="1" min="3" max="3" style="1" width="14.140625"/>
     <col customWidth="1" min="4" max="4" style="1" width="16.28125"/>
-    <col min="5" max="16384" style="1" width="10.28125"/>
+    <col min="5" max="9" style="1" width="10.28125"/>
+    <col customWidth="1" min="10" max="10" style="1" width="31.28125"/>
+    <col min="11" max="16384" style="1" width="10.28125"/>
   </cols>
   <sheetData>
     <row r="1" ht="28.5">
@@ -2458,7 +2456,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="12" ht="42.75">
+    <row r="12" ht="57">
       <c r="A12" s="1" t="s">
         <v>60</v>
       </c>
@@ -2486,7 +2484,7 @@
       <c r="I12" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="J12" s="7" t="s">
+      <c r="J12" s="3" t="s">
         <v>65</v>
       </c>
     </row>
@@ -2809,13 +2807,13 @@
       </c>
     </row>
     <row r="25" ht="28.5">
-      <c r="A25" s="8" t="s">
+      <c r="A25" s="7" t="s">
         <v>118</v>
       </c>
-      <c r="B25" s="8" t="s">
+      <c r="B25" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="C25" s="8"/>
+      <c r="C25" s="7"/>
       <c r="D25" s="1"/>
       <c r="H25" s="1" t="s">
         <v>13</v>
@@ -2824,45 +2822,45 @@
         <v>120</v>
       </c>
     </row>
-    <row r="26" s="9" customFormat="1" ht="28.5">
-      <c r="A26" s="10" t="s">
+    <row r="26" s="8" customFormat="1" ht="28.5">
+      <c r="A26" s="9" t="s">
         <v>121</v>
       </c>
-      <c r="B26" s="10" t="s">
+      <c r="B26" s="9" t="s">
         <v>122</v>
       </c>
-      <c r="C26" s="10"/>
-      <c r="D26" s="9"/>
+      <c r="C26" s="9"/>
+      <c r="D26" s="8"/>
     </row>
     <row r="27" ht="42.75">
-      <c r="A27" s="8" t="s">
+      <c r="A27" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="B27" s="8" t="s">
+      <c r="B27" s="7" t="s">
         <v>124</v>
       </c>
-      <c r="C27" s="8"/>
+      <c r="C27" s="7"/>
     </row>
     <row r="28" ht="42.75">
-      <c r="A28" s="8" t="s">
+      <c r="A28" s="7" t="s">
         <v>125</v>
       </c>
-      <c r="B28" s="8" t="s">
+      <c r="B28" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="C28" s="8"/>
+      <c r="C28" s="7"/>
       <c r="I28" s="1" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="29" ht="28.5">
-      <c r="A29" s="8" t="s">
+      <c r="A29" s="7" t="s">
         <v>127</v>
       </c>
-      <c r="B29" s="8" t="s">
+      <c r="B29" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="C29" s="8"/>
+      <c r="C29" s="7"/>
     </row>
   </sheetData>
   <printOptions headings="0" gridLines="0"/>
@@ -2876,264 +2874,264 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" min="1" max="1" style="12" width="12.57421875"/>
-    <col customWidth="1" min="2" max="2" style="12" width="13.8515625"/>
-    <col min="3" max="4" style="12" width="9.140625"/>
-    <col customWidth="1" min="5" max="5" style="12" width="12.8515625"/>
-    <col customWidth="1" min="6" max="6" style="12" width="12.421875"/>
-    <col min="7" max="16384" style="12" width="9.140625"/>
+    <col customWidth="1" min="1" max="1" style="10" width="12.57421875"/>
+    <col customWidth="1" min="2" max="2" style="10" width="13.8515625"/>
+    <col min="3" max="4" style="10" width="9.140625"/>
+    <col customWidth="1" min="5" max="5" style="10" width="12.8515625"/>
+    <col customWidth="1" min="6" max="6" style="10" width="12.421875"/>
+    <col min="7" max="16384" style="10" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1" ht="28.5">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="10" t="s">
         <v>354</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="10" t="s">
         <v>355</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="10" t="s">
         <v>356</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="10" t="s">
         <v>197</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="10" t="s">
         <v>357</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="G1" s="10" t="s">
         <v>198</v>
       </c>
     </row>
     <row r="2" ht="25.5">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="10" t="s">
         <v>358</v>
       </c>
-      <c r="B2" s="12" t="s">
+      <c r="B2" s="10" t="s">
         <v>359</v>
       </c>
-      <c r="C2" s="17">
+      <c r="C2" s="15">
         <v>200000000000</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="D2" s="10" t="s">
         <v>360</v>
       </c>
-      <c r="E2" s="12" t="s">
+      <c r="E2" s="10" t="s">
         <v>361</v>
       </c>
-      <c r="F2" s="12" t="s">
+      <c r="F2" s="10" t="s">
         <v>208</v>
       </c>
-      <c r="G2" s="12" t="s">
+      <c r="G2" s="10" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="3" ht="42.75">
-      <c r="A3" s="12" t="s">
+      <c r="A3" s="10" t="s">
         <v>362</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="B3" s="10" t="s">
         <v>363</v>
       </c>
-      <c r="C3" s="12">
+      <c r="C3" s="10">
         <v>5500</v>
       </c>
-      <c r="D3" s="12" t="s">
+      <c r="D3" s="10" t="s">
         <v>360</v>
       </c>
-      <c r="E3" s="12" t="s">
+      <c r="E3" s="10" t="s">
         <v>364</v>
       </c>
-      <c r="F3" s="12" t="s">
+      <c r="F3" s="10" t="s">
         <v>208</v>
       </c>
-      <c r="G3" s="12" t="s">
+      <c r="G3" s="10" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="4" ht="28.5">
-      <c r="A4" s="12" t="s">
+      <c r="A4" s="10" t="s">
         <v>365</v>
       </c>
-      <c r="B4" s="12" t="s">
+      <c r="B4" s="10" t="s">
         <v>366</v>
       </c>
-      <c r="C4" s="12">
+      <c r="C4" s="10">
         <v>24</v>
       </c>
-      <c r="D4" s="12" t="s">
+      <c r="D4" s="10" t="s">
         <v>360</v>
       </c>
-      <c r="E4" s="12" t="s">
+      <c r="E4" s="10" t="s">
         <v>367</v>
       </c>
-      <c r="F4" s="12" t="s">
+      <c r="F4" s="10" t="s">
         <v>208</v>
       </c>
-      <c r="G4" s="12" t="s">
+      <c r="G4" s="10" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="5" ht="25.5">
-      <c r="A5" s="12" t="s">
+      <c r="A5" s="10" t="s">
         <v>368</v>
       </c>
-      <c r="B5" s="12" t="s">
+      <c r="B5" s="10" t="s">
         <v>369</v>
       </c>
-      <c r="C5" s="17">
+      <c r="C5" s="15">
         <v>4540000000</v>
       </c>
-      <c r="D5" s="12" t="s">
+      <c r="D5" s="10" t="s">
         <v>348</v>
       </c>
-      <c r="E5" s="12" t="s">
+      <c r="E5" s="10" t="s">
         <v>370</v>
       </c>
-      <c r="F5" s="12" t="s">
+      <c r="F5" s="10" t="s">
         <v>371</v>
       </c>
-      <c r="G5" s="12" t="s">
+      <c r="G5" s="10" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="6" ht="28.5">
-      <c r="A6" s="12" t="s">
+      <c r="A6" s="10" t="s">
         <v>372</v>
       </c>
-      <c r="B6" s="12" t="s">
+      <c r="B6" s="10" t="s">
         <v>373</v>
       </c>
-      <c r="C6" s="17">
+      <c r="C6" s="15">
         <v>500000000</v>
       </c>
-      <c r="D6" s="12" t="s">
+      <c r="D6" s="10" t="s">
         <v>348</v>
       </c>
-      <c r="E6" s="12" t="s">
+      <c r="E6" s="10" t="s">
         <v>374</v>
       </c>
-      <c r="F6" s="12" t="s">
+      <c r="F6" s="10" t="s">
         <v>371</v>
       </c>
-      <c r="G6" s="12" t="s">
+      <c r="G6" s="10" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="7" ht="28.5">
-      <c r="A7" s="12" t="s">
+      <c r="A7" s="10" t="s">
         <v>375</v>
       </c>
-      <c r="B7" s="12" t="s">
+      <c r="B7" s="10" t="s">
         <v>376</v>
       </c>
-      <c r="C7" s="12">
+      <c r="C7" s="10">
         <v>230</v>
       </c>
-      <c r="D7" s="12" t="s">
+      <c r="D7" s="10" t="s">
         <v>377</v>
       </c>
-      <c r="E7" s="12" t="s">
+      <c r="E7" s="10" t="s">
         <v>378</v>
       </c>
-      <c r="F7" s="12" t="s">
+      <c r="F7" s="10" t="s">
         <v>379</v>
       </c>
-      <c r="G7" s="12" t="s">
+      <c r="G7" s="10" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="8" ht="28.5">
-      <c r="A8" s="12" t="s">
+      <c r="A8" s="10" t="s">
         <v>380</v>
       </c>
-      <c r="B8" s="12" t="s">
+      <c r="B8" s="10" t="s">
         <v>381</v>
       </c>
-      <c r="C8" s="12">
+      <c r="C8" s="10">
         <v>0.01</v>
       </c>
-      <c r="D8" s="12" t="s">
+      <c r="D8" s="10" t="s">
         <v>206</v>
       </c>
-      <c r="E8" s="12" t="s">
+      <c r="E8" s="10" t="s">
         <v>382</v>
       </c>
-      <c r="F8" s="12" t="s">
+      <c r="F8" s="10" t="s">
         <v>379</v>
       </c>
-      <c r="G8" s="12" t="s">
+      <c r="G8" s="10" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="9" ht="25.5">
-      <c r="A9" s="12" t="s">
+      <c r="A9" s="10" t="s">
         <v>383</v>
       </c>
-      <c r="B9" s="12" t="s">
+      <c r="B9" s="10" t="s">
         <v>384</v>
       </c>
-      <c r="C9" s="12">
+      <c r="C9" s="10">
         <v>1366</v>
       </c>
-      <c r="D9" s="12" t="s">
+      <c r="D9" s="10" t="s">
         <v>385</v>
       </c>
-      <c r="E9" s="12" t="s">
+      <c r="E9" s="10" t="s">
         <v>386</v>
       </c>
-      <c r="F9" s="12" t="s">
+      <c r="F9" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="G9" s="12" t="s">
+      <c r="G9" s="10" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="10" ht="25.5">
-      <c r="A10" s="12" t="s">
+      <c r="A10" s="10" t="s">
         <v>387</v>
       </c>
-      <c r="B10" s="12" t="s">
+      <c r="B10" s="10" t="s">
         <v>388</v>
       </c>
-      <c r="C10" s="12">
+      <c r="C10" s="10">
         <v>587</v>
       </c>
-      <c r="D10" s="12" t="s">
+      <c r="D10" s="10" t="s">
         <v>385</v>
       </c>
-      <c r="E10" s="12" t="s">
+      <c r="E10" s="10" t="s">
         <v>389</v>
       </c>
-      <c r="F10" s="12" t="s">
+      <c r="F10" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="G10" s="12" t="s">
+      <c r="G10" s="10" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="11" ht="25.5">
-      <c r="A11" s="12" t="s">
+      <c r="A11" s="10" t="s">
         <v>390</v>
       </c>
-      <c r="B11" s="12" t="s">
+      <c r="B11" s="10" t="s">
         <v>391</v>
       </c>
-      <c r="C11" s="12">
+      <c r="C11" s="10">
         <v>101.325</v>
       </c>
-      <c r="D11" s="12" t="s">
+      <c r="D11" s="10" t="s">
         <v>392</v>
       </c>
-      <c r="E11" s="12" t="s">
+      <c r="E11" s="10" t="s">
         <v>386</v>
       </c>
-      <c r="F11" s="12" t="s">
+      <c r="F11" s="10" t="s">
         <v>379</v>
       </c>
-      <c r="G11" s="12" t="s">
+      <c r="G11" s="10" t="s">
         <v>12</v>
       </c>
     </row>
@@ -3154,182 +3152,182 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="10" t="s">
         <v>393</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="10" t="s">
         <v>355</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="10" t="s">
         <v>356</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="10" t="s">
         <v>197</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="10" t="s">
         <v>357</v>
       </c>
     </row>
     <row r="2" ht="25.5">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="10" t="s">
         <v>394</v>
       </c>
-      <c r="B2" s="12" t="s">
+      <c r="B2" s="10" t="s">
         <v>395</v>
       </c>
-      <c r="C2" s="17">
+      <c r="C2" s="15">
         <v>6.0220000000000003e+23</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="D2" s="10" t="s">
         <v>396</v>
       </c>
-      <c r="E2" s="12" t="s">
+      <c r="E2" s="10" t="s">
         <v>397</v>
       </c>
-      <c r="F2" s="12" t="s">
+      <c r="F2" s="10" t="s">
         <v>398</v>
       </c>
     </row>
     <row r="3" ht="25.5">
-      <c r="A3" s="12" t="s">
+      <c r="A3" s="10" t="s">
         <v>399</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="B3" s="10" t="s">
         <v>400</v>
       </c>
-      <c r="C3" s="22">
+      <c r="C3" s="20">
         <v>46244</v>
       </c>
-      <c r="D3" s="12" t="s">
+      <c r="D3" s="10" t="s">
         <v>401</v>
       </c>
-      <c r="E3" s="12" t="s">
+      <c r="E3" s="10" t="s">
         <v>234</v>
       </c>
-      <c r="F3" s="12" t="s">
+      <c r="F3" s="10" t="s">
         <v>402</v>
       </c>
     </row>
     <row r="4" ht="25.5">
-      <c r="A4" s="12" t="s">
+      <c r="A4" s="10" t="s">
         <v>403</v>
       </c>
-      <c r="B4" s="12" t="s">
+      <c r="B4" s="10" t="s">
         <v>391</v>
       </c>
-      <c r="C4" s="12">
+      <c r="C4" s="10">
         <v>101.325</v>
       </c>
-      <c r="D4" s="12" t="s">
+      <c r="D4" s="10" t="s">
         <v>392</v>
       </c>
-      <c r="E4" s="12" t="s">
+      <c r="E4" s="10" t="s">
         <v>379</v>
       </c>
-      <c r="F4" s="12" t="s">
+      <c r="F4" s="10" t="s">
         <v>404</v>
       </c>
     </row>
     <row r="5" ht="25.5">
-      <c r="A5" s="12" t="s">
+      <c r="A5" s="10" t="s">
         <v>405</v>
       </c>
-      <c r="B5" s="12" t="s">
+      <c r="B5" s="10" t="s">
         <v>406</v>
       </c>
-      <c r="C5" s="12">
+      <c r="C5" s="10">
         <v>1366</v>
       </c>
-      <c r="D5" s="12" t="s">
+      <c r="D5" s="10" t="s">
         <v>385</v>
       </c>
-      <c r="E5" s="12" t="s">
+      <c r="E5" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="F5" s="12" t="s">
+      <c r="F5" s="10" t="s">
         <v>407</v>
       </c>
     </row>
     <row r="6" ht="25.5">
-      <c r="A6" s="12" t="s">
+      <c r="A6" s="10" t="s">
         <v>408</v>
       </c>
-      <c r="B6" s="12" t="s">
+      <c r="B6" s="10" t="s">
         <v>409</v>
       </c>
-      <c r="C6" s="12">
+      <c r="C6" s="10">
         <v>587</v>
       </c>
-      <c r="D6" s="12" t="s">
+      <c r="D6" s="10" t="s">
         <v>385</v>
       </c>
-      <c r="E6" s="12" t="s">
+      <c r="E6" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="F6" s="12" t="s">
+      <c r="F6" s="10" t="s">
         <v>389</v>
       </c>
     </row>
     <row r="7" ht="25.5">
-      <c r="A7" s="12" t="s">
+      <c r="A7" s="10" t="s">
         <v>410</v>
       </c>
-      <c r="B7" s="12" t="s">
+      <c r="B7" s="10" t="s">
         <v>411</v>
       </c>
-      <c r="C7" s="17">
+      <c r="C7" s="15">
         <v>299800000</v>
       </c>
-      <c r="D7" s="12" t="s">
+      <c r="D7" s="10" t="s">
         <v>412</v>
       </c>
-      <c r="E7" s="12" t="s">
+      <c r="E7" s="10" t="s">
         <v>413</v>
       </c>
-      <c r="F7" s="12" t="s">
+      <c r="F7" s="10" t="s">
         <v>398</v>
       </c>
     </row>
     <row r="8" ht="25.5">
-      <c r="A8" s="12" t="s">
+      <c r="A8" s="10" t="s">
         <v>414</v>
       </c>
-      <c r="B8" s="12" t="s">
+      <c r="B8" s="10" t="s">
         <v>415</v>
       </c>
-      <c r="C8" s="17">
+      <c r="C8" s="15">
         <v>6.6259999999999998e-34</v>
       </c>
-      <c r="D8" s="12" t="s">
+      <c r="D8" s="10" t="s">
         <v>416</v>
       </c>
-      <c r="E8" s="12" t="s">
+      <c r="E8" s="10" t="s">
         <v>413</v>
       </c>
-      <c r="F8" s="12" t="s">
+      <c r="F8" s="10" t="s">
         <v>398</v>
       </c>
     </row>
     <row r="9" ht="25.5">
-      <c r="A9" s="12" t="s">
+      <c r="A9" s="10" t="s">
         <v>417</v>
       </c>
-      <c r="B9" s="12" t="s">
+      <c r="B9" s="10" t="s">
         <v>418</v>
       </c>
-      <c r="C9" s="17">
+      <c r="C9" s="15">
         <v>1.3809999999999999e-23</v>
       </c>
-      <c r="D9" s="12" t="s">
+      <c r="D9" s="10" t="s">
         <v>419</v>
       </c>
-      <c r="E9" s="12" t="s">
+      <c r="E9" s="10" t="s">
         <v>413</v>
       </c>
-      <c r="F9" s="12" t="s">
+      <c r="F9" s="10" t="s">
         <v>398</v>
       </c>
     </row>
@@ -3351,194 +3349,194 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="10" t="s">
         <v>420</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="10" t="s">
         <v>421</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="10" t="s">
         <v>422</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="10" t="s">
         <v>195</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="10" t="s">
         <v>423</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="10" t="s">
         <v>424</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="G1" s="10" t="s">
         <v>425</v>
       </c>
-      <c r="H1" s="12" t="s">
+      <c r="H1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="I1" s="12" t="s">
+      <c r="I1" s="10" t="s">
         <v>426</v>
       </c>
-      <c r="J1" s="12"/>
-      <c r="K1" s="12"/>
+      <c r="J1" s="10"/>
+      <c r="K1" s="10"/>
     </row>
     <row r="2" ht="25.5">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="10" t="s">
         <v>427</v>
       </c>
-      <c r="B2" s="12" t="s">
+      <c r="B2" s="10" t="s">
         <v>428</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="C2" s="10" t="s">
         <v>429</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="D2" s="10" t="s">
         <v>430</v>
       </c>
-      <c r="E2" s="12" t="s">
+      <c r="E2" s="10" t="s">
         <v>431</v>
       </c>
-      <c r="F2" s="12">
+      <c r="F2" s="10">
         <v>0.23999999999999999</v>
       </c>
-      <c r="G2" s="12" t="s">
+      <c r="G2" s="10" t="s">
         <v>432</v>
       </c>
-      <c r="H2" s="12">
+      <c r="H2" s="10">
         <v>0.22</v>
       </c>
-      <c r="I2" s="12">
+      <c r="I2" s="10">
         <v>0.089999999999999997</v>
       </c>
-      <c r="J2" s="12" t="s">
+      <c r="J2" s="10" t="s">
         <v>433</v>
       </c>
-      <c r="K2" s="12">
+      <c r="K2" s="10">
         <v>0.29999999999999999</v>
       </c>
     </row>
     <row r="3" ht="25.5">
-      <c r="A3" s="12" t="s">
+      <c r="A3" s="10" t="s">
         <v>434</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="B3" s="10" t="s">
         <v>435</v>
       </c>
-      <c r="C3" s="12" t="s">
+      <c r="C3" s="10" t="s">
         <v>436</v>
       </c>
-      <c r="D3" s="12">
+      <c r="D3" s="10">
         <v>0.45000000000000001</v>
       </c>
-      <c r="E3" s="12" t="s">
+      <c r="E3" s="10" t="s">
         <v>437</v>
       </c>
-      <c r="F3" s="12">
+      <c r="F3" s="10">
         <v>0.42999999999999999</v>
       </c>
-      <c r="G3" s="12">
+      <c r="G3" s="10">
         <v>0.050000000000000003</v>
       </c>
-      <c r="H3" s="12" t="s">
+      <c r="H3" s="10" t="s">
         <v>438</v>
       </c>
-      <c r="I3" s="12">
+      <c r="I3" s="10">
         <v>0.25</v>
       </c>
-      <c r="J3" s="12"/>
-      <c r="K3" s="12"/>
+      <c r="J3" s="10"/>
+      <c r="K3" s="10"/>
     </row>
     <row r="4" ht="25.5">
-      <c r="A4" s="12" t="s">
+      <c r="A4" s="10" t="s">
         <v>439</v>
       </c>
-      <c r="B4" s="12" t="s">
+      <c r="B4" s="10" t="s">
         <v>440</v>
       </c>
-      <c r="C4" s="12" t="s">
+      <c r="C4" s="10" t="s">
         <v>441</v>
       </c>
-      <c r="D4" s="12">
+      <c r="D4" s="10">
         <v>0.59999999999999998</v>
       </c>
-      <c r="E4" s="12" t="s">
+      <c r="E4" s="10" t="s">
         <v>442</v>
       </c>
-      <c r="F4" s="12">
+      <c r="F4" s="10">
         <v>0.55000000000000004</v>
       </c>
-      <c r="G4" s="12">
+      <c r="G4" s="10">
         <v>0.089999999999999997</v>
       </c>
-      <c r="H4" s="12" t="s">
+      <c r="H4" s="10" t="s">
         <v>314</v>
       </c>
-      <c r="I4" s="12">
+      <c r="I4" s="10">
         <v>0.25</v>
       </c>
-      <c r="J4" s="12"/>
-      <c r="K4" s="12"/>
+      <c r="J4" s="10"/>
+      <c r="K4" s="10"/>
     </row>
     <row r="5" ht="25.5">
-      <c r="A5" s="12" t="s">
+      <c r="A5" s="10" t="s">
         <v>443</v>
       </c>
-      <c r="B5" s="12" t="s">
+      <c r="B5" s="10" t="s">
         <v>444</v>
       </c>
-      <c r="C5" s="12" t="s">
+      <c r="C5" s="10" t="s">
         <v>445</v>
       </c>
-      <c r="D5" s="12">
+      <c r="D5" s="10">
         <v>0.29999999999999999</v>
       </c>
-      <c r="E5" s="12" t="s">
+      <c r="E5" s="10" t="s">
         <v>446</v>
       </c>
-      <c r="F5" s="12">
+      <c r="F5" s="10">
         <v>0.29999999999999999</v>
       </c>
-      <c r="G5" s="12">
+      <c r="G5" s="10">
         <v>0</v>
       </c>
-      <c r="H5" s="12" t="s">
+      <c r="H5" s="10" t="s">
         <v>447</v>
       </c>
-      <c r="I5" s="12">
+      <c r="I5" s="10">
         <v>0.20000000000000001</v>
       </c>
-      <c r="J5" s="12"/>
-      <c r="K5" s="12"/>
+      <c r="J5" s="10"/>
+      <c r="K5" s="10"/>
     </row>
     <row r="6" ht="25.5">
-      <c r="A6" s="12" t="s">
+      <c r="A6" s="10" t="s">
         <v>448</v>
       </c>
-      <c r="B6" s="12" t="s">
+      <c r="B6" s="10" t="s">
         <v>449</v>
       </c>
-      <c r="C6" s="12" t="s">
+      <c r="C6" s="10" t="s">
         <v>450</v>
       </c>
-      <c r="D6" s="12">
+      <c r="D6" s="10">
         <v>0.46999999999999997</v>
       </c>
-      <c r="E6" s="12" t="s">
+      <c r="E6" s="10" t="s">
         <v>432</v>
       </c>
-      <c r="F6" s="12">
+      <c r="F6" s="10">
         <v>0.45000000000000001</v>
       </c>
-      <c r="G6" s="12">
+      <c r="G6" s="10">
         <v>0.040000000000000001</v>
       </c>
-      <c r="H6" s="12" t="s">
+      <c r="H6" s="10" t="s">
         <v>438</v>
       </c>
-      <c r="I6" s="12">
+      <c r="I6" s="10">
         <v>0.14999999999999999</v>
       </c>
-      <c r="J6" s="12"/>
-      <c r="K6" s="12"/>
+      <c r="J6" s="10"/>
+      <c r="K6" s="10"/>
     </row>
   </sheetData>
   <printOptions headings="0" gridLines="0"/>
@@ -3552,171 +3550,171 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="2" style="12" width="9.140625"/>
-    <col customWidth="1" min="3" max="3" style="12" width="11.421875"/>
-    <col customWidth="1" min="4" max="4" style="12" width="10.8515625"/>
-    <col customWidth="1" min="5" max="5" style="12" width="14.140625"/>
-    <col min="6" max="16384" style="12" width="9.140625"/>
+    <col min="1" max="2" style="10" width="9.140625"/>
+    <col customWidth="1" min="3" max="3" style="10" width="11.421875"/>
+    <col customWidth="1" min="4" max="4" style="10" width="10.8515625"/>
+    <col customWidth="1" min="5" max="5" style="10" width="14.140625"/>
+    <col min="6" max="16384" style="10" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="10" t="s">
         <v>451</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="10" t="s">
         <v>191</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="10" t="s">
         <v>192</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="10" t="s">
         <v>452</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="10" t="s">
         <v>453</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="10" t="s">
         <v>454</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="G1" s="10" t="s">
         <v>455</v>
       </c>
     </row>
     <row r="2" ht="25.5">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="12" t="s">
+      <c r="B2" s="10" t="s">
         <v>201</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="C2" s="10" t="s">
         <v>202</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="D2" s="10" t="s">
         <v>209</v>
       </c>
-      <c r="E2" s="12" t="s">
+      <c r="E2" s="10" t="s">
         <v>456</v>
       </c>
-      <c r="F2" s="12">
+      <c r="F2" s="10">
         <v>2025</v>
       </c>
-      <c r="G2" s="12" t="s">
+      <c r="G2" s="10" t="s">
         <v>457</v>
       </c>
     </row>
     <row r="3" ht="25.5">
-      <c r="A3" s="12" t="s">
+      <c r="A3" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="B3" s="10" t="s">
         <v>288</v>
       </c>
-      <c r="C3" s="12" t="s">
+      <c r="C3" s="10" t="s">
         <v>289</v>
       </c>
-      <c r="D3" s="12" t="s">
+      <c r="D3" s="10" t="s">
         <v>458</v>
       </c>
-      <c r="E3" s="12" t="s">
+      <c r="E3" s="10" t="s">
         <v>459</v>
       </c>
-      <c r="F3" s="12">
+      <c r="F3" s="10">
         <v>2026</v>
       </c>
-      <c r="G3" s="12" t="s">
+      <c r="G3" s="10" t="s">
         <v>460</v>
       </c>
     </row>
     <row r="4" ht="25.5">
-      <c r="A4" s="12" t="s">
+      <c r="A4" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="B4" s="12" t="s">
+      <c r="B4" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="C4" s="12" t="s">
+      <c r="C4" s="10" t="s">
         <v>231</v>
       </c>
-      <c r="D4" s="12" t="s">
+      <c r="D4" s="10" t="s">
         <v>461</v>
       </c>
-      <c r="E4" s="12" t="s">
+      <c r="E4" s="10" t="s">
         <v>462</v>
       </c>
-      <c r="F4" s="12">
+      <c r="F4" s="10">
         <v>2024</v>
       </c>
-      <c r="G4" s="12" t="s">
+      <c r="G4" s="10" t="s">
         <v>463</v>
       </c>
     </row>
     <row r="5" ht="38.25">
-      <c r="A5" s="12" t="s">
+      <c r="A5" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="B5" s="12" t="s">
+      <c r="B5" s="10" t="s">
         <v>310</v>
       </c>
-      <c r="C5" s="12" t="s">
+      <c r="C5" s="10" t="s">
         <v>311</v>
       </c>
-      <c r="D5" s="12" t="s">
+      <c r="D5" s="10" t="s">
         <v>464</v>
       </c>
-      <c r="E5" s="12" t="s">
+      <c r="E5" s="10" t="s">
         <v>465</v>
       </c>
-      <c r="F5" s="12">
+      <c r="F5" s="10">
         <v>2024</v>
       </c>
-      <c r="G5" s="12" t="s">
+      <c r="G5" s="10" t="s">
         <v>466</v>
       </c>
     </row>
     <row r="6" ht="25.5">
-      <c r="A6" s="12" t="s">
+      <c r="A6" s="10" t="s">
         <v>91</v>
       </c>
-      <c r="B6" s="12" t="s">
+      <c r="B6" s="10" t="s">
         <v>224</v>
       </c>
-      <c r="C6" s="12" t="s">
+      <c r="C6" s="10" t="s">
         <v>225</v>
       </c>
-      <c r="D6" s="12" t="s">
+      <c r="D6" s="10" t="s">
         <v>467</v>
       </c>
-      <c r="E6" s="12" t="s">
+      <c r="E6" s="10" t="s">
         <v>468</v>
       </c>
-      <c r="F6" s="12">
+      <c r="F6" s="10">
         <v>2030</v>
       </c>
-      <c r="G6" s="12" t="s">
+      <c r="G6" s="10" t="s">
         <v>469</v>
       </c>
     </row>
     <row r="7" ht="25.5">
-      <c r="A7" s="12" t="s">
+      <c r="A7" s="10" t="s">
         <v>91</v>
       </c>
-      <c r="B7" s="12" t="s">
+      <c r="B7" s="10" t="s">
         <v>299</v>
       </c>
-      <c r="C7" s="12" t="s">
+      <c r="C7" s="10" t="s">
         <v>300</v>
       </c>
-      <c r="D7" s="12" t="s">
+      <c r="D7" s="10" t="s">
         <v>304</v>
       </c>
-      <c r="E7" s="12" t="s">
+      <c r="E7" s="10" t="s">
         <v>470</v>
       </c>
-      <c r="F7" s="12">
+      <c r="F7" s="10">
         <v>2028</v>
       </c>
-      <c r="G7" s="12" t="s">
+      <c r="G7" s="10" t="s">
         <v>471</v>
       </c>
     </row>
@@ -3732,143 +3730,143 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col bestFit="1" min="1" max="1" style="12" width="10.7109375"/>
-    <col min="2" max="2" style="12" width="9.140625"/>
-    <col customWidth="1" min="3" max="3" style="12" width="10.7109375"/>
-    <col min="4" max="5" style="12" width="9.140625"/>
-    <col customWidth="1" min="6" max="6" style="12" width="11.57421875"/>
-    <col min="7" max="7" style="12" width="9.140625"/>
-    <col customWidth="1" min="8" max="8" style="12" width="10.8515625"/>
-    <col min="9" max="16384" style="12" width="9.140625"/>
+    <col bestFit="1" min="1" max="1" style="10" width="10.7109375"/>
+    <col min="2" max="2" style="10" width="9.140625"/>
+    <col customWidth="1" min="3" max="3" style="10" width="10.7109375"/>
+    <col min="4" max="5" style="10" width="9.140625"/>
+    <col customWidth="1" min="6" max="6" style="10" width="11.57421875"/>
+    <col min="7" max="7" style="10" width="9.140625"/>
+    <col customWidth="1" min="8" max="8" style="10" width="10.8515625"/>
+    <col min="9" max="16384" style="10" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="10" t="s">
         <v>472</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="10" t="s">
         <v>191</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="10" t="s">
         <v>192</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="10" t="s">
         <v>473</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="10" t="s">
         <v>474</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="10" t="s">
         <v>475</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="G1" s="10" t="s">
         <v>476</v>
       </c>
-      <c r="H1" s="12" t="s">
+      <c r="H1" s="10" t="s">
         <v>477</v>
       </c>
     </row>
     <row r="2" ht="25.5">
-      <c r="A2" s="23">
+      <c r="A2" s="21">
         <v>45306</v>
       </c>
-      <c r="B2" s="12" t="s">
+      <c r="B2" s="10" t="s">
         <v>211</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="C2" s="10" t="s">
         <v>212</v>
       </c>
-      <c r="D2" s="12">
+      <c r="D2" s="10">
         <v>0.20000000000000001</v>
       </c>
-      <c r="E2" s="12">
+      <c r="E2" s="10">
         <v>0.22</v>
       </c>
-      <c r="F2" s="12" t="s">
+      <c r="F2" s="10" t="s">
         <v>478</v>
       </c>
-      <c r="G2" s="12" t="s">
+      <c r="G2" s="10" t="s">
         <v>457</v>
       </c>
-      <c r="H2" s="12" t="s">
+      <c r="H2" s="10" t="s">
         <v>479</v>
       </c>
     </row>
     <row r="3" ht="25.5">
-      <c r="A3" s="23">
+      <c r="A3" s="21">
         <v>45301</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="B3" s="10" t="s">
         <v>237</v>
       </c>
-      <c r="C3" s="12" t="s">
+      <c r="C3" s="10" t="s">
         <v>238</v>
       </c>
-      <c r="D3" s="12">
+      <c r="D3" s="10">
         <v>0.12</v>
       </c>
-      <c r="E3" s="12">
+      <c r="E3" s="10">
         <v>0.14999999999999999</v>
       </c>
-      <c r="F3" s="12" t="s">
+      <c r="F3" s="10" t="s">
         <v>480</v>
       </c>
-      <c r="G3" s="12" t="s">
+      <c r="G3" s="10" t="s">
         <v>481</v>
       </c>
-      <c r="H3" s="12" t="s">
+      <c r="H3" s="10" t="s">
         <v>482</v>
       </c>
     </row>
     <row r="4" ht="25.5">
-      <c r="A4" s="23">
+      <c r="A4" s="21">
         <v>45265</v>
       </c>
-      <c r="B4" s="12" t="s">
+      <c r="B4" s="10" t="s">
         <v>257</v>
       </c>
-      <c r="C4" s="12" t="s">
+      <c r="C4" s="10" t="s">
         <v>258</v>
       </c>
-      <c r="D4" s="12">
+      <c r="D4" s="10">
         <v>150</v>
       </c>
-      <c r="E4" s="12">
+      <c r="E4" s="10">
         <v>180</v>
       </c>
-      <c r="F4" s="12" t="s">
+      <c r="F4" s="10" t="s">
         <v>483</v>
       </c>
-      <c r="G4" s="12" t="s">
+      <c r="G4" s="10" t="s">
         <v>484</v>
       </c>
-      <c r="H4" s="12" t="s">
+      <c r="H4" s="10" t="s">
         <v>485</v>
       </c>
     </row>
     <row r="5" ht="38.25">
-      <c r="A5" s="23">
+      <c r="A5" s="21">
         <v>45250</v>
       </c>
-      <c r="B5" s="12" t="s">
+      <c r="B5" s="10" t="s">
         <v>310</v>
       </c>
-      <c r="C5" s="12" t="s">
+      <c r="C5" s="10" t="s">
         <v>311</v>
       </c>
-      <c r="D5" s="12">
+      <c r="D5" s="10">
         <v>0.080000000000000002</v>
       </c>
-      <c r="E5" s="12">
+      <c r="E5" s="10">
         <v>0.10000000000000001</v>
       </c>
-      <c r="F5" s="12" t="s">
+      <c r="F5" s="10" t="s">
         <v>486</v>
       </c>
-      <c r="G5" s="12" t="s">
+      <c r="G5" s="10" t="s">
         <v>466</v>
       </c>
-      <c r="H5" s="12" t="s">
+      <c r="H5" s="10" t="s">
         <v>487</v>
       </c>
     </row>
@@ -3884,111 +3882,111 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="3" style="12" width="9.140625"/>
-    <col customWidth="1" min="4" max="4" style="12" width="13.421875"/>
-    <col customWidth="1" min="5" max="5" style="12" width="12.8515625"/>
-    <col min="6" max="16384" style="12" width="9.140625"/>
+    <col min="1" max="3" style="10" width="9.140625"/>
+    <col customWidth="1" min="4" max="4" style="10" width="13.421875"/>
+    <col customWidth="1" min="5" max="5" style="10" width="12.8515625"/>
+    <col min="6" max="16384" style="10" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="10" t="s">
         <v>488</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="10" t="s">
         <v>489</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="10" t="s">
         <v>490</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="10" t="s">
         <v>491</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="10" t="s">
         <v>355</v>
       </c>
     </row>
     <row r="2" ht="38.25">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="10" t="s">
         <v>201</v>
       </c>
-      <c r="B2" s="12" t="s">
+      <c r="B2" s="10" t="s">
         <v>211</v>
       </c>
-      <c r="C2" s="12">
+      <c r="C2" s="10">
         <v>0.84999999999999998</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="D2" s="10" t="s">
         <v>492</v>
       </c>
-      <c r="E2" s="12" t="s">
+      <c r="E2" s="10" t="s">
         <v>493</v>
       </c>
     </row>
     <row r="3" ht="38.25">
-      <c r="A3" s="12" t="s">
+      <c r="A3" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="B3" s="10" t="s">
         <v>237</v>
       </c>
-      <c r="C3" s="12">
+      <c r="C3" s="10">
         <v>0.59999999999999998</v>
       </c>
-      <c r="D3" s="12" t="s">
+      <c r="D3" s="10" t="s">
         <v>494</v>
       </c>
-      <c r="E3" s="12" t="s">
+      <c r="E3" s="10" t="s">
         <v>495</v>
       </c>
     </row>
     <row r="4" ht="38.25">
-      <c r="A4" s="12" t="s">
+      <c r="A4" s="10" t="s">
         <v>257</v>
       </c>
-      <c r="B4" s="12" t="s">
+      <c r="B4" s="10" t="s">
         <v>280</v>
       </c>
-      <c r="C4" s="12">
+      <c r="C4" s="10">
         <v>0.75</v>
       </c>
-      <c r="D4" s="12" t="s">
+      <c r="D4" s="10" t="s">
         <v>492</v>
       </c>
-      <c r="E4" s="12" t="s">
+      <c r="E4" s="10" t="s">
         <v>496</v>
       </c>
     </row>
     <row r="5" ht="38.25">
-      <c r="A5" s="12" t="s">
+      <c r="A5" s="10" t="s">
         <v>288</v>
       </c>
-      <c r="B5" s="12" t="s">
+      <c r="B5" s="10" t="s">
         <v>294</v>
       </c>
-      <c r="C5" s="12">
+      <c r="C5" s="10">
         <v>0.40000000000000002</v>
       </c>
-      <c r="D5" s="12" t="s">
+      <c r="D5" s="10" t="s">
         <v>497</v>
       </c>
-      <c r="E5" s="12" t="s">
+      <c r="E5" s="10" t="s">
         <v>498</v>
       </c>
     </row>
     <row r="6" ht="38.25">
-      <c r="A6" s="12" t="s">
+      <c r="A6" s="10" t="s">
         <v>310</v>
       </c>
-      <c r="B6" s="12" t="s">
+      <c r="B6" s="10" t="s">
         <v>322</v>
       </c>
-      <c r="C6" s="12">
+      <c r="C6" s="10">
         <v>-0.69999999999999996</v>
       </c>
-      <c r="D6" s="12" t="s">
+      <c r="D6" s="10" t="s">
         <v>499</v>
       </c>
-      <c r="E6" s="12" t="s">
+      <c r="E6" s="10" t="s">
         <v>500</v>
       </c>
     </row>
@@ -4270,7 +4268,7 @@
       <c r="H10" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="I10" s="11" t="s">
+      <c r="I10" s="1" t="s">
         <v>168</v>
       </c>
     </row>
@@ -4312,86 +4310,86 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
   <sheetFormatPr baseColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" style="12" width="10.28125"/>
-    <col customWidth="1" min="2" max="2" style="12" width="12.00390625"/>
-    <col customWidth="1" min="3" max="3" style="12" width="11.140625"/>
-    <col min="4" max="16384" style="12" width="10.28125"/>
+    <col min="1" max="1" style="10" width="10.28125"/>
+    <col customWidth="1" min="2" max="2" style="10" width="12.00390625"/>
+    <col customWidth="1" min="3" max="3" style="10" width="11.140625"/>
+    <col min="4" max="16384" style="10" width="10.28125"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="10" t="s">
         <v>172</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="10" t="s">
         <v>173</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="10" t="s">
         <v>174</v>
       </c>
     </row>
     <row r="2" ht="25.5">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="10" t="s">
         <v>175</v>
       </c>
-      <c r="B2" s="12" t="s">
+      <c r="B2" s="10" t="s">
         <v>176</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="C2" s="10" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="12" t="s">
+      <c r="A3" s="10" t="s">
         <v>178</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="B3" s="10" t="s">
         <v>179</v>
       </c>
-      <c r="C3" s="13">
+      <c r="C3" s="11">
         <v>1</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="12" t="s">
+      <c r="A4" s="10" t="s">
         <v>180</v>
       </c>
-      <c r="B4" s="12" t="s">
+      <c r="B4" s="10" t="s">
         <v>181</v>
       </c>
-      <c r="C4" s="12">
+      <c r="C4" s="10">
         <v>2024</v>
       </c>
     </row>
     <row r="5" ht="38.25">
-      <c r="A5" s="12" t="s">
+      <c r="A5" s="10" t="s">
         <v>182</v>
       </c>
-      <c r="B5" s="12" t="s">
+      <c r="B5" s="10" t="s">
         <v>183</v>
       </c>
-      <c r="C5" s="12" t="s">
+      <c r="C5" s="10" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="6" ht="25.5">
-      <c r="A6" s="12" t="s">
+      <c r="A6" s="10" t="s">
         <v>185</v>
       </c>
-      <c r="B6" s="12" t="s">
+      <c r="B6" s="10" t="s">
         <v>186</v>
       </c>
-      <c r="C6" s="12" t="s">
+      <c r="C6" s="10" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="12" t="s">
+      <c r="A7" s="10" t="s">
         <v>188</v>
       </c>
-      <c r="B7" s="12" t="s">
+      <c r="B7" s="10" t="s">
         <v>189</v>
       </c>
-      <c r="C7" s="12" t="s">
+      <c r="C7" s="10" t="s">
         <v>190</v>
       </c>
     </row>
@@ -4407,199 +4405,199 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
   <sheetFormatPr baseColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="3" style="12" width="10.28125"/>
-    <col customWidth="1" min="4" max="4" style="12" width="12.8515625"/>
-    <col bestFit="1" customWidth="1" min="5" max="6" style="12" width="9"/>
-    <col min="7" max="16384" style="12" width="10.28125"/>
+    <col min="1" max="3" style="10" width="10.28125"/>
+    <col customWidth="1" min="4" max="4" style="10" width="12.8515625"/>
+    <col bestFit="1" customWidth="1" min="5" max="6" style="10" width="9"/>
+    <col min="7" max="16384" style="10" width="10.28125"/>
   </cols>
   <sheetData>
     <row r="1" ht="14.25">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="10" t="s">
         <v>191</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="10" t="s">
         <v>192</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="10" t="s">
         <v>193</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="10" t="s">
         <v>194</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="10" t="s">
         <v>195</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="10" t="s">
         <v>196</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="G1" s="10" t="s">
         <v>197</v>
       </c>
-      <c r="H1" s="12" t="s">
+      <c r="H1" s="10" t="s">
         <v>198</v>
       </c>
-      <c r="I1" s="12" t="s">
+      <c r="I1" s="10" t="s">
         <v>199</v>
       </c>
-      <c r="J1" s="12" t="s">
+      <c r="J1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="K1" s="12" t="s">
+      <c r="K1" s="10" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="2" ht="51">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="10" t="s">
         <v>201</v>
       </c>
-      <c r="B2" s="12" t="s">
+      <c r="B2" s="10" t="s">
         <v>202</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="C2" s="10" t="s">
         <v>203</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="D2" s="10" t="s">
         <v>204</v>
       </c>
-      <c r="E2" s="14">
+      <c r="E2" s="12">
         <v>0.0001</v>
       </c>
-      <c r="F2" s="12" t="s">
+      <c r="F2" s="10" t="s">
         <v>205</v>
       </c>
-      <c r="G2" s="12" t="s">
+      <c r="G2" s="10" t="s">
         <v>206</v>
       </c>
-      <c r="H2" s="12" t="s">
+      <c r="H2" s="10" t="s">
         <v>91</v>
       </c>
-      <c r="I2" s="12" t="s">
+      <c r="I2" s="10" t="s">
         <v>207</v>
       </c>
-      <c r="J2" s="12" t="s">
+      <c r="J2" s="10" t="s">
         <v>208</v>
       </c>
-      <c r="K2" s="12" t="s">
+      <c r="K2" s="10" t="s">
         <v>209</v>
       </c>
-      <c r="L2" s="12" t="s">
+      <c r="L2" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="M2" s="12" t="s">
+      <c r="M2" s="10" t="s">
         <v>210</v>
       </c>
     </row>
     <row r="3" ht="51">
-      <c r="A3" s="12" t="s">
+      <c r="A3" s="10" t="s">
         <v>211</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="B3" s="10" t="s">
         <v>212</v>
       </c>
-      <c r="C3" s="12" t="s">
+      <c r="C3" s="10" t="s">
         <v>213</v>
       </c>
-      <c r="D3" s="12" t="s">
+      <c r="D3" s="10" t="s">
         <v>214</v>
       </c>
-      <c r="E3" s="15">
+      <c r="E3" s="13">
         <v>0.22</v>
       </c>
-      <c r="F3" s="15">
+      <c r="F3" s="13">
         <v>0.25</v>
       </c>
-      <c r="G3" s="12" t="s">
+      <c r="G3" s="10" t="s">
         <v>206</v>
       </c>
-      <c r="H3" s="12" t="s">
+      <c r="H3" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="I3" s="12" t="s">
+      <c r="I3" s="10" t="s">
         <v>207</v>
       </c>
-      <c r="J3" s="12" t="s">
+      <c r="J3" s="10" t="s">
         <v>208</v>
       </c>
-      <c r="K3" s="12" t="s">
+      <c r="K3" s="10" t="s">
         <v>215</v>
       </c>
-      <c r="M3" s="16" t="s">
+      <c r="M3" s="14" t="s">
         <v>216</v>
       </c>
     </row>
     <row r="4" ht="38.25">
-      <c r="A4" s="12" t="s">
+      <c r="A4" s="10" t="s">
         <v>217</v>
       </c>
-      <c r="B4" s="12" t="s">
+      <c r="B4" s="10" t="s">
         <v>218</v>
       </c>
-      <c r="C4" s="12" t="s">
+      <c r="C4" s="10" t="s">
         <v>219</v>
       </c>
-      <c r="D4" s="12" t="s">
+      <c r="D4" s="10" t="s">
         <v>220</v>
       </c>
-      <c r="E4" s="13">
+      <c r="E4" s="11">
         <v>0.5</v>
       </c>
-      <c r="F4" s="13">
+      <c r="F4" s="11">
         <v>0.80000000000000004</v>
       </c>
-      <c r="G4" s="12" t="s">
+      <c r="G4" s="10" t="s">
         <v>206</v>
       </c>
-      <c r="H4" s="12" t="s">
+      <c r="H4" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="I4" s="12" t="s">
+      <c r="I4" s="10" t="s">
         <v>221</v>
       </c>
-      <c r="J4" s="12" t="s">
+      <c r="J4" s="10" t="s">
         <v>208</v>
       </c>
-      <c r="K4" s="12" t="s">
+      <c r="K4" s="10" t="s">
         <v>222</v>
       </c>
-      <c r="L4" s="12" t="s">
+      <c r="L4" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="M4" s="12" t="s">
+      <c r="M4" s="10" t="s">
         <v>223</v>
       </c>
     </row>
     <row r="5" ht="25.5">
-      <c r="A5" s="12" t="s">
+      <c r="A5" s="10" t="s">
         <v>224</v>
       </c>
-      <c r="B5" s="12" t="s">
+      <c r="B5" s="10" t="s">
         <v>225</v>
       </c>
-      <c r="C5" s="12" t="s">
+      <c r="C5" s="10" t="s">
         <v>226</v>
       </c>
-      <c r="D5" s="12" t="s">
+      <c r="D5" s="10" t="s">
         <v>227</v>
       </c>
-      <c r="E5" s="17">
+      <c r="E5" s="15">
         <v>1.0000000000000001e-15</v>
       </c>
-      <c r="F5" s="17">
+      <c r="F5" s="15">
         <v>1e-10</v>
       </c>
-      <c r="G5" s="12" t="s">
+      <c r="G5" s="10" t="s">
         <v>206</v>
       </c>
-      <c r="H5" s="12" t="s">
+      <c r="H5" s="10" t="s">
         <v>91</v>
       </c>
-      <c r="I5" s="12" t="s">
+      <c r="I5" s="10" t="s">
         <v>228</v>
       </c>
-      <c r="J5" s="12" t="s">
+      <c r="J5" s="10" t="s">
         <v>208</v>
       </c>
-      <c r="K5" s="12" t="s">
+      <c r="K5" s="10" t="s">
         <v>229</v>
       </c>
     </row>
@@ -4615,206 +4613,206 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
   <sheetFormatPr baseColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="3" style="12" width="10.28125"/>
-    <col customWidth="1" min="4" max="4" style="12" width="14.57421875"/>
-    <col min="5" max="16384" style="12" width="10.28125"/>
+    <col min="1" max="3" style="10" width="10.28125"/>
+    <col customWidth="1" min="4" max="4" style="10" width="14.57421875"/>
+    <col min="5" max="16384" style="10" width="10.28125"/>
   </cols>
   <sheetData>
     <row r="1" ht="14.25">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="10" t="s">
         <v>191</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="10" t="s">
         <v>192</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="10" t="s">
         <v>193</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="10" t="s">
         <v>194</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="10" t="s">
         <v>195</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="10" t="s">
         <v>196</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="G1" s="10" t="s">
         <v>197</v>
       </c>
-      <c r="H1" s="12" t="s">
+      <c r="H1" s="10" t="s">
         <v>198</v>
       </c>
-      <c r="I1" s="12" t="s">
+      <c r="I1" s="10" t="s">
         <v>199</v>
       </c>
-      <c r="J1" s="12" t="s">
+      <c r="J1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="K1" s="12" t="s">
+      <c r="K1" s="10" t="s">
         <v>200</v>
       </c>
-      <c r="L1" s="12"/>
+      <c r="L1" s="10"/>
     </row>
     <row r="2" ht="51">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="B2" s="12" t="s">
+      <c r="B2" s="10" t="s">
         <v>231</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="C2" s="10" t="s">
         <v>232</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="D2" s="10" t="s">
         <v>233</v>
       </c>
-      <c r="E2" s="18">
+      <c r="E2" s="16">
         <v>0.012</v>
       </c>
-      <c r="F2" s="18">
+      <c r="F2" s="16">
         <v>0.014999999999999999</v>
       </c>
-      <c r="G2" s="12" t="s">
+      <c r="G2" s="10" t="s">
         <v>206</v>
       </c>
-      <c r="H2" s="12" t="s">
+      <c r="H2" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="I2" s="12" t="s">
+      <c r="I2" s="10" t="s">
         <v>207</v>
       </c>
-      <c r="J2" s="12" t="s">
+      <c r="J2" s="10" t="s">
         <v>234</v>
       </c>
-      <c r="K2" s="12" t="s">
+      <c r="K2" s="10" t="s">
         <v>235</v>
       </c>
-      <c r="L2" s="12" t="s">
+      <c r="L2" s="10" t="s">
         <v>236</v>
       </c>
-      <c r="M2" s="12" t="s">
+      <c r="M2" s="10" t="s">
         <v>210</v>
       </c>
     </row>
     <row r="3" ht="51">
-      <c r="A3" s="12" t="s">
+      <c r="A3" s="10" t="s">
         <v>237</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="B3" s="10" t="s">
         <v>238</v>
       </c>
-      <c r="C3" s="12" t="s">
+      <c r="C3" s="10" t="s">
         <v>239</v>
       </c>
-      <c r="D3" s="12" t="s">
+      <c r="D3" s="10" t="s">
         <v>240</v>
       </c>
-      <c r="E3" s="15">
+      <c r="E3" s="13">
         <v>0.14999999999999999</v>
       </c>
-      <c r="F3" s="15">
+      <c r="F3" s="13">
         <v>0.29999999999999999</v>
       </c>
-      <c r="G3" s="12" t="s">
+      <c r="G3" s="10" t="s">
         <v>206</v>
       </c>
-      <c r="H3" s="12" t="s">
+      <c r="H3" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="I3" s="12" t="s">
+      <c r="I3" s="10" t="s">
         <v>207</v>
       </c>
-      <c r="J3" s="12" t="s">
+      <c r="J3" s="10" t="s">
         <v>234</v>
       </c>
-      <c r="K3" s="12" t="s">
+      <c r="K3" s="10" t="s">
         <v>241</v>
       </c>
-      <c r="L3" s="12" t="s">
+      <c r="L3" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="M3" s="12" t="s">
+      <c r="M3" s="10" t="s">
         <v>242</v>
       </c>
     </row>
     <row r="4" ht="51">
-      <c r="A4" s="12" t="s">
+      <c r="A4" s="10" t="s">
         <v>243</v>
       </c>
-      <c r="B4" s="12" t="s">
+      <c r="B4" s="10" t="s">
         <v>244</v>
       </c>
-      <c r="C4" s="12" t="s">
+      <c r="C4" s="10" t="s">
         <v>245</v>
       </c>
-      <c r="D4" s="12" t="s">
+      <c r="D4" s="10" t="s">
         <v>246</v>
       </c>
-      <c r="E4" s="13">
+      <c r="E4" s="11">
         <v>0.29999999999999999</v>
       </c>
-      <c r="F4" s="13">
+      <c r="F4" s="11">
         <v>0.90000000000000002</v>
       </c>
-      <c r="G4" s="12" t="s">
+      <c r="G4" s="10" t="s">
         <v>206</v>
       </c>
-      <c r="H4" s="12" t="s">
+      <c r="H4" s="10" t="s">
         <v>91</v>
       </c>
-      <c r="I4" s="12" t="s">
+      <c r="I4" s="10" t="s">
         <v>247</v>
       </c>
-      <c r="J4" s="12" t="s">
+      <c r="J4" s="10" t="s">
         <v>234</v>
       </c>
-      <c r="K4" s="12" t="s">
+      <c r="K4" s="10" t="s">
         <v>248</v>
       </c>
-      <c r="L4" s="12" t="s">
+      <c r="L4" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="M4" s="12" t="s">
+      <c r="M4" s="10" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="5" s="19" customFormat="1" ht="38.25">
-      <c r="A5" s="19" t="s">
+    <row r="5" s="17" customFormat="1" ht="38.25">
+      <c r="A5" s="17" t="s">
         <v>250</v>
       </c>
-      <c r="B5" s="19" t="s">
+      <c r="B5" s="17" t="s">
         <v>251</v>
       </c>
-      <c r="C5" s="19" t="s">
+      <c r="C5" s="17" t="s">
         <v>252</v>
       </c>
-      <c r="D5" s="19" t="s">
+      <c r="D5" s="17" t="s">
         <v>253</v>
       </c>
-      <c r="E5" s="19">
+      <c r="E5" s="17">
         <v>10</v>
       </c>
-      <c r="F5" s="19">
+      <c r="F5" s="17">
         <v>5</v>
       </c>
-      <c r="G5" s="19" t="s">
+      <c r="G5" s="17" t="s">
         <v>254</v>
       </c>
-      <c r="H5" s="19" t="s">
+      <c r="H5" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="I5" s="19" t="s">
+      <c r="I5" s="17" t="s">
         <v>221</v>
       </c>
-      <c r="J5" s="19" t="s">
+      <c r="J5" s="17" t="s">
         <v>234</v>
       </c>
-      <c r="K5" s="19" t="s">
+      <c r="K5" s="17" t="s">
         <v>255</v>
       </c>
-      <c r="L5" s="19"/>
-      <c r="M5" s="16" t="s">
+      <c r="L5" s="17"/>
+      <c r="M5" s="14" t="s">
         <v>256</v>
       </c>
     </row>
@@ -4830,220 +4828,220 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
   <sheetFormatPr baseColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="3" style="12" width="10.28125"/>
-    <col customWidth="1" min="4" max="4" style="12" width="14.421875"/>
-    <col min="5" max="6" style="12" width="10.28125"/>
-    <col customWidth="1" min="7" max="7" style="12" width="14.00390625"/>
-    <col min="8" max="14" style="12" width="10.28125"/>
-    <col customWidth="1" min="15" max="15" style="12" width="20.140625"/>
-    <col min="16" max="16384" style="12" width="10.28125"/>
+    <col min="1" max="3" style="10" width="10.28125"/>
+    <col customWidth="1" min="4" max="4" style="10" width="14.421875"/>
+    <col min="5" max="6" style="10" width="10.28125"/>
+    <col customWidth="1" min="7" max="7" style="10" width="14.00390625"/>
+    <col min="8" max="14" style="10" width="10.28125"/>
+    <col customWidth="1" min="15" max="15" style="10" width="20.140625"/>
+    <col min="16" max="16384" style="10" width="10.28125"/>
   </cols>
   <sheetData>
     <row r="1" ht="14.25">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="10" t="s">
         <v>191</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="10" t="s">
         <v>192</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="10" t="s">
         <v>193</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="10" t="s">
         <v>194</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="10" t="s">
         <v>195</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="10" t="s">
         <v>196</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="G1" s="10" t="s">
         <v>197</v>
       </c>
-      <c r="H1" s="12" t="s">
+      <c r="H1" s="10" t="s">
         <v>198</v>
       </c>
-      <c r="I1" s="12" t="s">
+      <c r="I1" s="10" t="s">
         <v>199</v>
       </c>
-      <c r="J1" s="12" t="s">
+      <c r="J1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="K1" s="12" t="s">
+      <c r="K1" s="10" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="2" ht="153">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="10" t="s">
         <v>257</v>
       </c>
-      <c r="B2" s="12" t="s">
+      <c r="B2" s="10" t="s">
         <v>258</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="C2" s="10" t="s">
         <v>259</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="D2" s="10" t="s">
         <v>260</v>
       </c>
-      <c r="E2" s="12" t="s">
+      <c r="E2" s="10" t="s">
         <v>261</v>
       </c>
-      <c r="F2" s="12" t="s">
+      <c r="F2" s="10" t="s">
         <v>262</v>
       </c>
-      <c r="G2" s="12" t="s">
+      <c r="G2" s="10" t="s">
         <v>263</v>
       </c>
-      <c r="H2" s="12">
+      <c r="H2" s="10">
         <v>180</v>
       </c>
-      <c r="I2" s="12">
+      <c r="I2" s="10">
         <v>3650</v>
       </c>
-      <c r="J2" s="12" t="s">
+      <c r="J2" s="10" t="s">
         <v>264</v>
       </c>
-      <c r="K2" s="12" t="s">
+      <c r="K2" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="L2" s="12" t="s">
+      <c r="L2" s="10" t="s">
         <v>207</v>
       </c>
-      <c r="M2" s="12" t="s">
+      <c r="M2" s="10" t="s">
         <v>265</v>
       </c>
-      <c r="N2" s="12" t="s">
+      <c r="N2" s="10" t="s">
         <v>266</v>
       </c>
-      <c r="O2" s="20" t="s">
+      <c r="O2" s="18" t="s">
         <v>267</v>
       </c>
-      <c r="P2" s="12" t="s">
+      <c r="P2" s="10" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="3" ht="51">
-      <c r="A3" s="12" t="s">
+      <c r="A3" s="10" t="s">
         <v>268</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="B3" s="10" t="s">
         <v>269</v>
       </c>
-      <c r="C3" s="12" t="s">
+      <c r="C3" s="10" t="s">
         <v>270</v>
       </c>
-      <c r="D3" s="12" t="s">
+      <c r="D3" s="10" t="s">
         <v>271</v>
       </c>
-      <c r="E3" s="15">
+      <c r="E3" s="13">
         <v>0.84999999999999998</v>
       </c>
-      <c r="F3" s="15">
+      <c r="F3" s="13">
         <v>0.98999999999999999</v>
       </c>
-      <c r="G3" s="12" t="s">
+      <c r="G3" s="10" t="s">
         <v>206</v>
       </c>
-      <c r="H3" s="12" t="s">
+      <c r="H3" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="I3" s="12" t="s">
+      <c r="I3" s="10" t="s">
         <v>207</v>
       </c>
-      <c r="J3" s="12" t="s">
+      <c r="J3" s="10" t="s">
         <v>265</v>
       </c>
-      <c r="K3" s="12" t="s">
+      <c r="K3" s="10" t="s">
         <v>272</v>
       </c>
-      <c r="O3" s="20"/>
+      <c r="O3" s="18"/>
     </row>
     <row r="4" ht="38.25">
-      <c r="A4" s="12" t="s">
+      <c r="A4" s="10" t="s">
         <v>273</v>
       </c>
-      <c r="B4" s="12" t="s">
+      <c r="B4" s="10" t="s">
         <v>274</v>
       </c>
-      <c r="C4" s="12" t="s">
+      <c r="C4" s="10" t="s">
         <v>275</v>
       </c>
-      <c r="D4" s="12" t="s">
+      <c r="D4" s="10" t="s">
         <v>276</v>
       </c>
-      <c r="E4" s="13">
+      <c r="E4" s="11">
         <v>1.5</v>
       </c>
-      <c r="F4" s="13">
+      <c r="F4" s="11">
         <v>2.5</v>
       </c>
-      <c r="G4" s="12" t="s">
+      <c r="G4" s="10" t="s">
         <v>206</v>
       </c>
-      <c r="H4" s="12" t="s">
+      <c r="H4" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="I4" s="12" t="s">
+      <c r="I4" s="10" t="s">
         <v>277</v>
       </c>
-      <c r="J4" s="12" t="s">
+      <c r="J4" s="10" t="s">
         <v>265</v>
       </c>
-      <c r="K4" s="12" t="s">
+      <c r="K4" s="10" t="s">
         <v>278</v>
       </c>
-      <c r="O4" s="20" t="s">
+      <c r="O4" s="18" t="s">
         <v>279</v>
       </c>
     </row>
     <row r="5" ht="51">
-      <c r="A5" s="12" t="s">
+      <c r="A5" s="10" t="s">
         <v>280</v>
       </c>
-      <c r="B5" s="12" t="s">
+      <c r="B5" s="10" t="s">
         <v>281</v>
       </c>
-      <c r="C5" s="12" t="s">
+      <c r="C5" s="10" t="s">
         <v>282</v>
       </c>
-      <c r="D5" s="12" t="s">
+      <c r="D5" s="10" t="s">
         <v>283</v>
       </c>
-      <c r="E5" s="13">
+      <c r="E5" s="11">
         <v>0.69999999999999996</v>
       </c>
-      <c r="F5" s="15">
+      <c r="F5" s="13">
         <v>1.05</v>
       </c>
-      <c r="G5" s="12" t="s">
+      <c r="G5" s="10" t="s">
         <v>206</v>
       </c>
-      <c r="H5" s="12" t="s">
+      <c r="H5" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="I5" s="12" t="s">
+      <c r="I5" s="10" t="s">
         <v>284</v>
       </c>
-      <c r="J5" s="12" t="s">
+      <c r="J5" s="10" t="s">
         <v>265</v>
       </c>
-      <c r="K5" s="12" t="s">
+      <c r="K5" s="10" t="s">
         <v>285</v>
       </c>
-      <c r="O5" s="20"/>
+      <c r="O5" s="18"/>
     </row>
     <row r="6" ht="89.25">
-      <c r="O6" s="20" t="s">
+      <c r="O6" s="18" t="s">
         <v>286</v>
       </c>
     </row>
     <row r="7" ht="14.25">
-      <c r="O7" s="20"/>
+      <c r="O7" s="18"/>
     </row>
     <row r="8" ht="51">
-      <c r="O8" s="20" t="s">
+      <c r="O8" s="18" t="s">
         <v>287</v>
       </c>
     </row>
@@ -5059,183 +5057,183 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
   <sheetFormatPr baseColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="3" style="12" width="10.28125"/>
-    <col customWidth="1" min="4" max="4" style="12" width="18.28125"/>
-    <col min="5" max="16384" style="12" width="10.28125"/>
+    <col min="1" max="3" style="10" width="10.28125"/>
+    <col customWidth="1" min="4" max="4" style="10" width="18.28125"/>
+    <col min="5" max="16384" style="10" width="10.28125"/>
   </cols>
   <sheetData>
     <row r="1" ht="14.25">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="10" t="s">
         <v>191</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="10" t="s">
         <v>192</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="10" t="s">
         <v>193</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="10" t="s">
         <v>194</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="10" t="s">
         <v>195</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="10" t="s">
         <v>196</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="G1" s="10" t="s">
         <v>197</v>
       </c>
-      <c r="H1" s="12" t="s">
+      <c r="H1" s="10" t="s">
         <v>198</v>
       </c>
-      <c r="I1" s="12" t="s">
+      <c r="I1" s="10" t="s">
         <v>199</v>
       </c>
-      <c r="J1" s="12" t="s">
+      <c r="J1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="K1" s="12" t="s">
+      <c r="K1" s="10" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="2" ht="38.25">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="10" t="s">
         <v>288</v>
       </c>
-      <c r="B2" s="12" t="s">
+      <c r="B2" s="10" t="s">
         <v>289</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="C2" s="10" t="s">
         <v>290</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="D2" s="10" t="s">
         <v>291</v>
       </c>
-      <c r="E2" s="15">
+      <c r="E2" s="13">
         <v>0.25</v>
       </c>
-      <c r="F2" s="15">
+      <c r="F2" s="13">
         <v>0.90000000000000002</v>
       </c>
-      <c r="G2" s="12" t="s">
+      <c r="G2" s="10" t="s">
         <v>206</v>
       </c>
-      <c r="H2" s="12" t="s">
+      <c r="H2" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="I2" s="12" t="s">
+      <c r="I2" s="10" t="s">
         <v>247</v>
       </c>
-      <c r="J2" s="12" t="s">
+      <c r="J2" s="10" t="s">
         <v>292</v>
       </c>
-      <c r="K2" s="12" t="s">
+      <c r="K2" s="10" t="s">
         <v>293</v>
       </c>
     </row>
     <row r="3" ht="63.75">
-      <c r="A3" s="12" t="s">
+      <c r="A3" s="10" t="s">
         <v>294</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="B3" s="10" t="s">
         <v>295</v>
       </c>
-      <c r="C3" s="12" t="s">
+      <c r="C3" s="10" t="s">
         <v>296</v>
       </c>
-      <c r="D3" s="12" t="s">
+      <c r="D3" s="10" t="s">
         <v>297</v>
       </c>
-      <c r="E3" s="13">
+      <c r="E3" s="11">
         <v>1.5</v>
       </c>
-      <c r="F3" s="21">
+      <c r="F3" s="19">
         <v>10</v>
       </c>
-      <c r="G3" s="12" t="s">
+      <c r="G3" s="10" t="s">
         <v>206</v>
       </c>
-      <c r="H3" s="12" t="s">
+      <c r="H3" s="10" t="s">
         <v>91</v>
       </c>
-      <c r="I3" s="12" t="s">
+      <c r="I3" s="10" t="s">
         <v>221</v>
       </c>
-      <c r="J3" s="12" t="s">
+      <c r="J3" s="10" t="s">
         <v>292</v>
       </c>
-      <c r="K3" s="12" t="s">
+      <c r="K3" s="10" t="s">
         <v>298</v>
       </c>
     </row>
     <row r="4" ht="25.5">
-      <c r="A4" s="12" t="s">
+      <c r="A4" s="10" t="s">
         <v>299</v>
       </c>
-      <c r="B4" s="12" t="s">
+      <c r="B4" s="10" t="s">
         <v>300</v>
       </c>
-      <c r="C4" s="12" t="s">
+      <c r="C4" s="10" t="s">
         <v>301</v>
       </c>
-      <c r="D4" s="12" t="s">
+      <c r="D4" s="10" t="s">
         <v>302</v>
       </c>
-      <c r="E4" s="15">
+      <c r="E4" s="13">
         <v>0.01</v>
       </c>
-      <c r="F4" s="15">
+      <c r="F4" s="13">
         <v>0.10000000000000001</v>
       </c>
-      <c r="G4" s="12" t="s">
+      <c r="G4" s="10" t="s">
         <v>303</v>
       </c>
-      <c r="H4" s="12" t="s">
+      <c r="H4" s="10" t="s">
         <v>91</v>
       </c>
-      <c r="I4" s="12" t="s">
+      <c r="I4" s="10" t="s">
         <v>228</v>
       </c>
-      <c r="J4" s="12" t="s">
+      <c r="J4" s="10" t="s">
         <v>292</v>
       </c>
-      <c r="K4" s="12" t="s">
+      <c r="K4" s="10" t="s">
         <v>304</v>
       </c>
     </row>
     <row r="5" ht="38.25">
-      <c r="A5" s="12" t="s">
+      <c r="A5" s="10" t="s">
         <v>305</v>
       </c>
-      <c r="B5" s="12" t="s">
+      <c r="B5" s="10" t="s">
         <v>306</v>
       </c>
-      <c r="C5" s="12" t="s">
+      <c r="C5" s="10" t="s">
         <v>307</v>
       </c>
-      <c r="D5" s="12" t="s">
+      <c r="D5" s="10" t="s">
         <v>308</v>
       </c>
-      <c r="E5" s="15">
+      <c r="E5" s="13">
         <v>0.29999999999999999</v>
       </c>
-      <c r="F5" s="15">
+      <c r="F5" s="13">
         <v>0.80000000000000004</v>
       </c>
-      <c r="G5" s="12" t="s">
+      <c r="G5" s="10" t="s">
         <v>206</v>
       </c>
-      <c r="H5" s="12" t="s">
+      <c r="H5" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="I5" s="12" t="s">
+      <c r="I5" s="10" t="s">
         <v>207</v>
       </c>
-      <c r="J5" s="12" t="s">
+      <c r="J5" s="10" t="s">
         <v>292</v>
       </c>
-      <c r="K5" s="12" t="s">
+      <c r="K5" s="10" t="s">
         <v>309</v>
       </c>
     </row>
@@ -5251,185 +5249,185 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" style="12" width="9.140625"/>
-    <col customWidth="1" min="2" max="2" style="12" width="11.57421875"/>
-    <col customWidth="1" min="3" max="3" style="12" width="12.421875"/>
-    <col customWidth="1" min="4" max="4" style="12" width="14.421875"/>
-    <col min="5" max="16384" style="12" width="9.140625"/>
+    <col min="1" max="1" style="10" width="9.140625"/>
+    <col customWidth="1" min="2" max="2" style="10" width="11.57421875"/>
+    <col customWidth="1" min="3" max="3" style="10" width="12.421875"/>
+    <col customWidth="1" min="4" max="4" style="10" width="14.421875"/>
+    <col min="5" max="16384" style="10" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="10" t="s">
         <v>191</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="10" t="s">
         <v>192</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="10" t="s">
         <v>193</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="10" t="s">
         <v>194</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="10" t="s">
         <v>195</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="10" t="s">
         <v>196</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="G1" s="10" t="s">
         <v>197</v>
       </c>
-      <c r="H1" s="12" t="s">
+      <c r="H1" s="10" t="s">
         <v>198</v>
       </c>
-      <c r="I1" s="12" t="s">
+      <c r="I1" s="10" t="s">
         <v>199</v>
       </c>
-      <c r="J1" s="12" t="s">
+      <c r="J1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="K1" s="12" t="s">
+      <c r="K1" s="10" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="2" ht="38.25">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="10" t="s">
         <v>310</v>
       </c>
-      <c r="B2" s="12" t="s">
+      <c r="B2" s="10" t="s">
         <v>311</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="C2" s="10" t="s">
         <v>312</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="D2" s="10" t="s">
         <v>313</v>
       </c>
-      <c r="E2" s="12">
+      <c r="E2" s="10">
         <v>0.10000000000000001</v>
       </c>
-      <c r="F2" s="12">
+      <c r="F2" s="10">
         <v>0.94999999999999996</v>
       </c>
-      <c r="G2" s="12" t="s">
+      <c r="G2" s="10" t="s">
         <v>206</v>
       </c>
-      <c r="H2" s="12" t="s">
+      <c r="H2" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="I2" s="12" t="s">
+      <c r="I2" s="10" t="s">
         <v>207</v>
       </c>
-      <c r="J2" s="12" t="s">
+      <c r="J2" s="10" t="s">
         <v>314</v>
       </c>
-      <c r="K2" s="12" t="s">
+      <c r="K2" s="10" t="s">
         <v>315</v>
       </c>
     </row>
     <row r="3" ht="51">
-      <c r="A3" s="12" t="s">
+      <c r="A3" s="10" t="s">
         <v>316</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="B3" s="10" t="s">
         <v>317</v>
       </c>
-      <c r="C3" s="12" t="s">
+      <c r="C3" s="10" t="s">
         <v>318</v>
       </c>
-      <c r="D3" s="12" t="s">
+      <c r="D3" s="10" t="s">
         <v>319</v>
       </c>
-      <c r="E3" s="12">
+      <c r="E3" s="10">
         <v>100</v>
       </c>
-      <c r="F3" s="12">
+      <c r="F3" s="10">
         <v>1</v>
       </c>
-      <c r="G3" s="12" t="s">
+      <c r="G3" s="10" t="s">
         <v>320</v>
       </c>
-      <c r="H3" s="12" t="s">
+      <c r="H3" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="I3" s="12" t="s">
+      <c r="I3" s="10" t="s">
         <v>247</v>
       </c>
-      <c r="J3" s="12" t="s">
+      <c r="J3" s="10" t="s">
         <v>314</v>
       </c>
-      <c r="K3" s="12" t="s">
+      <c r="K3" s="10" t="s">
         <v>321</v>
       </c>
     </row>
     <row r="4" ht="51">
-      <c r="A4" s="12" t="s">
+      <c r="A4" s="10" t="s">
         <v>322</v>
       </c>
-      <c r="B4" s="12" t="s">
+      <c r="B4" s="10" t="s">
         <v>323</v>
       </c>
-      <c r="C4" s="12" t="s">
+      <c r="C4" s="10" t="s">
         <v>324</v>
       </c>
-      <c r="D4" s="12" t="s">
+      <c r="D4" s="10" t="s">
         <v>325</v>
       </c>
-      <c r="E4" s="12">
+      <c r="E4" s="10">
         <v>0.10000000000000001</v>
       </c>
-      <c r="F4" s="12">
+      <c r="F4" s="10">
         <v>0.001</v>
       </c>
-      <c r="G4" s="12" t="s">
+      <c r="G4" s="10" t="s">
         <v>206</v>
       </c>
-      <c r="H4" s="12" t="s">
+      <c r="H4" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="I4" s="12" t="s">
+      <c r="I4" s="10" t="s">
         <v>207</v>
       </c>
-      <c r="J4" s="12" t="s">
+      <c r="J4" s="10" t="s">
         <v>314</v>
       </c>
-      <c r="K4" s="12" t="s">
+      <c r="K4" s="10" t="s">
         <v>326</v>
       </c>
     </row>
     <row r="5" ht="51">
-      <c r="A5" s="12" t="s">
+      <c r="A5" s="10" t="s">
         <v>327</v>
       </c>
-      <c r="B5" s="12" t="s">
+      <c r="B5" s="10" t="s">
         <v>328</v>
       </c>
-      <c r="C5" s="12" t="s">
+      <c r="C5" s="10" t="s">
         <v>329</v>
       </c>
-      <c r="D5" s="12" t="s">
+      <c r="D5" s="10" t="s">
         <v>330</v>
       </c>
-      <c r="E5" s="12">
+      <c r="E5" s="10">
         <v>0.69999999999999996</v>
       </c>
-      <c r="F5" s="12">
+      <c r="F5" s="10">
         <v>0.98999999999999999</v>
       </c>
-      <c r="G5" s="12" t="s">
+      <c r="G5" s="10" t="s">
         <v>206</v>
       </c>
-      <c r="H5" s="12" t="s">
+      <c r="H5" s="10" t="s">
         <v>91</v>
       </c>
-      <c r="I5" s="12" t="s">
+      <c r="I5" s="10" t="s">
         <v>331</v>
       </c>
-      <c r="J5" s="12" t="s">
+      <c r="J5" s="10" t="s">
         <v>314</v>
       </c>
-      <c r="K5" s="12" t="s">
+      <c r="K5" s="10" t="s">
         <v>332</v>
       </c>
     </row>
@@ -5445,191 +5443,191 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="3" style="12" width="9.140625"/>
-    <col customWidth="1" min="4" max="4" style="12" width="14.28125"/>
-    <col min="5" max="5" style="12" width="9.140625"/>
-    <col customWidth="1" min="6" max="6" style="12" width="13.7109375"/>
-    <col min="7" max="16384" style="12" width="9.140625"/>
+    <col min="1" max="3" style="10" width="9.140625"/>
+    <col customWidth="1" min="4" max="4" style="10" width="14.28125"/>
+    <col min="5" max="5" style="10" width="9.140625"/>
+    <col customWidth="1" min="6" max="6" style="10" width="13.7109375"/>
+    <col min="7" max="16384" style="10" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="10" t="s">
         <v>191</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="10" t="s">
         <v>192</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="10" t="s">
         <v>193</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="10" t="s">
         <v>194</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="10" t="s">
         <v>195</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="10" t="s">
         <v>196</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="G1" s="10" t="s">
         <v>197</v>
       </c>
-      <c r="H1" s="12" t="s">
+      <c r="H1" s="10" t="s">
         <v>198</v>
       </c>
-      <c r="I1" s="12" t="s">
+      <c r="I1" s="10" t="s">
         <v>199</v>
       </c>
-      <c r="J1" s="12" t="s">
+      <c r="J1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="K1" s="12" t="s">
+      <c r="K1" s="10" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="2" ht="38.25">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="12" t="s">
+      <c r="B2" s="10" t="s">
         <v>333</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="C2" s="10" t="s">
         <v>334</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="D2" s="10" t="s">
         <v>335</v>
       </c>
-      <c r="E2" s="12">
+      <c r="E2" s="10">
         <v>10000</v>
       </c>
-      <c r="F2" s="12">
+      <c r="F2" s="10">
         <v>100</v>
       </c>
-      <c r="G2" s="12" t="s">
+      <c r="G2" s="10" t="s">
         <v>336</v>
       </c>
-      <c r="H2" s="12" t="s">
+      <c r="H2" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="I2" s="12" t="s">
+      <c r="I2" s="10" t="s">
         <v>207</v>
       </c>
-      <c r="J2" s="12" t="s">
+      <c r="J2" s="10" t="s">
         <v>111</v>
       </c>
-      <c r="K2" s="12" t="s">
+      <c r="K2" s="10" t="s">
         <v>337</v>
       </c>
     </row>
     <row r="3" ht="51">
-      <c r="A3" s="12" t="s">
+      <c r="A3" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="B3" s="10" t="s">
         <v>338</v>
       </c>
-      <c r="C3" s="12" t="s">
+      <c r="C3" s="10" t="s">
         <v>339</v>
       </c>
-      <c r="D3" s="12" t="s">
+      <c r="D3" s="10" t="s">
         <v>340</v>
       </c>
-      <c r="E3" s="12">
+      <c r="E3" s="10">
         <v>100</v>
       </c>
-      <c r="F3" s="12">
+      <c r="F3" s="10">
         <v>10</v>
       </c>
-      <c r="G3" s="12" t="s">
+      <c r="G3" s="10" t="s">
         <v>341</v>
       </c>
-      <c r="H3" s="12" t="s">
+      <c r="H3" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="I3" s="12" t="s">
+      <c r="I3" s="10" t="s">
         <v>207</v>
       </c>
-      <c r="J3" s="12" t="s">
+      <c r="J3" s="10" t="s">
         <v>111</v>
       </c>
-      <c r="K3" s="12" t="s">
+      <c r="K3" s="10" t="s">
         <v>342</v>
       </c>
     </row>
     <row r="4" ht="51">
-      <c r="A4" s="12" t="s">
+      <c r="A4" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="B4" s="12" t="s">
+      <c r="B4" s="10" t="s">
         <v>343</v>
       </c>
-      <c r="C4" s="12" t="s">
+      <c r="C4" s="10" t="s">
         <v>344</v>
       </c>
-      <c r="D4" s="12" t="s">
+      <c r="D4" s="10" t="s">
         <v>345</v>
       </c>
-      <c r="E4" s="12" t="s">
+      <c r="E4" s="10" t="s">
         <v>346</v>
       </c>
-      <c r="F4" s="12" t="s">
+      <c r="F4" s="10" t="s">
         <v>347</v>
       </c>
-      <c r="G4" s="12">
+      <c r="G4" s="10">
         <v>10</v>
       </c>
-      <c r="H4" s="12">
+      <c r="H4" s="10">
         <v>2</v>
       </c>
-      <c r="I4" s="12" t="s">
+      <c r="I4" s="10" t="s">
         <v>348</v>
       </c>
-      <c r="J4" s="12" t="s">
+      <c r="J4" s="10" t="s">
         <v>91</v>
       </c>
-      <c r="K4" s="12" t="s">
+      <c r="K4" s="10" t="s">
         <v>221</v>
       </c>
-      <c r="L4" s="12" t="s">
+      <c r="L4" s="10" t="s">
         <v>111</v>
       </c>
-      <c r="M4" s="12" t="s">
+      <c r="M4" s="10" t="s">
         <v>349</v>
       </c>
     </row>
     <row r="5" ht="51">
-      <c r="A5" s="12" t="s">
+      <c r="A5" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="B5" s="12" t="s">
+      <c r="B5" s="10" t="s">
         <v>350</v>
       </c>
-      <c r="C5" s="12" t="s">
+      <c r="C5" s="10" t="s">
         <v>351</v>
       </c>
-      <c r="D5" s="12" t="s">
+      <c r="D5" s="10" t="s">
         <v>352</v>
       </c>
-      <c r="E5" s="12">
+      <c r="E5" s="10">
         <v>0.80000000000000004</v>
       </c>
-      <c r="F5" s="12">
+      <c r="F5" s="10">
         <v>0.59999999999999998</v>
       </c>
-      <c r="G5" s="12" t="s">
+      <c r="G5" s="10" t="s">
         <v>206</v>
       </c>
-      <c r="H5" s="12" t="s">
+      <c r="H5" s="10" t="s">
         <v>91</v>
       </c>
-      <c r="I5" s="12" t="s">
+      <c r="I5" s="10" t="s">
         <v>228</v>
       </c>
-      <c r="J5" s="12" t="s">
+      <c r="J5" s="10" t="s">
         <v>111</v>
       </c>
-      <c r="K5" s="12" t="s">
+      <c r="K5" s="10" t="s">
         <v>353</v>
       </c>
     </row>
